--- a/workspaces/btc_daily_14days/ma/ma_ratio_100.xlsx
+++ b/workspaces/btc_daily_14days/ma/ma_ratio_100.xlsx
@@ -575,46 +575,46 @@
         <v>44</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>13.41565258888093</v>
+        <v>13.37135203736668</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-6.379328402191803</v>
+        <v>-6.358668850415874</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>6.867286182442562</v>
+        <v>6.844338201695017</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>11.54822885860724</v>
+        <v>11.51024521299609</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>15.56225827653864</v>
+        <v>15.51103325779674</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>6.76162189465316</v>
+        <v>6.739281874257507</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>11.23089235625906</v>
+        <v>11.19375146684552</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>1.658813057740304</v>
+        <v>1.652953511781874</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>8.429795862389945</v>
+        <v>8.402242341617928</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>7.580115028803995</v>
+        <v>7.554981169368695</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>5.098349932964126</v>
+        <v>5.08129930790578</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>14.2500636969741</v>
+        <v>14.20333770102872</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>4.713430207809907</v>
+        <v>4.698190314445505</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>7.245305255537914</v>
+        <v>7.221811218940068</v>
       </c>
     </row>
     <row r="7">
@@ -627,46 +627,46 @@
         <v>78</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-1.211387038158399</v>
+        <v>-1.208170396290733</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-4.106066309468424</v>
+        <v>-4.09235941764279</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-8.350221182385255</v>
+        <v>-8.3230076553929</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-8.221995651734154</v>
+        <v>-8.195067025260734</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-10.04634402967646</v>
+        <v>-10.01355094716027</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-9.751185588679533</v>
+        <v>-9.71901403119741</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-13.69047854252545</v>
+        <v>-13.64545723204775</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-15.44647657351994</v>
+        <v>-15.39532637138227</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-10.37292958170239</v>
+        <v>-10.33847849824755</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-11.22744375237865</v>
+        <v>-11.19048092114885</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-12.72096284922141</v>
+        <v>-12.67896746349899</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-17.83247115685813</v>
+        <v>-17.77339149910136</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-16.97310875304925</v>
+        <v>-16.91631527719988</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-18.0132377140777</v>
+        <v>-17.95301395588614</v>
       </c>
     </row>
     <row r="8">
@@ -679,46 +679,46 @@
         <v>92</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-6.841264407166747</v>
+        <v>-6.818623309316052</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-3.018870601286189</v>
+        <v>-3.008273133222616</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-2.327168421540314</v>
+        <v>-2.319363057430444</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-3.285262056746511</v>
+        <v>-3.274034081018286</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-4.913181757472927</v>
+        <v>-4.896499392952492</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-4.616771676320688</v>
+        <v>-4.600742957639355</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-9.057553371207177</v>
+        <v>-9.026382009214402</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-9.528212309482647</v>
+        <v>-9.495039425856902</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-11.77035808904405</v>
+        <v>-11.72957843478179</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-13.71497801958076</v>
+        <v>-13.66784089257041</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-8.474880515358997</v>
+        <v>-8.445545786846381</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-12.80341438556844</v>
+        <v>-12.75891170257652</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-8.867335176592654</v>
+        <v>-8.835757761227569</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-7.528523200573048</v>
+        <v>-7.501508939163735</v>
       </c>
     </row>
     <row r="9">
@@ -731,46 +731,46 @@
         <v>114</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-3.370631302666311</v>
+        <v>-3.358977213017077</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-7.615893173350145</v>
+        <v>-7.58847213878402</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-7.135339312925808</v>
+        <v>-7.110121095313531</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-4.373250008291102</v>
+        <v>-4.357552503402211</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-2.27902833741966</v>
+        <v>-2.270713009121685</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-3.738731264655136</v>
+        <v>-3.724905861916973</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-3.824812202438899</v>
+        <v>-3.81037205571549</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-2.536514432458404</v>
+        <v>-2.526171113844534</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>1.796999114027599</v>
+        <v>1.792158172184145</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-0.8134146435311038</v>
+        <v>-0.8091917141646832</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-1.898403879493898</v>
+        <v>-1.890647435118325</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-1.865138949636361</v>
+        <v>-1.856766094991706</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-1.407582962008483</v>
+        <v>-1.400576929376911</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-1.157425805202415</v>
+        <v>-1.151394522687752</v>
       </c>
     </row>
     <row r="10">
@@ -780,49 +780,49 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-5.090840917612425</v>
+        <v>-5.106786151949301</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-6.054890961691555</v>
+        <v>-6.07495302170269</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-3.852843609376571</v>
+        <v>-3.865545831098245</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-2.423815556539587</v>
+        <v>-2.432014239937608</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-0.3631749278623886</v>
+        <v>-0.3647691465163945</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-0.7159402844184655</v>
+        <v>-0.7190969187767493</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-2.752636082180494</v>
+        <v>-2.762422408738125</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-3.221824251836743</v>
+        <v>-3.233357270369709</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-3.283787556736549</v>
+        <v>-3.295201287369927</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-2.835198989625219</v>
+        <v>-2.84532933422873</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-1.087718974461744</v>
+        <v>-1.092244952838954</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>0.2484544517724459</v>
+        <v>0.2474233899768308</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-0.1735281634387178</v>
+        <v>-0.1760544837931519</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>2.40337578954567</v>
+        <v>2.408976994340108</v>
       </c>
     </row>
     <row r="11">
@@ -832,49 +832,49 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>209</v>
+        <v>200</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-0.8187971718846114</v>
+        <v>-0.866147602778149</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>2.616411182829232</v>
+        <v>2.702054596937231</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>3.920276389216852</v>
+        <v>4.075076075693801</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>1.439392140601925</v>
+        <v>1.488469202304323</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>3.562371472301962</v>
+        <v>3.711761923244858</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>1.249516778070337</v>
+        <v>1.289473238831334</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-2.392250424112149</v>
+        <v>-2.520945800487674</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-2.365114930672462</v>
+        <v>-2.497748238691834</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>1.401884712279511</v>
+        <v>1.439700272498136</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>2.491791476404636</v>
+        <v>2.576819911421516</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>3.997350929981735</v>
+        <v>4.154514133688352</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>5.265972590470241</v>
+        <v>5.471789789307785</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>3.702296162885119</v>
+        <v>3.835726250299111</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>1.540706858894957</v>
+        <v>1.585447582575391</v>
       </c>
     </row>
     <row r="12">
@@ -884,49 +884,49 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-2.493438320210053</v>
+        <v>-2.523514265993981</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-3.048673905005295</v>
+        <v>-3.087093960625424</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-3.443542611601885</v>
+        <v>-3.482284335091364</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-2.256951450825127</v>
+        <v>-2.283772208382011</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-0.3305839335030143</v>
+        <v>-0.3336635635620127</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-0.03314199578743171</v>
+        <v>-0.03654329371578058</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>0.5863496390529619</v>
+        <v>0.5849984074749557</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>2.429016905443859</v>
+        <v>2.446034185483427</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>0.80262405598328</v>
+        <v>0.8059673389771902</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>0.5092440437278896</v>
+        <v>0.5099809214546767</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>0.6562848375571519</v>
+        <v>0.6610994832580985</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>1.043417786777923</v>
+        <v>1.051354526724445</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-0.07469101808803913</v>
+        <v>-0.08064385646245853</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>0.1721632930021002</v>
+        <v>0.1690774758139142</v>
       </c>
     </row>
     <row r="13">
@@ -2213,10 +2213,8 @@
           <t>X &gt; -0.3302</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>3997~4010</t>
-        </is>
+      <c r="B6" t="n">
+        <v>3997</v>
       </c>
       <c r="C6" s="4" t="n">
         <v>-0.09942335761645893</v>
@@ -2267,10 +2265,8 @@
           <t>X &gt; -0.2939</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>3953~3966</t>
-        </is>
+      <c r="B7" t="n">
+        <v>3953</v>
       </c>
       <c r="C7" s="4" t="n">
         <v>-0.2493636858176416</v>
@@ -2321,10 +2317,8 @@
           <t>X &gt; -0.2575</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>3875~3888</t>
-        </is>
+      <c r="B8" t="n">
+        <v>3875</v>
       </c>
       <c r="C8" s="4" t="n">
         <v>-0.2300638346132757</v>
@@ -2375,10 +2369,8 @@
           <t>X &gt; -0.2212</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>3783~3796</t>
-        </is>
+      <c r="B9" t="n">
+        <v>3783</v>
       </c>
       <c r="C9" s="4" t="n">
         <v>-0.06983452674316482</v>
@@ -2429,10 +2421,8 @@
           <t>X &gt; -0.1849</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>3669~3682</t>
-        </is>
+      <c r="B10" t="n">
+        <v>3669</v>
       </c>
       <c r="C10" s="4" t="n">
         <v>0.0323628747927458</v>
@@ -2483,10 +2473,8 @@
           <t>X &gt; -0.1485</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>3516~3528</t>
-        </is>
+      <c r="B11" t="n">
+        <v>3516</v>
       </c>
       <c r="C11" s="4" t="n">
         <v>0.2559947863659886</v>
@@ -2537,10 +2525,8 @@
           <t>X &gt; -0.1122</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>3316~3319</t>
-        </is>
+      <c r="B12" t="n">
+        <v>3316</v>
       </c>
       <c r="C12" s="4" t="n">
         <v>0.3236752682202777</v>
@@ -2591,10 +2577,8 @@
           <t>X &gt; -0.07583</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>3035~3035</t>
-        </is>
+      <c r="B13" t="n">
+        <v>3035</v>
       </c>
       <c r="C13" s="4" t="n">
         <v>0.5872865562315468</v>
@@ -2645,10 +2629,8 @@
           <t>X &gt; -0.03949</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>2746~2746</t>
-        </is>
+      <c r="B14" t="n">
+        <v>2746</v>
       </c>
       <c r="C14" s="4" t="n">
         <v>0.4198901575758924</v>
@@ -2699,10 +2681,8 @@
           <t>X &gt; -0.003153</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>2427~2427</t>
-        </is>
+      <c r="B15" t="n">
+        <v>2427</v>
       </c>
       <c r="C15" s="4" t="n">
         <v>1.235445074928052</v>
@@ -2753,10 +2733,8 @@
           <t>X &gt; 0.03319</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>2112~2112</t>
-        </is>
+      <c r="B16" t="n">
+        <v>2112</v>
       </c>
       <c r="C16" s="4" t="n">
         <v>1.389137437365783</v>
@@ -2807,10 +2785,8 @@
           <t>X &gt; 0.06953</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>1818~1818</t>
-        </is>
+      <c r="B17" t="n">
+        <v>1818</v>
       </c>
       <c r="C17" s="4" t="n">
         <v>1.631974221044153</v>
@@ -2861,10 +2837,8 @@
           <t>X &gt; 0.1059</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>1577~1577</t>
-        </is>
+      <c r="B18" t="n">
+        <v>1577</v>
       </c>
       <c r="C18" s="4" t="n">
         <v>2.294133017773532</v>
@@ -2915,10 +2889,8 @@
           <t>X &gt; 0.1422</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>1384~1384</t>
-        </is>
+      <c r="B19" t="n">
+        <v>1384</v>
       </c>
       <c r="C19" s="4" t="n">
         <v>2.347602142217774</v>
@@ -2969,10 +2941,8 @@
           <t>X &gt; 0.1785</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>1172~1172</t>
-        </is>
+      <c r="B20" t="n">
+        <v>1172</v>
       </c>
       <c r="C20" s="4" t="n">
         <v>2.455367140540872</v>
@@ -3023,10 +2993,8 @@
           <t>X &gt; 0.2149</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>1004~1004</t>
-        </is>
+      <c r="B21" t="n">
+        <v>1004</v>
       </c>
       <c r="C21" s="4" t="n">
         <v>2.785446141941414</v>
@@ -3077,10 +3045,8 @@
           <t>X &gt; 0.2512</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>840~840</t>
-        </is>
+      <c r="B22" t="n">
+        <v>840</v>
       </c>
       <c r="C22" s="4" t="n">
         <v>2.387514060742411</v>
@@ -3131,10 +3097,8 @@
           <t>X &gt; 0.2876</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>672~672</t>
-        </is>
+      <c r="B23" t="n">
+        <v>672</v>
       </c>
       <c r="C23" s="4" t="n">
         <v>3.16132358455193</v>
@@ -3185,10 +3149,8 @@
           <t>X &gt; 0.3239</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>566~566</t>
-        </is>
+      <c r="B24" t="n">
+        <v>566</v>
       </c>
       <c r="C24" s="4" t="n">
         <v>3.866985708058579</v>
@@ -3239,10 +3201,8 @@
           <t>X &gt; 0.3602</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>481~481</t>
-        </is>
+      <c r="B25" t="n">
+        <v>481</v>
       </c>
       <c r="C25" s="4" t="n">
         <v>4.471218644446992</v>
@@ -3293,10 +3253,8 @@
           <t>X &gt; 0.3966</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>398~398</t>
-        </is>
+      <c r="B26" t="n">
+        <v>398</v>
       </c>
       <c r="C26" s="4" t="n">
         <v>4.039224996372937</v>
@@ -3347,10 +3305,8 @@
           <t>X &gt; 0.4329</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>356~356</t>
-        </is>
+      <c r="B27" t="n">
+        <v>356</v>
       </c>
       <c r="C27" s="4" t="n">
         <v>4.248134713497898</v>
@@ -3401,10 +3357,8 @@
           <t>X &gt; 0.4693</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>313~313</t>
-        </is>
+      <c r="B28" t="n">
+        <v>313</v>
       </c>
       <c r="C28" s="4" t="n">
         <v>2.778127174997692</v>
@@ -3455,10 +3409,8 @@
           <t>X &gt; 0.5056</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>253~253</t>
-        </is>
+      <c r="B29" t="n">
+        <v>253</v>
       </c>
       <c r="C29" s="4" t="n">
         <v>0.8662454742564307</v>
@@ -3509,10 +3461,8 @@
           <t>X &gt; 0.5419</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>205~205</t>
-        </is>
+      <c r="B30" t="n">
+        <v>205</v>
       </c>
       <c r="C30" s="4" t="n">
         <v>1.652903143204661</v>
@@ -3563,10 +3513,8 @@
           <t>X &gt; 0.5783</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>174~174</t>
-        </is>
+      <c r="B31" t="n">
+        <v>174</v>
       </c>
       <c r="C31" s="4" t="n">
         <v>0.3801248981808314</v>
@@ -3617,10 +3565,8 @@
           <t>X &gt; 0.6146</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>138~138</t>
-        </is>
+      <c r="B32" t="n">
+        <v>138</v>
       </c>
       <c r="C32" s="4" t="n">
         <v>-1.044162957891139</v>
@@ -3671,10 +3617,8 @@
           <t>X &gt; 0.651</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>116~116</t>
-        </is>
+      <c r="B33" t="n">
+        <v>116</v>
       </c>
       <c r="C33" s="4" t="n">
         <v>0.09276857634174718</v>
@@ -3725,10 +3669,8 @@
           <t>X &gt; 0.6873</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>100~100</t>
-        </is>
+      <c r="B34" t="n">
+        <v>100</v>
       </c>
       <c r="C34" s="4" t="n">
         <v>1.506561679790025</v>
@@ -3779,10 +3721,8 @@
           <t>X &gt; 0.7236</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>82~82</t>
-        </is>
+      <c r="B35" t="n">
+        <v>82</v>
       </c>
       <c r="C35" s="4" t="n">
         <v>1.165098265155883</v>
@@ -3967,10 +3907,8 @@
           <t>X &lt; -0.3302</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>82~82</t>
-        </is>
+      <c r="B6" t="n">
+        <v>82</v>
       </c>
       <c r="C6" s="4" t="n">
         <v>8.482171435887587</v>
@@ -4021,10 +3959,8 @@
           <t>X &lt; -0.2939</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>126~126</t>
-        </is>
+      <c r="B7" t="n">
+        <v>126</v>
       </c>
       <c r="C7" s="4" t="n">
         <v>10.20497437820272</v>
@@ -4075,10 +4011,8 @@
           <t>X &lt; -0.2575</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>204~204</t>
-        </is>
+      <c r="B8" t="n">
+        <v>204</v>
       </c>
       <c r="C8" s="4" t="n">
         <v>5.83989501312336</v>
@@ -4129,10 +4063,8 @@
           <t>X &lt; -0.2212</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>296~296</t>
-        </is>
+      <c r="B9" t="n">
+        <v>296</v>
       </c>
       <c r="C9" s="4" t="n">
         <v>1.89845357168192</v>
@@ -4183,10 +4115,8 @@
           <t>X &lt; -0.1849</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>410~410</t>
-        </is>
+      <c r="B10" t="n">
+        <v>410</v>
       </c>
       <c r="C10" s="4" t="n">
         <v>0.4333909480827103</v>
@@ -4237,10 +4167,8 @@
           <t>X &lt; -0.1485</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>563~564</t>
-        </is>
+      <c r="B11" t="n">
+        <v>563</v>
       </c>
       <c r="C11" s="4" t="n">
         <v>-1.074998603897917</v>
@@ -4291,10 +4219,8 @@
           <t>X &lt; -0.1122</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>763~773</t>
-        </is>
+      <c r="B12" t="n">
+        <v>763</v>
       </c>
       <c r="C12" s="4" t="n">
         <v>-1.005728100287598</v>
@@ -4345,10 +4271,8 @@
           <t>X &lt; -0.07583</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>1044~1057</t>
-        </is>
+      <c r="B13" t="n">
+        <v>1044</v>
       </c>
       <c r="C13" s="4" t="n">
         <v>-1.405453457390671</v>
@@ -4399,10 +4323,8 @@
           <t>X &lt; -0.03949</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>1333~1346</t>
-        </is>
+      <c r="B14" t="n">
+        <v>1333</v>
       </c>
       <c r="C14" s="4" t="n">
         <v>-0.636083193909819</v>
@@ -4453,10 +4375,8 @@
           <t>X &lt; -0.003153</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>1652~1665</t>
-        </is>
+      <c r="B15" t="n">
+        <v>1652</v>
       </c>
       <c r="C15" s="4" t="n">
         <v>-1.622567449339108</v>
@@ -4507,10 +4427,8 @@
           <t>X &lt; 0.03319</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>1967~1980</t>
-        </is>
+      <c r="B16" t="n">
+        <v>1967</v>
       </c>
       <c r="C16" s="4" t="n">
         <v>-1.331822158593809</v>
@@ -4561,10 +4479,8 @@
           <t>X &lt; 0.06953</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>2261~2274</t>
-        </is>
+      <c r="B17" t="n">
+        <v>2261</v>
       </c>
       <c r="C17" s="4" t="n">
         <v>-1.174177106489665</v>
@@ -4615,10 +4531,8 @@
           <t>X &lt; 0.1059</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>2502~2515</t>
-        </is>
+      <c r="B18" t="n">
+        <v>2502</v>
       </c>
       <c r="C18" s="4" t="n">
         <v>-1.320476093569816</v>
@@ -4669,10 +4583,8 @@
           <t>X &lt; 0.1422</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>2695~2708</t>
-        </is>
+      <c r="B19" t="n">
+        <v>2695</v>
       </c>
       <c r="C19" s="4" t="n">
         <v>-1.090188689486197</v>
@@ -4723,10 +4635,8 @@
           <t>X &lt; 0.1785</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>2907~2920</t>
-        </is>
+      <c r="B20" t="n">
+        <v>2907</v>
       </c>
       <c r="C20" s="4" t="n">
         <v>-0.8838492791140808</v>
@@ -4777,10 +4687,8 @@
           <t>X &lt; 0.2149</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>3075~3088</t>
-        </is>
+      <c r="B21" t="n">
+        <v>3075</v>
       </c>
       <c r="C21" s="4" t="n">
         <v>-0.809500496375783</v>
@@ -4831,10 +4739,8 @@
           <t>X &lt; 0.2512</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>3239~3252</t>
-        </is>
+      <c r="B22" t="n">
+        <v>3239</v>
       </c>
       <c r="C22" s="4" t="n">
         <v>-0.5254186400131786</v>
@@ -4885,10 +4791,8 @@
           <t>X &lt; 0.2876</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>3407~3420</t>
-        </is>
+      <c r="B23" t="n">
+        <v>3407</v>
       </c>
       <c r="C23" s="4" t="n">
         <v>-0.5343739927245963</v>
@@ -4939,10 +4843,8 @@
           <t>X &lt; 0.3239</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>3513~3526</t>
-        </is>
+      <c r="B24" t="n">
+        <v>3513</v>
       </c>
       <c r="C24" s="4" t="n">
         <v>-0.5365466582700975</v>
@@ -4993,10 +4895,8 @@
           <t>X &lt; 0.3602</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>3598~3611</t>
-        </is>
+      <c r="B25" t="n">
+        <v>3598</v>
       </c>
       <c r="C25" s="4" t="n">
         <v>-0.5133773952584448</v>
@@ -5047,10 +4947,8 @@
           <t>X &lt; 0.3966</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>3681~3694</t>
-        </is>
+      <c r="B26" t="n">
+        <v>3681</v>
       </c>
       <c r="C26" s="4" t="n">
         <v>-0.3548351799825866</v>
@@ -5101,10 +4999,8 @@
           <t>X &lt; 0.4329</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>3723~3736</t>
-        </is>
+      <c r="B27" t="n">
+        <v>3723</v>
       </c>
       <c r="C27" s="4" t="n">
         <v>-0.3253441017945562</v>
@@ -5155,10 +5051,8 @@
           <t>X &lt; 0.4693</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>3766~3779</t>
-        </is>
+      <c r="B28" t="n">
+        <v>3766</v>
       </c>
       <c r="C28" s="4" t="n">
         <v>-0.1515489314827931</v>
@@ -5209,10 +5103,8 @@
           <t>X &lt; 0.5056</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>3826~3839</t>
-        </is>
+      <c r="B29" t="n">
+        <v>3826</v>
       </c>
       <c r="C29" s="4" t="n">
         <v>0.02023711610156198</v>
@@ -5263,10 +5155,8 @@
           <t>X &lt; 0.5419</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>3874~3887</t>
-        </is>
+      <c r="B30" t="n">
+        <v>3874</v>
       </c>
       <c r="C30" s="4" t="n">
         <v>-0.0108038977762277</v>
@@ -5317,10 +5207,8 @@
           <t>X &lt; 0.5783</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>3905~3918</t>
-        </is>
+      <c r="B31" t="n">
+        <v>3905</v>
       </c>
       <c r="C31" s="4" t="n">
         <v>0.05888429336838641</v>
@@ -5371,10 +5259,8 @@
           <t>X &lt; 0.6146</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>3941~3954</t>
-        </is>
+      <c r="B32" t="n">
+        <v>3941</v>
       </c>
       <c r="C32" s="4" t="n">
         <v>0.1115186853540138</v>
@@ -5425,10 +5311,8 @@
           <t>X &lt; 0.651</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>3963~3976</t>
-        </is>
+      <c r="B33" t="n">
+        <v>3963</v>
       </c>
       <c r="C33" s="4" t="n">
         <v>0.07195403391477839</v>
@@ -5479,10 +5363,8 @@
           <t>X &lt; 0.6873</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>3979~3992</t>
-        </is>
+      <c r="B34" t="n">
+        <v>3979</v>
       </c>
       <c r="C34" s="4" t="n">
         <v>0.03662180003050963</v>
@@ -5533,10 +5415,8 @@
           <t>X &lt; 0.7236</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>3997~4010</t>
-        </is>
+      <c r="B35" t="n">
+        <v>3997</v>
       </c>
       <c r="C35" s="4" t="n">
         <v>0.05020257754563318</v>

--- a/workspaces/btc_daily_14days/ma/ma_ratio_100.xlsx
+++ b/workspaces/btc_daily_14days/ma/ma_ratio_100.xlsx
@@ -479,7 +479,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Measures the winrate at horizon h days, given that MA Ratio-100 is approximately at value x, minus the unconditional baseline winrate.</t>
+          <t>Measures the winrate at horizon h, given that MA Ratio-100 is approximately at value x, minus the unconditional baseline winrate.</t>
         </is>
       </c>
     </row>
@@ -575,46 +575,46 @@
         <v>44</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>13.37135203736668</v>
+        <v>13.38384268776593</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-6.358668850415874</v>
+        <v>-6.345804616093709</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>6.844338201695017</v>
+        <v>6.857312608250965</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>11.51024521299609</v>
+        <v>11.52319753008707</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>15.51103325779674</v>
+        <v>15.52412192815257</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>6.739281874257507</v>
+        <v>6.752300741656377</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>11.19375146684552</v>
+        <v>11.20679867955565</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>1.652953511781874</v>
+        <v>1.666114378723265</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>8.402242341617928</v>
+        <v>8.41542632685816</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>7.554981169368695</v>
+        <v>7.568374112956121</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>5.08129930790578</v>
+        <v>5.094746951385254</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>14.20333770102872</v>
+        <v>14.21678469882024</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>4.698190314445505</v>
+        <v>4.711743070446815</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>7.221811218940068</v>
+        <v>7.211381583240879</v>
       </c>
     </row>
     <row r="7">
@@ -627,46 +627,46 @@
         <v>78</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-1.208170396290733</v>
+        <v>-1.195692956790559</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-4.09235941764279</v>
+        <v>-4.07949496273104</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-8.3230076553929</v>
+        <v>-8.310045195526861</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-8.195067025260734</v>
+        <v>-8.1821283996753</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-10.01355094716027</v>
+        <v>-10.00047794391597</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-9.71901403119741</v>
+        <v>-9.706004555431477</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-13.64545723204775</v>
+        <v>-13.63242201116286</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-15.39532637138227</v>
+        <v>-15.38217291545289</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-10.33847849824755</v>
+        <v>-10.32530112158189</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-11.19048092114885</v>
+        <v>-11.17709328506895</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-12.67896746349899</v>
+        <v>-12.6655236362932</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-17.77339149910136</v>
+        <v>-17.75994886523129</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-16.91631527719988</v>
+        <v>-16.90276405394299</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-17.95301395588614</v>
+        <v>-17.9634435915837</v>
       </c>
     </row>
     <row r="8">
@@ -679,46 +679,46 @@
         <v>92</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-6.818623309316052</v>
+        <v>-6.806152993593273</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-3.008273133222616</v>
+        <v>-2.995409953349963</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-2.319363057430444</v>
+        <v>-2.306398271313086</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-3.274034081018286</v>
+        <v>-3.261094087599304</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-4.896499392952492</v>
+        <v>-4.883425143362786</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-4.600742957639355</v>
+        <v>-4.587732360417178</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-9.026382009214402</v>
+        <v>-9.013346212760055</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-9.495039425856902</v>
+        <v>-9.481885016589288</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-11.72957843478179</v>
+        <v>-11.71640265897564</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-13.66784089257041</v>
+        <v>-13.65445486792552</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-8.445545786846381</v>
+        <v>-8.432101792652468</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-12.75891170257652</v>
+        <v>-12.74546890988811</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-8.835757761227569</v>
+        <v>-8.822206242128054</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-7.501508939163735</v>
+        <v>-7.511938574862377</v>
       </c>
     </row>
     <row r="9">
@@ -731,46 +731,46 @@
         <v>114</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-3.358977213017077</v>
+        <v>-3.346506821168667</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-7.58847213878402</v>
+        <v>-7.575615785410676</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-7.110121095313531</v>
+        <v>-7.097162681672117</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-4.357552503402211</v>
+        <v>-4.344615635741953</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-2.270713009121685</v>
+        <v>-2.257639231868666</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-3.724905861916973</v>
+        <v>-3.711896705076157</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-3.81037205571549</v>
+        <v>-3.797335515503853</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-2.526171113844534</v>
+        <v>-2.513015328866274</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>1.792158172184145</v>
+        <v>1.805337435330252</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-0.8091917141646832</v>
+        <v>-0.7958031666174179</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-1.890647435118325</v>
+        <v>-1.877202831095843</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-1.856766094991706</v>
+        <v>-1.84332232129767</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-1.400576929376911</v>
+        <v>-1.387025149450594</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-1.151394522687752</v>
+        <v>-1.161824158385905</v>
       </c>
     </row>
     <row r="10">
@@ -780,49 +780,49 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-5.106786151949301</v>
+        <v>-5.059498495507881</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-6.07495302170269</v>
+        <v>-6.018285663035627</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-3.865545831098245</v>
+        <v>-3.824847932165433</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-2.432014239937608</v>
+        <v>-2.401173939562504</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-0.3647691465163945</v>
+        <v>-0.3482152622740529</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-0.7190969187767493</v>
+        <v>-0.6991947021902192</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-2.762422408738125</v>
+        <v>-2.728015054557851</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-3.233357270369709</v>
+        <v>-3.195016549980465</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-3.295201287369927</v>
+        <v>-3.257098739075282</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-2.84532933422873</v>
+        <v>-2.809818779266472</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-1.092244952838954</v>
+        <v>-1.068916744488185</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>0.2474233899768308</v>
+        <v>0.2631185930864888</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-0.1760544837931519</v>
+        <v>-0.1569856379552022</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>2.408976994340108</v>
+        <v>2.665927037786339</v>
       </c>
     </row>
     <row r="11">
@@ -835,358 +835,358 @@
         <v>200</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-0.866147602778149</v>
+        <v>-1.116400896557721</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>2.702054596937231</v>
+        <v>2.442008839256516</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>4.075076075693801</v>
+        <v>3.814407369423897</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>1.488469202304323</v>
+        <v>1.228748763476453</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>3.711761923244858</v>
+        <v>3.4501785937777</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>1.289473238831334</v>
+        <v>1.028374069510448</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-2.520945800487674</v>
+        <v>-2.78345243033975</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-2.497748238691834</v>
+        <v>-2.483397041329567</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>1.439700272498136</v>
+        <v>1.452856801429078</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>2.576819911421516</v>
+        <v>2.589853964677467</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>4.154514133688352</v>
+        <v>3.884671365895308</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>5.471789789307785</v>
+        <v>5.201212570089062</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>3.835726250299111</v>
+        <v>3.562674392186651</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>1.585447582575391</v>
+        <v>1.575017946877239</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X ≈ -0.09401</t>
+          <t>X ≈ -0.09402</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>281</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-2.523514265993981</v>
+        <v>-2.510991976318358</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-3.087093960625424</v>
+        <v>-3.074184151049373</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-3.482284335091364</v>
+        <v>-3.469277203673762</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-2.283772208382011</v>
+        <v>-2.270793065983547</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-0.3336635635620127</v>
+        <v>-0.3205527591870734</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-0.03654329371578058</v>
+        <v>-0.02350039742141519</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>0.5849984074749557</v>
+        <v>0.5980646617754317</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>2.446034185483427</v>
+        <v>2.260115645197168</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>0.8059673389771902</v>
+        <v>0.6210187064219213</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>0.5099809214546767</v>
+        <v>0.322329698612819</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>0.6610994832580985</v>
+        <v>0.6745567769683163</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>1.051354526724445</v>
+        <v>1.064806815444555</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-0.08064385646245853</v>
+        <v>-0.06708781011085563</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>0.1690774758139142</v>
+        <v>0.1586478401157621</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X ≈ -0.05766</t>
+          <t>X ≈ -0.05768</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>289</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>2.177841956606713</v>
+        <v>2.190364246282336</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-0.1257731788490588</v>
+        <v>-0.1128633692730077</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-2.250745691673856</v>
+        <v>-2.237738560256254</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-2.120492559066513</v>
+        <v>-2.107513416668048</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-2.312893012892935</v>
+        <v>-2.299782208517996</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-1.323409552686002</v>
+        <v>-1.310366656391636</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-0.02406022497542182</v>
+        <v>-0.01099397067494579</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-2.221347429985371</v>
+        <v>-2.208166420690134</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-4.358471883641649</v>
+        <v>-4.345273144686885</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-5.208597068669647</v>
+        <v>-5.195191941016816</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-4.72130887049596</v>
+        <v>-4.707851576785743</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-6.071008758133225</v>
+        <v>-6.057556469413115</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-6.491263369078048</v>
+        <v>-6.477707322726445</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-7.625625081784541</v>
+        <v>-7.636054717482693</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X ≈ -0.02132</t>
+          <t>X ≈ -0.02134</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>319</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-5.784974370366641</v>
+        <v>-5.772452080691018</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-2.694353625964133</v>
+        <v>-2.681443816388082</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-2.775742708736338</v>
+        <v>-2.762735577318736</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-3.272448823777744</v>
+        <v>-3.259469681379279</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-6.945666277094425</v>
+        <v>-6.932555472719486</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-7.588663210852047</v>
+        <v>-7.575620314557682</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-8.613835799597823</v>
+        <v>-8.600769545297346</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-7.200141455432615</v>
+        <v>-7.186960446137377</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-6.320702470141562</v>
+        <v>-6.307503731186799</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-8.111266526642702</v>
+        <v>-8.09786139898987</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-8.94297909860925</v>
+        <v>-8.929521804899032</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-8.908595941263755</v>
+        <v>-8.895143652543645</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-8.074932056910924</v>
+        <v>-8.061376010559322</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-5.630853357863472</v>
+        <v>-5.641282993561624</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X ≈ 0.01502</t>
+          <t>X ≈ 0.01499</t>
         </is>
       </c>
       <c r="B15" t="n">
         <v>315</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>0.2049743782026496</v>
+        <v>0.2174966678782724</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-1.406599234761529</v>
+        <v>-1.393689425185478</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>0.4207542808641023</v>
+        <v>0.4337614122817044</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>0.8684677309319184</v>
+        <v>0.8814468733303826</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>1.599887785701014</v>
+        <v>1.612998590075954</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>1.262409088496042</v>
+        <v>1.275451984790408</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>2.130056323604713</v>
+        <v>2.143122577905189</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-0.5593492973988674</v>
+        <v>-0.5461682881036296</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-1.255269818501802</v>
+        <v>-1.242071079547038</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-0.8355537336887409</v>
+        <v>-0.8221486060359098</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-1.992688010387134</v>
+        <v>-1.979230716676916</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-2.275765170502019</v>
+        <v>-2.262312881781909</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-1.108718194145332</v>
+        <v>-1.095162147793729</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-1.17645717932929</v>
+        <v>-1.186886815027442</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X ≈ 0.05136</t>
+          <t>X ≈ 0.05133</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-0.1124859392575885</v>
+        <v>-0.2624859964046564</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-4.10501193317431</v>
+        <v>-4.262750587761929</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-3.479472476505514</v>
+        <v>-3.633631187534029</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-5.049899616006783</v>
+        <v>-5.209890685583972</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-3.547504504548336</v>
+        <v>-3.359101740386073</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-4.270470730098062</v>
+        <v>-4.085618495734082</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-2.994660229683262</v>
+        <v>-2.805141141689589</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-3.12170757404315</v>
+        <v>-2.930912857148755</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-3.862979569068912</v>
+        <v>-3.674488870326826</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-2.332152373144304</v>
+        <v>-2.135329168362929</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-2.877041751883809</v>
+        <v>-2.681327254951007</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-3.52293070338191</v>
+        <v>-3.329542959250816</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-4.283321368748503</v>
+        <v>-4.090990740891947</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-5.734280308581063</v>
+        <v>-5.571739732303719</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X ≈ 0.08771</t>
+          <t>X ≈ 0.08765</t>
         </is>
       </c>
       <c r="B17" t="n">
         <v>241</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-2.700907199877982</v>
+        <v>-2.688384910202402</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>1.496647817863206</v>
+        <v>1.509557627439122</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>0.6868413519304681</v>
+        <v>1.114786242683984</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-5.821909664839765</v>
+        <v>-5.393992763105153</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-2.210953286550946</v>
+        <v>-2.197842482176007</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>0.5761152071814166</v>
+        <v>0.1742203441397265</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>0.9063192492452785</v>
+        <v>0.5044477442096564</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>1.683949128472072</v>
+        <v>1.282192378431169</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>3.282700279634078</v>
+        <v>2.880961259252842</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>3.262450613278403</v>
+        <v>2.860917981595087</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>2.227821770288713</v>
+        <v>1.826341304662876</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>4.751831483650747</v>
+        <v>4.350346013034567</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>4.331576872705753</v>
+        <v>3.930195159721251</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>4.996235964318039</v>
+        <v>4.570868569283938</v>
       </c>
     </row>
     <row r="18">
@@ -1199,46 +1199,46 @@
         <v>193</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>1.910706757510169</v>
+        <v>1.923229047185792</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>0.2991331445459764</v>
+        <v>0.830177669147929</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>3.531207443130668</v>
+        <v>3.544214574548398</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>3.661460575738225</v>
+        <v>3.67443971813676</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-4.648981364722538</v>
+        <v>-4.635870560347598</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-4.869674142032785</v>
+        <v>-4.856631245738356</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-4.436273144279212</v>
+        <v>-4.4232068899788</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-2.312782967931071</v>
+        <v>-2.29960195863589</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-1.337513424061555</v>
+        <v>-1.324314685106913</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-1.669503894063631</v>
+        <v>-1.656098766410864</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-0.3198530733034346</v>
+        <v>-0.3063957795933945</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>0.7507995140938135</v>
+        <v>0.7642518028137957</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>0.8486796181747636</v>
+        <v>1.380370379552261</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>0.06213152039923386</v>
+        <v>0.5698365997269192</v>
       </c>
     </row>
     <row r="19">
@@ -1248,101 +1248,101 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>1.751844698657997</v>
+        <v>1.97917786617937</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>3.913855991354076</v>
+        <v>3.654376749641202</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-0.2545976209028922</v>
+        <v>-0.4962631797147239</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>2.234146077742395</v>
+        <v>1.981379804249286</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>4.52591354191545</v>
+        <v>4.259991659604232</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>4.351657366423566</v>
+        <v>4.557365689239319</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>8.983904781226762</v>
+        <v>9.167491010724383</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>11.34691006169054</v>
+        <v>11.51732377538828</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>13.64440074154597</v>
+        <v>13.80375945924111</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>13.73767178293313</v>
+        <v>13.89280779906147</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>13.06122034540796</v>
+        <v>13.21862307272622</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>12.1522072763383</v>
+        <v>12.31403408893132</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>12.20365077860099</v>
+        <v>11.89388323561785</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>11.98167399766974</v>
+        <v>11.65013531776928</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X ≈ 0.1967</t>
+          <t>X ≈ 0.1966</t>
         </is>
       </c>
       <c r="B20" t="n">
         <v>168</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>0.4827521559804993</v>
+        <v>0.495274445656122</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>3.633083304921001</v>
+        <v>3.645993114497053</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>2.642976503086317</v>
+        <v>2.655983634503919</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>0.3922772547413658</v>
+        <v>0.40525639713983</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>2.234808420621647</v>
+        <v>2.247919224996586</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>1.341774167861125</v>
+        <v>1.35481706415549</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>0.06656426011265637</v>
+        <v>0.0796305144131324</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>0.7898570518072745</v>
+        <v>0.8030380611025123</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-5.818761881994078</v>
+        <v>-5.805563143039315</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-1.906982305117175</v>
+        <v>-1.893577177464344</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-4.492688010387127</v>
+        <v>-4.479230716676909</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-0.8868762816131976</v>
+        <v>-0.8734239928930876</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-0.1166547020818456</v>
+        <v>-0.1030986557302427</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-1.057409560281812</v>
+        <v>-1.067839195979964</v>
       </c>
     </row>
     <row r="21">
@@ -1355,150 +1355,150 @@
         <v>164</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>4.823634850521628</v>
+        <v>4.836157140197251</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>6.87059782292333</v>
+        <v>6.883507632499381</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>4.646460823643807</v>
+        <v>4.659467955061409</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>9.045006639178105</v>
+        <v>9.057985781576569</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>9.116341521666953</v>
+        <v>9.129452326041893</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>8.194271264260621</v>
+        <v>8.207314160554986</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>8.109537546988413</v>
+        <v>8.122603801288889</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>9.471622440889909</v>
+        <v>9.484803450185147</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>8.191110359585586</v>
+        <v>8.20430909854035</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>7.950741272118606</v>
+        <v>7.964146399771437</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>5.306963557557118</v>
+        <v>5.320420851267336</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>5.341346714902613</v>
+        <v>5.354799003622723</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>3.09182381127475</v>
+        <v>3.105379857626353</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>6.39032563135595</v>
+        <v>6.379895995657797</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X ≈ 0.2694</t>
+          <t>X ≈ 0.2693</t>
         </is>
       </c>
       <c r="B22" t="n">
         <v>168</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-0.707724034495655</v>
+        <v>-0.6952017448200323</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>1.847369019206752</v>
+        <v>1.860278828782803</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>2.642976503086317</v>
+        <v>2.655983634503919</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>1.582753445217662</v>
+        <v>1.595732587616126</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>1.639570325383552</v>
+        <v>1.652681129758491</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>3.722726548813505</v>
+        <v>3.73576944510787</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>4.82846902201738</v>
+        <v>4.841535276317856</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>1.385095147045405</v>
+        <v>1.398276156340643</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>1.919333356101262</v>
+        <v>1.932532095056025</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>0.4739700758352043</v>
+        <v>0.4873752034880354</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-0.3260213437204627</v>
+        <v>-0.3125640500102449</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>0.898838004101151</v>
+        <v>0.9122902928212611</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>3.454773869346695</v>
+        <v>3.468329915698298</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>1.323542820670632</v>
+        <v>1.31311318497248</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X ≈ 0.3058</t>
+          <t>X ≈ 0.3057</t>
         </is>
       </c>
       <c r="B23" t="n">
         <v>106</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-0.6066458673797896</v>
+        <v>-0.5941235777041669</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-3.161615706759193</v>
+        <v>-3.148705897183142</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>1.160496718719799</v>
+        <v>1.173503850137401</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-2.482835054333137</v>
+        <v>-2.469855911934673</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-3.021256269405306</v>
+        <v>-3.008145465030367</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>2.936563026800975</v>
+        <v>2.949605923095341</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>0.965036856698454</v>
+        <v>0.97810311099893</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-2.332335221328329</v>
+        <v>-2.319154212033091</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>2.323646024564844</v>
+        <v>2.336844763519608</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-0.4132716132932757</v>
+        <v>-0.3998664856404446</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>4.09895619446462</v>
+        <v>4.112413488174838</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>2.246546898979858</v>
+        <v>2.259999187699968</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>4.656480967280238</v>
+        <v>4.670037013631841</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>9.623183431632</v>
+        <v>9.612753795933848</v>
       </c>
     </row>
     <row r="24">
@@ -1511,46 +1511,46 @@
         <v>85</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>0.4477381503782638</v>
+        <v>0.4602604400538866</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>4.718517478590478</v>
+        <v>4.731427288166529</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-3.911645345653312</v>
+        <v>-3.89863821423571</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>4.453901904601388</v>
+        <v>4.466881046999852</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>1.562539513058695</v>
+        <v>1.575650317433634</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>1.859981450774285</v>
+        <v>1.87302434706865</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-2.930634619439161</v>
+        <v>-2.917568365138685</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>3.661005511191163</v>
+        <v>3.674186520486401</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>1.247064448538275</v>
+        <v>1.260263187493038</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>7.455762792922108</v>
+        <v>7.46916792057494</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>4.898068292133878</v>
+        <v>4.911525585844096</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>10.81480439065577</v>
+        <v>10.82825667937588</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>6.865138015004923</v>
+        <v>6.878694061356526</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>7.114859347281275</v>
+        <v>7.104429711583123</v>
       </c>
     </row>
     <row r="25">
@@ -1563,98 +1563,98 @@
         <v>83</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>6.54270625810328</v>
+        <v>6.555228547778903</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>10.95522903068119</v>
+        <v>10.96813884025724</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>10.56036032408467</v>
+        <v>10.57336745550227</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>9.485794179583657</v>
+        <v>9.498773321982121</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>8.947372964511423</v>
+        <v>8.960483768886363</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>10.44963417933559</v>
+        <v>10.46267707562995</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>10.36490046206328</v>
+        <v>10.37796671636376</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>9.897717063281739</v>
+        <v>9.910898072576977</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>7.427078622882576</v>
+        <v>7.440277361837339</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>6.576953437854648</v>
+        <v>6.590358565507479</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>9.986657944862444</v>
+        <v>10.00011523857266</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>7.611402547990991</v>
+        <v>7.624854836711101</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>8.395967214154602</v>
+        <v>8.409523260506205</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>8.64568854643079</v>
+        <v>8.635258910732638</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X ≈ 0.4148</t>
+          <t>X ≈ 0.4147</t>
         </is>
       </c>
       <c r="B26" t="n">
         <v>42</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>2.268466441694713</v>
+        <v>2.280988731370336</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>0.6568928287304558</v>
+        <v>0.669802638306507</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>0.2620241221339441</v>
+        <v>0.2750312535515462</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>5.154182016646203</v>
+        <v>5.167161159044667</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>6.996713182526413</v>
+        <v>7.009823986901353</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>9.675107501194461</v>
+        <v>9.688150397488826</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>16.73323092677939</v>
+        <v>16.74629718107987</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>16.26604752799782</v>
+        <v>16.27922853729306</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>16.20504764181552</v>
+        <v>16.21824638077028</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>10.59301769488282</v>
+        <v>10.60642282253565</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>12.76921675151756</v>
+        <v>12.78267404522778</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>10.42264752791067</v>
+        <v>10.43609981663078</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>14.76429767887061</v>
+        <v>14.77785372522222</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>10.25211424924213</v>
+        <v>10.24168461354397</v>
       </c>
     </row>
     <row r="27">
@@ -1667,150 +1667,150 @@
         <v>43</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>14.94842214490637</v>
+        <v>14.960944434582</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>13.33684853194212</v>
+        <v>13.34975834151817</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>12.94197982534546</v>
+        <v>12.95498695676306</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>15.39781435330173</v>
+        <v>15.4107934957002</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>17.18497453357845</v>
+        <v>17.19808533795339</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>12.83125368059645</v>
+        <v>12.84429657689081</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>8.095357172626493</v>
+        <v>8.108423426926969</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>5.302592378496151</v>
+        <v>5.315773387791388</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>7.56717388766269</v>
+        <v>7.580372626617454</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>9.042630097983604</v>
+        <v>9.056035225636435</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>18.14020235506143</v>
+        <v>18.15365964877165</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>15.84900411705803</v>
+        <v>15.86245640577814</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>13.10316811076417</v>
+        <v>13.11672415711577</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>11.02730804769168</v>
+        <v>11.01687841199352</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X ≈ 0.4875</t>
+          <t>X ≈ 0.4873</t>
         </is>
       </c>
       <c r="B28" t="n">
         <v>60</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>10.83989501312335</v>
+        <v>10.85241730279898</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>5.894988066825768</v>
+        <v>5.907897876401819</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-1.166547306437486</v>
+        <v>-1.153540175019884</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>3.963705826170013</v>
+        <v>3.976684968568478</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>3.425284611097887</v>
+        <v>3.438395415472826</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>0.3893932154802187</v>
+        <v>0.402436111774584</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-3.028673835125439</v>
+        <v>-3.015607580824962</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>3.170809432759768</v>
+        <v>3.183990442055006</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-0.223523786755905</v>
+        <v>-0.2103250478011418</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>2.259684361549496</v>
+        <v>2.273089489202327</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>3.721597703898532</v>
+        <v>3.735054997608749</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>3.755980861243962</v>
+        <v>3.769433149964073</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>8.335726250299111</v>
+        <v>8.349282296650713</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>6.918780915908727</v>
+        <v>6.908351280210574</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X ≈ 0.5238</t>
+          <t>X ≈ 0.5237</t>
         </is>
       </c>
       <c r="B29" t="n">
         <v>48</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-2.493438320209975</v>
+        <v>-2.480916030534353</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-4.105011933174232</v>
+        <v>-4.092102123598181</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>3.833452693562478</v>
+        <v>3.84645982498008</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>10.21370582617003</v>
+        <v>10.2266849685685</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>5.508617944431116</v>
+        <v>5.521728748806055</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>9.972726548813441</v>
+        <v>9.985769445107806</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>9.887992831541233</v>
+        <v>9.901059085841709</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>3.17080943275964</v>
+        <v>3.183990442054878</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>9.359809546577388</v>
+        <v>9.373008285532151</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>12.67635102821616</v>
+        <v>12.68975615586899</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>8.304931037231981</v>
+        <v>8.318388330942199</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>6.255980861244012</v>
+        <v>6.269433149964122</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>10.00239291696577</v>
+        <v>10.01594896331737</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>6.085447582575398</v>
+        <v>6.075017946877246</v>
       </c>
     </row>
     <row r="30">
@@ -1823,254 +1823,254 @@
         <v>31</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>8.796884260435185</v>
+        <v>8.809406550110808</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>16.86273000230968</v>
+        <v>16.87563981188573</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>19.69366774732605</v>
+        <v>19.70667487874365</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>13.3723079767077</v>
+        <v>13.38528711910616</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>16.05969321324838</v>
+        <v>16.07280401762332</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>19.58294160257694</v>
+        <v>19.5959844988713</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>25.94982078853047</v>
+        <v>25.96288704283094</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>31.93425029297482</v>
+        <v>31.94743130227005</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>25.42163750356672</v>
+        <v>25.43483624252148</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>8.442480060474225</v>
+        <v>8.455885188127056</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>8.237726736156603</v>
+        <v>8.25118402986682</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>8.272109893502076</v>
+        <v>8.285562182222186</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>7.851855282557175</v>
+        <v>7.865411328908777</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-1.57584274000525</v>
+        <v>-1.586272375703402</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X ≈ 0.5965</t>
+          <t>X ≈ 0.5964</t>
         </is>
       </c>
       <c r="B31" t="n">
         <v>36</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>5.839895013123396</v>
+        <v>5.852417302799019</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>4.228321400159061</v>
+        <v>4.241231209735112</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-7.277658417548679</v>
+        <v>-7.264651286131077</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-7.147405284941101</v>
+        <v>-7.134426142542637</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-2.130270944457756</v>
+        <v>-2.117160140082817</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>0.9449487710357261</v>
+        <v>0.9579916673300914</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>0.8602150537634472</v>
+        <v>0.8732813080639232</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>0.3930316549819466</v>
+        <v>0.4062126642771844</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-2.445746008978134</v>
+        <v>-2.43254727002337</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>-6.07364897178384</v>
+        <v>-6.060243844131008</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>-6.278402296101376</v>
+        <v>-6.264945002391158</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>-9.021796916533766</v>
+        <v>-9.008344627813656</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>-1.108718194145332</v>
+        <v>-1.095162147793729</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>4.696558693686512</v>
+        <v>4.68612905798836</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>X ≈ 0.6328</t>
+          <t>X ≈ 0.6327</t>
         </is>
       </c>
       <c r="B32" t="n">
         <v>22</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>-7.038892865664586</v>
+        <v>-7.026370575988963</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>-13.19592102408332</v>
+        <v>-13.18301121450727</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-4.499880639770758</v>
+        <v>-4.486873508353156</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-4.369627507163258</v>
+        <v>-4.356648364764794</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-13.99895781314452</v>
+        <v>-13.98584700876958</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-9.156061329974378</v>
+        <v>-9.143018433680012</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>-13.7862495927012</v>
+        <v>-13.77318333840072</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>-23.34434208239179</v>
+        <v>-23.33116107309656</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-9.768978332210459</v>
+        <v>-9.755779593255696</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>-10.61910351723839</v>
+        <v>-10.60569838958556</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>-6.278402296101419</v>
+        <v>-6.264945002391201</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>2.846889952153106</v>
+        <v>2.860342240873216</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>2.426635341208204</v>
+        <v>2.440191387559807</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>-1.869097871970062</v>
+        <v>-1.879527507668215</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X ≈ 0.6692</t>
+          <t>X ≈ 0.6691</t>
         </is>
       </c>
       <c r="B33" t="n">
         <v>16</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>-8.743438320209975</v>
+        <v>-8.730916030534353</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>-10.35501193317423</v>
+        <v>-10.34210212359818</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>-4.499880639770865</v>
+        <v>-4.486873508353263</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>1.880372492836543</v>
+        <v>1.893351635235007</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>13.84195127776451</v>
+        <v>13.85506208213945</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-4.610606784519831</v>
+        <v>-4.597563888225466</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>-10.94534050179211</v>
+        <v>-10.93227424749163</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-5.162523900573611</v>
+        <v>-5.149342891278373</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>1.026476213244088</v>
+        <v>1.039674952198851</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>12.67635102821616</v>
+        <v>12.68975615586899</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>-0.02840229610141876</v>
+        <v>-0.014945002391201</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>6.255980861244012</v>
+        <v>6.269433149964122</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>5.835726250299111</v>
+        <v>5.849282296650713</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>6.085447582575398</v>
+        <v>6.075017946877246</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X ≈ 0.7055</t>
+          <t>X ≈ 0.7054</t>
         </is>
       </c>
       <c r="B34" t="n">
         <v>18</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>3.062117235345582</v>
+        <v>3.074639525021205</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>7.006099177936882</v>
+        <v>7.019008987512933</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>1.05567491578477</v>
+        <v>1.068682047202373</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-4.36962750716328</v>
+        <v>-4.356648364764816</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-16.0191598333466</v>
+        <v>-16.00604902897166</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-10.16616234007539</v>
+        <v>-10.15311944378102</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>11.97132616487452</v>
+        <v>11.98439241917499</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>0.3930316549819466</v>
+        <v>0.4062126642771844</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>5.88758732435516</v>
+        <v>5.900786063309923</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>10.59301769488279</v>
+        <v>10.60642282253562</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>15.9438199261208</v>
+        <v>15.95727721983101</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>4.867091972355084</v>
+        <v>4.880544261075194</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>4.446837361410225</v>
+        <v>4.460393407761828</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>10.25211424924206</v>
+        <v>10.2416846135439</v>
       </c>
     </row>
   </sheetData>
@@ -2121,7 +2121,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Measures the winrate at horizon h days, given that MA Ratio-100 is above threshold x, minus the unconditional baseline winrate.</t>
+          <t>Measures the winrate at horizon h, given that MA Ratio-100 is above threshold x, minus the unconditional baseline winrate.</t>
         </is>
       </c>
     </row>
@@ -2214,49 +2214,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3997</v>
+        <v>3998</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-0.09942335761645893</v>
+        <v>-0.0999636495819658</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-0.07657591421688181</v>
+        <v>-0.07713953008196484</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-0.1336131747009617</v>
+        <v>-0.1341670977770164</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-0.03970487177524973</v>
+        <v>-0.04028109929580381</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-0.06531282607971889</v>
+        <v>-0.06588875389748949</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-0.05380278951358974</v>
+        <v>-0.05437866605871733</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-0.09993590638751471</v>
+        <v>-0.1005014634716588</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-0.1287991941034647</v>
+        <v>-0.1293628712983548</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>0.02385252508816649</v>
+        <v>0.02324977108468573</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-0.08764547265862177</v>
+        <v>-0.08822985112750814</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-0.1034022961014216</v>
+        <v>-0.1039852423312198</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-0.004959373814756418</v>
+        <v>-0.005566850035876314</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>0.06409043239015233</v>
+        <v>0.06346084128687579</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>0.07781685953312234</v>
+        <v>0.07826957269015367</v>
       </c>
     </row>
     <row r="7">
@@ -2266,49 +2266,49 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3953</v>
+        <v>3954</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-0.2493636858176416</v>
+        <v>-0.2500110645651006</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-0.006651277436525049</v>
+        <v>-0.007382002569443102</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-0.2112832633833435</v>
+        <v>-0.2119680859068112</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-0.1682649030755101</v>
+        <v>-0.1689591619394264</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-0.238689812593897</v>
+        <v>-0.2393739511686519</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-0.1294151662416212</v>
+        <v>-0.1301232017035048</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-0.2256435320951411</v>
+        <v>-0.2263287791755531</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-0.1486315035036441</v>
+        <v>-0.1493428912783656</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-0.06940554521978015</v>
+        <v>-0.07013813191330343</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-0.1727139199769212</v>
+        <v>-0.1734323231608172</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-0.1611121039881738</v>
+        <v>-0.1618365869249345</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-0.1631088985537161</v>
+        <v>-0.1638327752128248</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>0.01250925485146581</v>
+        <v>0.01173488830684732</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-0.001701418183522208</v>
+        <v>-0.001107495712538764</v>
       </c>
     </row>
     <row r="8">
@@ -2318,49 +2318,49 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3875</v>
+        <v>3876</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-0.2300638346132757</v>
+        <v>-0.2309803144119584</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>0.07559007351472502</v>
+        <v>0.07456454306848315</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-0.04800210142805383</v>
+        <v>-0.04900368586801562</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-0.006693144228954395</v>
+        <v>-0.007703434245044605</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-0.0419313174981113</v>
+        <v>-0.04294306586569263</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>0.06361417865296914</v>
+        <v>0.0625802930309689</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>0.04448433076842662</v>
+        <v>0.04345328276846772</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>0.1582697093207486</v>
+        <v>0.1572001277839661</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>0.1373009555121314</v>
+        <v>0.1362351171048033</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>0.04906306740151223</v>
+        <v>0.04800357854940529</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>0.09086021034520542</v>
+        <v>0.08978559827907873</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>0.1913690479863419</v>
+        <v>0.1902686321714455</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>0.3532701099482338</v>
+        <v>0.3521195419434591</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>0.3596411309624941</v>
+        <v>0.3603636641115031</v>
       </c>
     </row>
     <row r="9">
@@ -2370,49 +2370,49 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3783</v>
+        <v>3784</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-0.06983452674316482</v>
+        <v>-0.07111882221199295</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>0.1505875398165486</v>
+        <v>0.14920451496873</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>0.007235859965604163</v>
+        <v>0.005880114835186134</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>0.07276637630623384</v>
+        <v>0.07139591567793957</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>0.07612849295438906</v>
+        <v>0.07474307343920827</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>0.1770481877829937</v>
+        <v>0.1756428628293847</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>0.2650816617962874</v>
+        <v>0.263650310672439</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>0.3930316549819466</v>
+        <v>0.3915542063469601</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>0.4258954318290904</v>
+        <v>0.4244070714915367</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>0.3826488893199382</v>
+        <v>0.3811500312649727</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>0.2984598275118984</v>
+        <v>0.296977363597712</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>0.5063111122347692</v>
+        <v>0.5047738789657075</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>0.576741049453446</v>
+        <v>0.5751739743257502</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>0.5508189809364836</v>
+        <v>0.5517621329237556</v>
       </c>
     </row>
     <row r="10">
@@ -2422,49 +2422,49 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3669</v>
+        <v>3670</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>0.0323628747927458</v>
+        <v>0.03062347530327969</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>0.391048919854839</v>
+        <v>0.3891580610840535</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>0.2283802297943964</v>
+        <v>0.2265195913479516</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>0.2104214191753542</v>
+        <v>0.2085690265394859</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>0.1490475257253507</v>
+        <v>0.1471930960019066</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>0.2982863348709799</v>
+        <v>0.2964002227043849</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>0.3917106407541411</v>
+        <v>0.3897953744828087</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>0.4837346028277452</v>
+        <v>0.4817778921819169</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>0.3834440956610692</v>
+        <v>0.3815116868927291</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>0.4196807314560189</v>
+        <v>0.4177093404089973</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>0.3664778781905156</v>
+        <v>0.3645132061576675</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>0.5797346068174249</v>
+        <v>0.5777120170665242</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>0.6381785663754016</v>
+        <v>0.6361251187700248</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>0.6037086891439429</v>
+        <v>0.6049906989208438</v>
       </c>
     </row>
     <row r="11">
@@ -2477,46 +2477,46 @@
         <v>3516</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>0.2559947863659886</v>
+        <v>0.2535696594628192</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>0.6724193115096426</v>
+        <v>0.6698026383065852</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>0.4065288894407502</v>
+        <v>0.4039685670649789</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>0.3254079538295827</v>
+        <v>0.3228751746565806</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>0.1714064423502109</v>
+        <v>0.1688918693734891</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>0.3425581317447239</v>
+        <v>0.3400070538857705</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>0.5289638707235085</v>
+        <v>0.5263547618753819</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>0.6454851877535717</v>
+        <v>0.642820652162861</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>0.5435216677895411</v>
+        <v>0.5408819956524198</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>0.5617588145190879</v>
+        <v>0.5590743376871714</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>0.4299547249332676</v>
+        <v>0.4272971118458031</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>0.5941952485058906</v>
+        <v>0.5914911374570124</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>0.6736102093434795</v>
+        <v>0.67086318945708</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>0.5251517919041788</v>
+        <v>0.5147221562060267</v>
       </c>
     </row>
     <row r="12">
@@ -2529,358 +2529,358 @@
         <v>3316</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>0.3236752682202777</v>
+        <v>0.3361975578959004</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>0.5500046380821644</v>
+        <v>0.5629144476582155</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>0.1852654885810949</v>
+        <v>0.1982726199986971</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>0.2552595069975752</v>
+        <v>0.2682386493960394</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-0.04212525131050882</v>
+        <v>-0.02901444693556954</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>0.2854462435006582</v>
+        <v>0.2984891397950236</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>0.7129149968520565</v>
+        <v>0.7259812511525325</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>0.8350650084077031</v>
+        <v>0.8313741921805047</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>0.4894698822220818</v>
+        <v>0.4858774838444191</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>0.4402231633186986</v>
+        <v>0.4365906448650776</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>0.2053130235608265</v>
+        <v>0.2187703172710442</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>0.3000098117868362</v>
+        <v>0.3134621005069462</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>0.4828915096477218</v>
+        <v>0.4964475559993247</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>0.4612015029614085</v>
+        <v>0.4507718672632564</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X &gt; -0.07583</t>
+          <t>X &gt; -0.07585</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>3035</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>0.5872865562315468</v>
+        <v>0.5998088459071695</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>0.8867508345358175</v>
+        <v>0.8996606441118686</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>0.5248310570990355</v>
+        <v>0.5378381885166377</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>0.4903395439075098</v>
+        <v>0.503318686305974</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-0.01513274200485171</v>
+        <v>-0.002021937629912429</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>0.3152581248706099</v>
+        <v>0.3283010211649753</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>0.7247583449953723</v>
+        <v>0.7378245992958483</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>0.685911025291297</v>
+        <v>0.6990920345865348</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>0.4601664933099912</v>
+        <v>0.4733652322647544</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>0.4337645372771135</v>
+        <v>0.4471696649299446</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>0.1631133546399255</v>
+        <v>0.1765706483501432</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>0.2304454411451644</v>
+        <v>0.2438977298652745</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>0.5350672717159171</v>
+        <v>0.54862331806752</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>0.4882482415539755</v>
+        <v>0.4778186058558234</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X &gt; -0.03949</t>
+          <t>X &gt; -0.03951</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>2746</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>0.4198901575758924</v>
+        <v>0.4324124472515152</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>0.9933129029510468</v>
+        <v>1.006222712527098</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>0.8169438321883931</v>
+        <v>0.8299509636059952</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>0.765113934934277</v>
+        <v>0.7780930773327412</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>0.2266927198621076</v>
+        <v>0.2398035242370469</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>0.487718051605448</v>
+        <v>0.5007609478998134</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>0.8035670000287141</v>
+        <v>0.8166332543291901</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>0.9918825087490433</v>
+        <v>1.005063518044281</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>0.967299228539062</v>
+        <v>0.9804979674938252</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>1.027589192819221</v>
+        <v>1.040994320472052</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>0.6771694446123462</v>
+        <v>0.6906267383225639</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>0.8936356318194001</v>
+        <v>0.9070879205395102</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>1.274546352265602</v>
+        <v>1.288102398617205</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>1.342184654680281</v>
+        <v>1.331755018982129</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X &gt; -0.003153</t>
+          <t>X &gt; -0.003174</t>
         </is>
       </c>
       <c r="B15" t="n">
         <v>2427</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>1.235445074928052</v>
+        <v>1.247967364603674</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>1.47801237667332</v>
+        <v>1.490922186249371</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>1.289159327266667</v>
+        <v>1.302166458684269</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>1.295803065560207</v>
+        <v>1.308782207958672</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>1.169413164867926</v>
+        <v>1.182523969242865</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>1.549261365459564</v>
+        <v>1.56230426175393</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>2.041371488319136</v>
+        <v>2.054437742619612</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>2.068625666793515</v>
+        <v>2.081806676088753</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>1.925219517735236</v>
+        <v>1.938418256689999</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>2.228782012970996</v>
+        <v>2.242187140623827</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>1.941622425777439</v>
+        <v>1.955079719487657</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>2.182021240312821</v>
+        <v>2.195473529032931</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>2.503422995251725</v>
+        <v>2.516979041603328</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>2.25870675027214</v>
+        <v>2.248277114573987</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X &gt; 0.03319</t>
+          <t>X &gt; 0.03316</t>
         </is>
       </c>
       <c r="B16" t="n">
         <v>2112</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>1.389137437365783</v>
+        <v>1.401659727041405</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>1.908245642583346</v>
+        <v>1.921155452159397</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>1.418679966289787</v>
+        <v>1.431687097707389</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>1.359539159503342</v>
+        <v>1.372518301901806</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>1.105208853522086</v>
+        <v>1.118319657897025</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>1.592044730631685</v>
+        <v>1.60508762692605</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>2.028144346692741</v>
+        <v>2.041210600993217</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>2.460582160032445</v>
+        <v>2.473763169327682</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>2.399582273850143</v>
+        <v>2.412781012804906</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>2.685820725185863</v>
+        <v>2.699225852838694</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>2.528415885716761</v>
+        <v>2.541873179426979</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>2.846889952153106</v>
+        <v>2.860342240873216</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>3.042165644238501</v>
+        <v>3.055721690590104</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>2.771053643181453</v>
+        <v>2.760624007483301</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X &gt; 0.06953</t>
+          <t>X &gt; 0.0695</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1818</v>
+        <v>1819</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>1.631974221044153</v>
+        <v>1.669716184968671</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>2.880686636682761</v>
+        <v>2.917243670794335</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>2.210790427335887</v>
+        <v>2.247595980376843</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>2.396049060493439</v>
+        <v>2.432796385097703</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>1.85762784542127</v>
+        <v>1.839531570869511</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>2.540108286987319</v>
+        <v>2.521732428432045</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>2.840413073565429</v>
+        <v>2.821848897093304</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>3.363328684684923</v>
+        <v>3.344334953691387</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>3.412339799602726</v>
+        <v>3.393303319433592</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>3.497308123925734</v>
+        <v>3.477963962356064</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>3.402565800708267</v>
+        <v>3.383213326360867</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>3.876992962454139</v>
+        <v>3.8573935677761</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>4.226815359210001</v>
+        <v>4.206896370317565</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>4.146503688185952</v>
+        <v>4.102780453749155</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X &gt; 0.1059</t>
+          <t>X &gt; 0.1058</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1577</v>
+        <v>1578</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>2.294133017773532</v>
+        <v>2.335307036639286</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>3.092197959026151</v>
+        <v>3.132232477162269</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>2.443683088827775</v>
+        <v>2.420604311672136</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>3.651932416742831</v>
+        <v>3.628142509759861</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>2.479395792666217</v>
+        <v>2.456139395193944</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>2.840249271282325</v>
+        <v>2.880256137123084</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>3.135984799412704</v>
+        <v>3.175773914739032</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>3.619974514137873</v>
+        <v>3.659275613157625</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>3.432151546154685</v>
+        <v>3.471550744340796</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>3.533199474633406</v>
+        <v>3.572202290216261</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>3.582092313917606</v>
+        <v>3.620986556544153</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>3.743298553063923</v>
+        <v>3.78210742119353</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>4.210805514725237</v>
+        <v>4.249155553938422</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>4.016646060698413</v>
+        <v>4.031291711135793</v>
       </c>
     </row>
     <row r="19">
@@ -2890,49 +2890,49 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1384</v>
+        <v>1385</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>2.347602142217774</v>
+        <v>2.392730178851934</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>3.481693269137907</v>
+        <v>3.453024230192426</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>2.292026874680047</v>
+        <v>2.264029018722589</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>3.650603706709511</v>
+        <v>3.621690985415647</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>3.473454167937916</v>
+        <v>3.44441226264486</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>3.915404776173816</v>
+        <v>3.958392790474896</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>4.191942735202105</v>
+        <v>4.234693261533643</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>4.447302689021761</v>
+        <v>4.489646278396719</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>4.097285461799004</v>
+        <v>4.139855457614011</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>4.258720970412689</v>
+        <v>4.300766986193906</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>4.126221981355222</v>
+        <v>4.168267993998697</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>4.160605138700653</v>
+        <v>4.20264614635402</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>4.679656886137259</v>
+        <v>4.648921285820393</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>4.568106542112972</v>
+        <v>4.51364610572201</v>
       </c>
     </row>
     <row r="20">
@@ -2945,98 +2945,98 @@
         <v>1172</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>2.455367140540872</v>
+        <v>2.467889430216495</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>3.403520490033962</v>
+        <v>3.416430299610013</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>2.752679087191638</v>
+        <v>2.76568621860924</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>3.906823004782062</v>
+        <v>3.919802147180526</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>3.28307755762799</v>
+        <v>3.29618836200293</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>3.836492191589379</v>
+        <v>3.849535087883744</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>3.325137313907547</v>
+        <v>3.338203568208023</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>3.199250843453697</v>
+        <v>3.212431852748935</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>2.370332868534184</v>
+        <v>2.383531607488948</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>2.544098468489196</v>
+        <v>2.557503596142027</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>2.509993608335442</v>
+        <v>2.52345090204566</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>2.715025229844692</v>
+        <v>2.728477518564802</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>3.318661403882729</v>
+        <v>3.332217450234332</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>3.227085807831372</v>
+        <v>3.21665617213322</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X &gt; 0.2149</t>
+          <t>X &gt; 0.2148</t>
         </is>
       </c>
       <c r="B21" t="n">
         <v>1004</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>2.785446141941414</v>
+        <v>2.797968431617036</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>3.36510758873812</v>
+        <v>3.378017398314171</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>2.771035694890536</v>
+        <v>2.784042826308138</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>4.494914325506002</v>
+        <v>4.507893467904466</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>3.458485142306344</v>
+        <v>3.471595946681283</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>4.253935048149494</v>
+        <v>4.266977944443859</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>3.87039655000072</v>
+        <v>3.883462804301196</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>3.602416338470221</v>
+        <v>3.615597347765458</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>3.740619639538913</v>
+        <v>3.753818378493676</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>3.288900829012974</v>
+        <v>3.302305956665805</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>3.681757066448384</v>
+        <v>3.695214360158602</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>3.317733849291827</v>
+        <v>3.331186138011937</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>3.893495174601902</v>
+        <v>3.907051220953505</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>3.944013319627196</v>
+        <v>3.933583683929044</v>
       </c>
     </row>
     <row r="22">
@@ -3049,98 +3049,98 @@
         <v>840</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>2.387514060742411</v>
+        <v>2.400036350418034</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>2.680702352540052</v>
+        <v>2.693612162116104</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>2.404881264991083</v>
+        <v>2.417888396408685</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>3.606562969027159</v>
+        <v>3.619542111425623</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>2.353856039669267</v>
+        <v>2.366966844044207</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>3.484631310718271</v>
+        <v>3.497674207012636</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>3.042754736303124</v>
+        <v>3.0558209906036</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>2.456523718474003</v>
+        <v>2.469704727769241</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>2.87171430848219</v>
+        <v>2.884913047436953</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>2.378731980597117</v>
+        <v>2.392137108249948</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>3.36445484675572</v>
+        <v>3.377912140465938</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>2.922647527910677</v>
+        <v>2.936099816630787</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>4.050011964584819</v>
+        <v>4.063568010936422</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>3.466399963527778</v>
+        <v>3.455970327829625</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X &gt; 0.2876</t>
+          <t>X &gt; 0.2875</t>
         </is>
       </c>
       <c r="B23" t="n">
         <v>672</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>3.16132358455193</v>
+        <v>3.173845874227553</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>2.889035685873381</v>
+        <v>2.901945495449432</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>2.345357455467273</v>
+        <v>2.358364586884875</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>4.112515349979539</v>
+        <v>4.125494492378003</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>2.532427468240698</v>
+        <v>2.545538272615637</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>3.425107501194461</v>
+        <v>3.438150397488826</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>2.596326164874554</v>
+        <v>2.60939241917503</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>2.724380861331156</v>
+        <v>2.737561870626394</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>3.109809546577424</v>
+        <v>3.123008285532187</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>2.854922456787591</v>
+        <v>2.868327584440422</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>4.287073894374771</v>
+        <v>4.300531188084989</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>3.428599908863056</v>
+        <v>3.442052197583166</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>4.198821488394344</v>
+        <v>4.212377534745947</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>4.002114249242062</v>
+        <v>3.99168461354391</v>
       </c>
     </row>
     <row r="24">
@@ -3153,46 +3153,46 @@
         <v>566</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>3.866985708058579</v>
+        <v>3.879507997734201</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>4.02219654739114</v>
+        <v>4.035106356967191</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>2.56725716941645</v>
+        <v>2.580264300834052</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>5.347686980469192</v>
+        <v>5.360666122867656</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>3.572516648789247</v>
+        <v>3.585627453164186</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>3.516601696045541</v>
+        <v>3.529644592339906</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>2.901832643084212</v>
+        <v>2.914898897384688</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>3.671398360910487</v>
+        <v>3.684579370205725</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>3.257041584268826</v>
+        <v>3.270240323223589</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>3.466987070618991</v>
+        <v>3.480392198271822</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>4.322304417679497</v>
+        <v>4.335761711389715</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>3.649973794106209</v>
+        <v>3.663426082826319</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>4.11311140930971</v>
+        <v>4.126667455661313</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>2.949405179748545</v>
+        <v>2.938975544050393</v>
       </c>
     </row>
     <row r="25">
@@ -3205,98 +3205,98 @@
         <v>481</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>4.471218644446992</v>
+        <v>4.483740934122615</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>3.899146070983768</v>
+        <v>3.912055880559819</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>3.712177572287395</v>
+        <v>3.725184703704997</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>5.505632368096556</v>
+        <v>5.51861151049502</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>3.927710113523339</v>
+        <v>3.940820917898279</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>3.809351635438588</v>
+        <v>3.822394531732954</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>3.932518126066519</v>
+        <v>3.945584380366995</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>3.673234935185221</v>
+        <v>3.686415944480459</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>3.612235049002919</v>
+        <v>3.625433787957682</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>2.762109863974992</v>
+        <v>2.775514991627823</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>4.220558202859081</v>
+        <v>4.234015496569299</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>2.383839489102641</v>
+        <v>2.397291777822751</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>3.626786541359408</v>
+        <v>3.640342587711011</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>2.213306210434027</v>
+        <v>2.202876574735875</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X &gt; 0.3966</t>
+          <t>X &gt; 0.3965</t>
         </is>
       </c>
       <c r="B26" t="n">
         <v>398</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>4.039224996372937</v>
+        <v>4.05174728604856</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>2.42765138340868</v>
+        <v>2.440561192984731</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>2.284038958219128</v>
+        <v>2.29704608963673</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>4.67559862348994</v>
+        <v>4.688577765888404</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>2.880896001382595</v>
+        <v>2.894006805757535</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>2.42456909487715</v>
+        <v>2.437611991171515</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>2.591091659011916</v>
+        <v>2.604157913312392</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>2.375164541637446</v>
+        <v>2.388345550932684</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>2.816677218269213</v>
+        <v>2.829875957223976</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>1.966552033241285</v>
+        <v>1.979957160894116</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>3.018080115958881</v>
+        <v>3.031537409669099</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>1.293669303455069</v>
+        <v>1.307121592175179</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>2.63220866235941</v>
+        <v>2.645764708711013</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>0.8718797433794236</v>
+        <v>0.8614501076812715</v>
       </c>
     </row>
     <row r="27">
@@ -3309,150 +3309,150 @@
         <v>356</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>4.248134713497898</v>
+        <v>4.26065700317352</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>2.63656110053364</v>
+        <v>2.649470910109692</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>2.522591270341536</v>
+        <v>2.535598401759138</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>4.619136537780498</v>
+        <v>4.632115680178963</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>2.395322064281359</v>
+        <v>2.408432868656298</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>1.569168496379049</v>
+        <v>1.582211392673415</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>0.9226370262977781</v>
+        <v>0.9357032805982541</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>0.7363525039207701</v>
+        <v>0.7495335132160079</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>1.237150370547461</v>
+        <v>1.250349109502224</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>0.9488229383285187</v>
+        <v>0.9622280659813498</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>1.867665119628924</v>
+        <v>1.881122413339142</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>0.2166550185473852</v>
+        <v>0.2301073072674953</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>1.200894789624947</v>
+        <v>1.21445083597655</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>-0.2347771365257216</v>
+        <v>-0.2452067722238738</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X &gt; 0.4693</t>
+          <t>X &gt; 0.4692</t>
         </is>
       </c>
       <c r="B28" t="n">
         <v>313</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>2.778127174997692</v>
+        <v>2.790649464673315</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>1.166553562033435</v>
+        <v>1.179463371609486</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>1.091173673328221</v>
+        <v>1.104180804745823</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>3.138359713283968</v>
+        <v>3.151338855682432</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>0.3635167729721758</v>
+        <v>0.3766275773471151</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>0.02198107490508505</v>
+        <v>0.03502397119945044</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-0.0627526423671938</v>
+        <v>-0.04968638806671777</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>0.109041594634057</v>
+        <v>0.1222226039292948</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>0.3675305263431312</v>
+        <v>0.3807292652978944</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-0.1631058407934205</v>
+        <v>-0.1497007131405894</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-0.3678591651109997</v>
+        <v>-0.3544018714007819</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-1.930920097222447</v>
+        <v>-1.917467808502337</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-0.4342418008191018</v>
+        <v>-0.4206857544674989</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>-1.781964557999686</v>
+        <v>-1.792394193697838</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X &gt; 0.5056</t>
+          <t>X &gt; 0.5055</t>
         </is>
       </c>
       <c r="B29" t="n">
         <v>253</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>0.8662454742564307</v>
+        <v>0.8787677639320535</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>0.04518569528426752</v>
+        <v>0.05809550486031867</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>1.626601573667912</v>
+        <v>1.639608705085514</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>2.94262545726356</v>
+        <v>2.955604599662024</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-0.3625941767809522</v>
+        <v>-0.3494833724060129</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-0.06515223906529144</v>
+        <v>-0.05210934277092605</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>0.6406278776545307</v>
+        <v>0.6536941319550067</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>-0.6170693551190709</v>
+        <v>-0.6038883458238331</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>0.5077015096867754</v>
+        <v>0.5209002486415386</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>-0.737680592337199</v>
+        <v>-0.7242754646843679</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>-1.337690833650818</v>
+        <v>-1.3242335399406</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>-3.279592261285629</v>
+        <v>-3.266139972565519</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>-2.51407612124239</v>
+        <v>-2.500520074890787</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>-3.845382456950297</v>
+        <v>-3.855812092648449</v>
       </c>
     </row>
     <row r="30">
@@ -3465,254 +3465,254 @@
         <v>205</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>1.652903143204661</v>
+        <v>1.665425432880284</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>1.016939286337966</v>
+        <v>1.029849095914017</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>1.10987545779016</v>
+        <v>1.122882589207762</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>1.24012859039766</v>
+        <v>1.253107732796124</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-1.737317014918418</v>
+        <v>-1.724206210543478</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-2.415484833300319</v>
+        <v>-2.402441937005953</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>-1.524608794475036</v>
+        <v>-1.51154254017456</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-1.503987315207752</v>
+        <v>-1.490806305912514</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-1.564987201390053</v>
+        <v>-1.55178846243529</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-3.878527020564327</v>
+        <v>-3.865121892911496</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>-3.595475466833122</v>
+        <v>-3.582018173122904</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>-5.512311821682815</v>
+        <v>-5.498859532962705</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-5.444761554578939</v>
+        <v>-5.431205508227336</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-6.170649978400213</v>
+        <v>-6.181079614098365</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X &gt; 0.5783</t>
+          <t>X &gt; 0.5782</t>
         </is>
       </c>
       <c r="B31" t="n">
         <v>174</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>0.3801248981808314</v>
+        <v>0.3926471878564541</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>-1.806161358461594</v>
+        <v>-1.793251548885543</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-2.201030065058184</v>
+        <v>-2.188022933640582</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-0.9213516450943615</v>
+        <v>-0.9083725026958973</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-4.908048722235492</v>
+        <v>-4.894937917860553</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-6.334744715554315</v>
+        <v>-6.32170181925995</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>-6.419478432826594</v>
+        <v>-6.406412178526118</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>-7.461374475286256</v>
+        <v>-7.448193465991018</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-6.372949074112235</v>
+        <v>-6.359750335157472</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>-6.07364897178384</v>
+        <v>-6.060243844131008</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>-5.70368965242325</v>
+        <v>-5.690232358713033</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>-7.968157069790472</v>
+        <v>-7.954704781070362</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>-7.813699037057212</v>
+        <v>-7.800142990705609</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>-6.989265061102763</v>
+        <v>-6.999694696800915</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>X &gt; 0.6146</t>
+          <t>X &gt; 0.6145</t>
         </is>
       </c>
       <c r="B32" t="n">
         <v>138</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>-1.044162957891139</v>
+        <v>-1.031640668215516</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>-3.380374252014811</v>
+        <v>-3.367464442438759</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-0.8766922339737135</v>
+        <v>-0.8636851025561114</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>0.7028362609526226</v>
+        <v>0.7158154033510868</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-5.632686403394906</v>
+        <v>-5.619575599019967</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-8.233795190316933</v>
+        <v>-8.220752294022567</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>-8.318528907589211</v>
+        <v>-8.305462653288735</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>-9.510349987530134</v>
+        <v>-9.497168978234896</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-7.39743683023417</v>
+        <v>-7.384238091279407</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>-6.07364897178384</v>
+        <v>-6.060243844131008</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>-5.553764614941997</v>
+        <v>-5.540307321231779</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>-7.693294501074831</v>
+        <v>-7.679842212354721</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>-9.562824474338569</v>
+        <v>-9.549268427986966</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>-10.0377408232217</v>
+        <v>-10.04817045891986</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X &gt; 0.651</t>
+          <t>X &gt; 0.6509</t>
         </is>
       </c>
       <c r="B33" t="n">
         <v>116</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>0.09276857634174718</v>
+        <v>0.1052908660173699</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>-1.51880503662251</v>
+        <v>-1.505895227046459</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>-0.1895358121846158</v>
+        <v>-0.1765286807670137</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>1.664855251457361</v>
+        <v>1.677834393855825</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-4.045979756718253</v>
+        <v>-4.032868952343314</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-8.058882646588799</v>
+        <v>-8.045839750294434</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>-7.281547398343832</v>
+        <v>-7.268481144043356</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-6.886661831608095</v>
+        <v>-6.873480822312857</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-6.947661717790396</v>
+        <v>-6.934462978835633</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>-5.211580006266601</v>
+        <v>-5.19817487861377</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>-5.41633333058418</v>
+        <v>-5.402876036873963</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>-9.692295000824956</v>
+        <v>-9.678842712104846</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>-11.83668754280433</v>
+        <v>-11.82313149645273</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>-11.58696621052805</v>
+        <v>-11.5973958462262</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X &gt; 0.6873</t>
+          <t>X &gt; 0.6872</t>
         </is>
       </c>
       <c r="B34" t="n">
         <v>100</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>1.506561679790025</v>
+        <v>1.519083969465647</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>-0.1050119331742323</v>
+        <v>-0.09210212359818115</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>0.5001193602291849</v>
+        <v>0.513126491646787</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>1.630372492836685</v>
+        <v>1.643351635235149</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-6.908048722235492</v>
+        <v>-6.894937917860553</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-8.610606784519831</v>
+        <v>-8.597563888225466</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>-6.69534050179211</v>
+        <v>-6.682274247491634</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>-7.162523900573611</v>
+        <v>-7.149342891278373</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>-8.223523786755912</v>
+        <v>-8.210325047801149</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>-8.07364897178384</v>
+        <v>-8.060243844131008</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>-6.278402296101419</v>
+        <v>-6.264945002391201</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>-12.24401913875599</v>
+        <v>-12.23056685003588</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>-14.66427374970089</v>
+        <v>-14.65071770334929</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>-14.4145524174246</v>
+        <v>-14.42498205312275</v>
       </c>
     </row>
     <row r="35">
@@ -3725,46 +3725,46 @@
         <v>82</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>1.165098265155883</v>
+        <v>1.177620554831506</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>-1.665987542930331</v>
+        <v>-1.65307773335428</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>0.378168140716987</v>
+        <v>0.3911752721345891</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>2.947445663568381</v>
+        <v>2.960424805966845</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>-4.908048722235492</v>
+        <v>-4.894937917860553</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>-8.269143369885683</v>
+        <v>-8.256100473591317</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>-10.79290147740186</v>
+        <v>-10.77983522310139</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>-8.821060485939462</v>
+        <v>-8.807879476644224</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>-11.32108476236566</v>
+        <v>-11.3078860234109</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>-12.17120994739359</v>
+        <v>-12.15780481974076</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>-11.15645107658922</v>
+        <v>-11.142993782879</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>-16.00011669973159</v>
+        <v>-15.98666441101148</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>-18.8593957009204</v>
+        <v>-18.8458396545688</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>-19.82918656376606</v>
+        <v>-19.83961619946422</v>
       </c>
     </row>
   </sheetData>
@@ -3815,7 +3815,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Measures the winrate at horizon h days, given that MA Ratio-100 is below threshold x, minus the unconditional baseline winrate.</t>
+          <t>Measures the winrate at horizon h, given that MA Ratio-100 is below threshold x, minus the unconditional baseline winrate.</t>
         </is>
       </c>
     </row>
@@ -3911,46 +3911,46 @@
         <v>82</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>8.482171435887587</v>
+        <v>8.494693725563209</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>6.87059782292333</v>
+        <v>6.883507632499381</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>6.47572911632674</v>
+        <v>6.488736247744342</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>9.045006639178141</v>
+        <v>9.057985781576605</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>10.94560981434988</v>
+        <v>10.95872061872482</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>11.24305175206554</v>
+        <v>11.25609464835991</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>12.37783022991521</v>
+        <v>12.39089648421569</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>11.91064683113371</v>
+        <v>11.92382784042895</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>9.410622554707508</v>
+        <v>9.423821293662272</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>13.43854615016737</v>
+        <v>13.4519512778202</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>15.6728172160937</v>
+        <v>15.68627450980392</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>13.26817598319522</v>
+        <v>13.28162827191533</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>14.06743356737228</v>
+        <v>14.08098961372389</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>14.31715489964857</v>
+        <v>14.30672526395042</v>
       </c>
     </row>
     <row r="7">
@@ -3963,46 +3963,46 @@
         <v>126</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>10.20497437820272</v>
+        <v>10.21749666787834</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>2.244194416032116</v>
+        <v>2.257104225608167</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>6.611230471340292</v>
+        <v>6.624237602757894</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>9.916086778550969</v>
+        <v>9.929065920949434</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>12.55226873808198</v>
+        <v>12.56537954245692</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>9.675107501194461</v>
+        <v>9.688150397488826</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>11.97132616487455</v>
+        <v>11.98439241917502</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>8.329539591489876</v>
+        <v>8.342720600785114</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>9.06219049895838</v>
+        <v>9.075389237913143</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>11.38666848853363</v>
+        <v>11.40007361618646</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>11.97556595786683</v>
+        <v>11.98902325157705</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>13.59725070251385</v>
+        <v>13.61070299123396</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>10.79604371061658</v>
+        <v>10.80959975696818</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>11.83941583654365</v>
+        <v>11.8289862008455</v>
       </c>
     </row>
     <row r="8">
@@ -4015,46 +4015,46 @@
         <v>204</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>5.83989501312336</v>
+        <v>5.852417302798983</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-0.1834433057232516</v>
+        <v>-0.1705334961472005</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>0.8922762229742816</v>
+        <v>0.9052833543918837</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>2.983313669307265</v>
+        <v>2.996292811705729</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>3.915480689529218</v>
+        <v>3.928591493904158</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>2.252138313519382</v>
+        <v>2.265181209813747</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>2.167404596247103</v>
+        <v>2.180470850547579</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-0.7507591946912626</v>
+        <v>-0.7375781853960248</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>1.639221311283301</v>
+        <v>1.652420050238064</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>2.749880439980871</v>
+        <v>2.763285567633702</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>2.545127115663291</v>
+        <v>2.558584409373509</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>1.599118116145981</v>
+        <v>1.612570404866091</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>0.1984713483383231</v>
+        <v>0.212027394689926</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>0.4481926806146106</v>
+        <v>0.4377630449164585</v>
       </c>
     </row>
     <row r="9">
@@ -4067,46 +4067,46 @@
         <v>296</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>1.89845357168192</v>
+        <v>1.910975861357542</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-1.064471392633692</v>
+        <v>-1.051561583057641</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-0.1079887478789274</v>
+        <v>-0.0949816164613253</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>1.035777898242081</v>
+        <v>1.048757040640545</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>1.173032358845596</v>
+        <v>1.186143163220535</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>0.1191229452098952</v>
+        <v>0.1321658415042606</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-1.316962123413731</v>
+        <v>-1.303895869113255</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-3.473334711384425</v>
+        <v>-3.460153702089187</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-2.520821084053217</v>
+        <v>-2.507622345098454</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-2.357432755567622</v>
+        <v>-2.344027627914791</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-0.8729968906960153</v>
+        <v>-0.8595395969857975</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-2.865640760377609</v>
+        <v>-2.852188471657499</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-2.610219695646833</v>
+        <v>-2.59666364929523</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-2.022660525532707</v>
+        <v>-2.033090161230859</v>
       </c>
     </row>
     <row r="10">
@@ -4119,46 +4119,46 @@
         <v>410</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>0.4333909480827103</v>
+        <v>0.445913237758333</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-2.885499738052282</v>
+        <v>-2.872589928476231</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-2.060856249526921</v>
+        <v>-2.047849118109319</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-0.467188482773075</v>
+        <v>-0.4542093403746108</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>0.2139024972767061</v>
+        <v>0.2270133016516453</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-0.9520701991539724</v>
+        <v>-0.939027302859607</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-2.012413672523813</v>
+        <v>-1.999347418223337</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-3.211304388378487</v>
+        <v>-3.198123379083249</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-1.321084762365665</v>
+        <v>-1.307886023410902</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-1.927307508369204</v>
+        <v>-1.913902380716372</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-1.156451076589221</v>
+        <v>-1.142993782879003</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-2.585482553390129</v>
+        <v>-2.572030264670019</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-2.274029847261865</v>
+        <v>-2.260473800910262</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-1.780406075961182</v>
+        <v>-1.790835711659334</v>
       </c>
     </row>
     <row r="11">
@@ -4168,49 +4168,49 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-1.074998603897917</v>
+        <v>-1.062476314222295</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-3.750402004096223</v>
+        <v>-3.737492194520172</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-2.549526029841751</v>
+        <v>-2.536518898424148</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-1.000833180922193</v>
+        <v>-0.9878540385237287</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>0.05649028485670016</v>
+        <v>0.06960108923163943</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-0.8872025292006782</v>
+        <v>-0.8741596329063128</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-2.21307099824601</v>
+        <v>-2.200004743945534</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-3.212169290644539</v>
+        <v>-3.198988281349301</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-1.854729460514783</v>
+        <v>-1.841530721560019</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-2.172939751925682</v>
+        <v>-2.159534624272851</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-1.136558324470208</v>
+        <v>-1.12310103075999</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-1.81139502528081</v>
+        <v>-1.797942736560699</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-1.699734742608698</v>
+        <v>-1.686178696257095</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-0.6419058810125264</v>
+        <v>-0.5739182233355251</v>
       </c>
     </row>
     <row r="12">
@@ -4220,361 +4220,361 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-1.005728100287598</v>
+        <v>-1.0597274000434</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-2.032473073070612</v>
+        <v>-2.086927479354969</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-0.8033825852961129</v>
+        <v>-0.8599305031718742</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-0.3436534811892997</v>
+        <v>-0.4007469380463107</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>1.00872631027427</v>
+        <v>0.9492179262952902</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-0.3137317845198311</v>
+        <v>-0.3712960078613534</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-2.283345716915974</v>
+        <v>-2.338524247491634</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-3.011285308657051</v>
+        <v>-2.998104299361813</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-0.9862356511626942</v>
+        <v>-0.973036912207931</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-0.9237141608320769</v>
+        <v>-0.9103090331792458</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>0.2490128475017173</v>
+        <v>0.1887707733584705</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>0.09585014228976263</v>
+        <v>0.03575168782312943</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-0.2506611842558613</v>
+        <v>-0.3108484223035362</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-0.05806486827649593</v>
+        <v>-0.01136948767772594</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X &lt; -0.07583</t>
+          <t>X &lt; -0.07585</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1044</v>
+        <v>1045</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-1.405453457390671</v>
+        <v>-1.441218488001276</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-2.30576950893181</v>
+        <v>-2.341865605149749</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-1.51409864924949</v>
+        <v>-1.551267447747165</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-0.8591910745257465</v>
+        <v>-0.8969327249544321</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>0.6475068333200653</v>
+        <v>0.6079083819496987</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-0.2379832103753472</v>
+        <v>-0.2765762339044784</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-1.507899968966228</v>
+        <v>-1.545392118214068</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-1.54347628152599</v>
+        <v>-1.581312444085221</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-0.504743996479462</v>
+        <v>-0.5436583811344846</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-0.5392978267456741</v>
+        <v>-0.5788329766381537</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>0.3596110754363124</v>
+        <v>0.3190244632576551</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>0.3525391786436245</v>
+        <v>0.3119355377387194</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-0.2049436061602279</v>
+        <v>-0.2453639748598064</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>0.003072103648193547</v>
+        <v>0.03434809041790743</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X &lt; -0.03949</t>
+          <t>X &lt; -0.03951</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1333</v>
+        <v>1334</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-0.636083193909819</v>
+        <v>-0.6620593119003573</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-1.837353940609177</v>
+        <v>-1.863275972037997</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-1.672499687389866</v>
+        <v>-1.698769419133889</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-1.130610381325646</v>
+        <v>-1.157243602860092</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>0.009984064649756874</v>
+        <v>-0.01779718815094355</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-0.471904323669726</v>
+        <v>-0.4992032324877584</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-1.187877815224944</v>
+        <v>-1.214712726238844</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-1.689783049191981</v>
+        <v>-1.716507070382853</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-1.337126178385205</v>
+        <v>-1.364171201647302</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-1.548592876047117</v>
+        <v>-1.575938911395582</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-0.7394801404128017</v>
+        <v>-0.7675628034383166</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-1.038026629392689</v>
+        <v>-1.065896191353239</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-1.566822475338071</v>
+        <v>-1.594537928068384</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-1.65086149469392</v>
+        <v>-1.62738085372245</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X &lt; -0.003153</t>
+          <t>X &lt; -0.003174</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1652</v>
+        <v>1653</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-1.622567449339108</v>
+        <v>-1.640579896080574</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-2.001646548558845</v>
+        <v>-2.020030051526106</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-1.884125979518267</v>
+        <v>-1.902738892968607</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-1.54170933628486</v>
+        <v>-1.560496831391433</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-1.325869312241515</v>
+        <v>-1.344998086332268</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-1.839522447170438</v>
+        <v>-1.858250221759484</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-2.615774498175469</v>
+        <v>-2.634081476407303</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-2.749978665350447</v>
+        <v>-2.768390510325986</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-2.296547323267681</v>
+        <v>-2.315270765533356</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-2.812779406566442</v>
+        <v>-2.831517229767698</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-2.320698368608966</v>
+        <v>-2.339824229444346</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-2.555990118199759</v>
+        <v>-2.574977726168811</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-2.822773447220548</v>
+        <v>-2.841769698512536</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-2.419395032436711</v>
+        <v>-2.401993547375625</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X &lt; 0.03319</t>
+          <t>X &lt; 0.03316</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1967</v>
+        <v>1968</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-1.331822158593809</v>
+        <v>-1.345126025486401</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-1.906932094872062</v>
+        <v>-1.920384951881012</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-1.517069719649484</v>
+        <v>-1.530835105119266</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-1.157690228458208</v>
+        <v>-1.171612975482759</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-0.8594657262840713</v>
+        <v>-0.8736936083006199</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-1.344783999709705</v>
+        <v>-1.358697491464333</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-1.858461069167994</v>
+        <v>-1.872147665213149</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-2.40023297305207</v>
+        <v>-2.413780581247977</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-2.130217498723461</v>
+        <v>-2.143928697066222</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-2.496784436015197</v>
+        <v>-2.510548103765899</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-2.268250011837459</v>
+        <v>-2.282195129230374</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-2.511159819304488</v>
+        <v>-2.5249830936907</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-2.548420091164303</v>
+        <v>-2.562347972521451</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-2.220348045284283</v>
+        <v>-2.207502378326012</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X &lt; 0.06953</t>
+          <t>X &lt; 0.0695</t>
         </is>
       </c>
       <c r="B17" t="n">
         <v>2261</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-1.174177106489665</v>
+        <v>-1.205630190604715</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-2.191241585615934</v>
+        <v>-2.222326496673404</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-1.771007400334199</v>
+        <v>-1.802014353423644</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-1.661569382988951</v>
+        <v>-1.692623706024222</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-1.207608193601132</v>
+        <v>-1.194497389226193</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-1.723872540359402</v>
+        <v>-1.710829644065036</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-2.005746145531084</v>
+        <v>-1.992679891230608</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-2.493798713101178</v>
+        <v>-2.48061770380594</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-2.355033054187508</v>
+        <v>-2.341834315232745</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-2.475414976198849</v>
+        <v>-2.462009848546018</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-2.347306889740999</v>
+        <v>-2.333849596030781</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-2.642605086612818</v>
+        <v>-2.629152797892708</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-2.773911238648722</v>
+        <v>-2.760355192297119</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-2.677268029985413</v>
+        <v>-2.643469448080737</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X &lt; 0.1059</t>
+          <t>X &lt; 0.1058</t>
         </is>
       </c>
       <c r="B18" t="n">
         <v>2502</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-1.320476093569816</v>
+        <v>-1.347715235305721</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-1.837708830548934</v>
+        <v>-1.86457626838736</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-1.535296477415066</v>
+        <v>-1.522289345997464</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-2.060710309711091</v>
+        <v>-2.047731167312627</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-1.303906946050702</v>
+        <v>-1.290796141675763</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-1.5030370634043</v>
+        <v>-1.529834804560124</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-1.72603001952826</v>
+        <v>-1.752820281768237</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-2.092348461977117</v>
+        <v>-2.119039860975342</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-1.813073048822119</v>
+        <v>-1.839762622591735</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-1.92360906755399</v>
+        <v>-1.95010816974952</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-1.907144811071475</v>
+        <v>-1.933607677041898</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-1.930920097222447</v>
+        <v>-1.957403910738755</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-2.089763162405646</v>
+        <v>-2.116159173584997</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-1.938133552516533</v>
+        <v>-1.948563188214685</v>
       </c>
     </row>
     <row r="19">
@@ -4587,46 +4587,46 @@
         <v>2695</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-1.090188689486197</v>
+        <v>-1.114594021671721</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-1.68535918105011</v>
+        <v>-1.672449371474059</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-1.173938289438233</v>
+        <v>-1.160931158020631</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-1.652437118993269</v>
+        <v>-1.639457976594805</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-1.542664106850879</v>
+        <v>-1.529553302475939</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-1.743422174826904</v>
+        <v>-1.767375208980184</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-1.919618814153324</v>
+        <v>-1.943562182354697</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-2.108099613272614</v>
+        <v>-2.131941928671928</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-1.779079342311462</v>
+        <v>-1.802917640393744</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-1.905438523469648</v>
+        <v>-1.929084155357387</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-1.793598737910166</v>
+        <v>-1.8172059364164</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-1.739013577020721</v>
+        <v>-1.762639523376627</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-1.87940728085816</v>
+        <v>-1.865851234506557</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-1.794886369187118</v>
+        <v>-1.768210253493812</v>
       </c>
     </row>
     <row r="20">
@@ -4636,101 +4636,101 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2907</v>
+        <v>2908</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-0.8838492791140808</v>
+        <v>-0.8889954553888515</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-1.278701552907016</v>
+        <v>-1.283882945515984</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-1.107145889942167</v>
+        <v>-1.11243020585237</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-1.369970325126978</v>
+        <v>-1.375154190673008</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-1.101464360095569</v>
+        <v>-1.106799419403238</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-1.300143662735948</v>
+        <v>-1.305382818266622</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-1.126363151071452</v>
+        <v>-1.131673904438458</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-1.128881607405049</v>
+        <v>-1.134243371717638</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-0.6562160944482258</v>
+        <v>-0.6617496959302258</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-0.7661944887883081</v>
+        <v>-0.7717823056694684</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-0.7113919868230667</v>
+        <v>-0.7170233259913417</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-0.726659221258565</v>
+        <v>-0.7322850630942952</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-0.8527194168260621</v>
+        <v>-0.8583491918332982</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-0.7901974122646465</v>
+        <v>-0.7853671975519134</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X &lt; 0.2149</t>
+          <t>X &lt; 0.2148</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>3075</v>
+        <v>3076</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-0.809500496375783</v>
+        <v>-0.813709814930597</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-1.011393533433385</v>
+        <v>-1.015677253131862</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-0.9029914628427562</v>
+        <v>-0.907346459438422</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-1.274003520129284</v>
+        <v>-1.278229699826426</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-0.9197218739864681</v>
+        <v>-0.9241113376336472</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-1.156179278843538</v>
+        <v>-1.160469205994595</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-1.061336608216514</v>
+        <v>-1.065667046713166</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-1.024257104078963</v>
+        <v>-1.028642047670324</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-0.9378095010416274</v>
+        <v>-0.9422302733772554</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-0.8284394881852748</v>
+        <v>-0.8329711168582818</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-0.9177785144250095</v>
+        <v>-0.922301286899156</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-0.7354068540631076</v>
+        <v>-0.7399885524400389</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-0.8125182230428933</v>
+        <v>-0.8171135434532886</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-0.8047963198636197</v>
+        <v>-0.8007947969459082</v>
       </c>
     </row>
     <row r="22">
@@ -4740,101 +4740,101 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>3239</v>
+        <v>3240</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-0.5254186400131786</v>
+        <v>-0.5288717637037337</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-0.613778466548581</v>
+        <v>-0.6173173757507016</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-0.6229575628477448</v>
+        <v>-0.6265228470182436</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-0.7531301233529177</v>
+        <v>-0.7566483647648568</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-0.4129748306098833</v>
+        <v>-0.4166369021634111</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-0.6839052138392105</v>
+        <v>-0.6874653660579852</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-0.5979899164563065</v>
+        <v>-0.6015843799215688</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-0.4938027911745309</v>
+        <v>-0.4974636552956255</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-0.476298139406957</v>
+        <v>-0.4799706564298134</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-0.3844722835322187</v>
+        <v>-0.3882339797660279</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-0.6028933510057968</v>
+        <v>-0.6066039601463729</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-0.4279129986757653</v>
+        <v>-0.4316772756990517</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-0.6148910336515101</v>
+        <v>-0.6186288418867747</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-0.4404863476499798</v>
+        <v>-0.4373277321350955</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X &lt; 0.2876</t>
+          <t>X &lt; 0.2875</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>3407</v>
+        <v>3408</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-0.5343739927245963</v>
+        <v>-0.5370399709026614</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-0.4928446327940037</v>
+        <v>-0.495610895528003</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-0.4624318393027096</v>
+        <v>-0.4652297528691562</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-0.6382842235812305</v>
+        <v>-0.6410251933195639</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-0.3120299868724956</v>
+        <v>-0.3148969462480338</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-0.4671221578726872</v>
+        <v>-0.4699292278039238</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-0.3309585451430195</v>
+        <v>-0.3338115827771446</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-0.4013167514379532</v>
+        <v>-0.4041759317001663</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-0.358342075149821</v>
+        <v>-0.361218689758374</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-0.3421919210655702</v>
+        <v>-0.3451207491720325</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-0.5892527359841182</v>
+        <v>-0.5921217833938428</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-0.3625289656847102</v>
+        <v>-0.3654642107396953</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-0.4142737497008895</v>
+        <v>-0.4172181433610191</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-0.3535016396142083</v>
+        <v>-0.3510383911509294</v>
       </c>
     </row>
     <row r="24">
@@ -4844,49 +4844,49 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>3513</v>
+        <v>3514</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-0.5365466582700975</v>
+        <v>-0.5387555542088549</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-0.5730970395572186</v>
+        <v>-0.5753692818511666</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-0.4136150325063497</v>
+        <v>-0.4159515225376182</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-0.693783056411128</v>
+        <v>-0.696035424923771</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-0.393568313376889</v>
+        <v>-0.3959313893337253</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-0.3646539302170737</v>
+        <v>-0.3670130648296706</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-0.2919314108830164</v>
+        <v>-0.2943162810048463</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-0.4594832640291386</v>
+        <v>-0.4618428912783727</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-0.2775317458235662</v>
+        <v>-0.2799470995203848</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-0.3443342148887609</v>
+        <v>-0.3467702796057139</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-0.4479131038374859</v>
+        <v>-0.4503302739294455</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-0.2838484417431886</v>
+        <v>-0.2863120149960565</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-0.2613141594903041</v>
+        <v>-0.2638044743307972</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-0.05246872827002846</v>
+        <v>-0.05048006109087311</v>
       </c>
     </row>
     <row r="25">
@@ -4896,101 +4896,101 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>3598</v>
+        <v>3599</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-0.5133773952584448</v>
+        <v>-0.515246041608556</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-0.4485022378833747</v>
+        <v>-0.4504516112747226</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-0.4960014488592179</v>
+        <v>-0.4979538407631878</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-0.5725099905336108</v>
+        <v>-0.5744372259452462</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-0.3474720657342445</v>
+        <v>-0.3494833724060129</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-0.3122152149136213</v>
+        <v>-0.3142259342470908</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-0.3541477139973779</v>
+        <v>-0.3561511193718374</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-0.3623019249909234</v>
+        <v>-0.3643220868400974</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-0.2415643085433103</v>
+        <v>-0.2436213852040297</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-0.1602675170364805</v>
+        <v>-0.1623809520965978</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-0.3217235957404085</v>
+        <v>-0.3238011933962071</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-0.02179691653377347</v>
+        <v>-0.0239575748345402</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-0.09300395253500682</v>
+        <v>-0.09516214779372945</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>0.1168539194292038</v>
+        <v>0.1185022480720264</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X &lt; 0.3966</t>
+          <t>X &lt; 0.3965</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3681</v>
+        <v>3682</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-0.3548351799825866</v>
+        <v>-0.3564234730242006</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-0.1922039180104065</v>
+        <v>-0.1938888047026737</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-0.2474429366288931</v>
+        <v>-0.2491264192657567</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-0.346327588442108</v>
+        <v>-0.3479809758157728</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-0.138401025758526</v>
+        <v>-0.1401289230082057</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-0.07008089674537388</v>
+        <v>-0.07181863077289563</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-0.1129110007075127</v>
+        <v>-0.1146407424767233</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-0.1313332306522597</v>
+        <v>-0.1330739108011514</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-0.06888461149817715</v>
+        <v>-0.07064509119686591</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-0.008520070834038052</v>
+        <v>-0.01032523317061873</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-0.08947721466819303</v>
+        <v>-0.09126793319174453</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>0.1502246842144146</v>
+        <v>0.1483690891606528</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>0.09835525627412522</v>
+        <v>0.09649923936045468</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>0.309163963993484</v>
+        <v>0.3104878002178282</v>
       </c>
     </row>
     <row r="27">
@@ -5000,153 +5000,153 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>3723</v>
+        <v>3724</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-0.3253441017945562</v>
+        <v>-0.3267816981822023</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-0.182655842143447</v>
+        <v>-0.1841792113926175</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-0.2417124555180123</v>
+        <v>-0.2432322767601747</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-0.2844413298260591</v>
+        <v>-0.2859467043470758</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-0.05810231280355538</v>
+        <v>-0.05968477025808028</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>0.03962103643969783</v>
+        <v>0.03802024896638301</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>0.07677746067438562</v>
+        <v>0.07516343677531978</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>0.05335166928426105</v>
+        <v>0.05172949478060929</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>0.1144590458621124</v>
+        <v>0.1128178859612561</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>0.110949901304437</v>
+        <v>0.1092840528647017</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>0.05546780588461786</v>
+        <v>0.05381002846471716</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>0.2660479753379761</v>
+        <v>0.2643338477633677</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>0.2637606219425095</v>
+        <v>0.262033974503062</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>0.4213326215224882</v>
+        <v>0.4224937793154879</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X &lt; 0.4693</t>
+          <t>X &lt; 0.4692</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>3766</v>
+        <v>3767</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>-0.1515489314827931</v>
+        <v>-0.1528737024920304</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-0.02878112322188286</v>
+        <v>-0.03018098043861528</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-0.09162011554525407</v>
+        <v>-0.09301432359938389</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-0.1058563207226442</v>
+        <v>-0.1072440756465056</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>0.1383088936585466</v>
+        <v>0.1368417431563884</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>0.1853656585114436</v>
+        <v>0.1838930654169175</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>0.1681633413035755</v>
+        <v>0.1666923661808681</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>0.1131919000626596</v>
+        <v>0.1117225738687253</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>0.1994409440847207</v>
+        <v>0.1979464262179391</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>0.2128231767572686</v>
+        <v>0.2113021648851614</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>0.261794042449921</v>
+        <v>0.2602539366008401</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>0.4438789504159857</v>
+        <v>0.4422906718532218</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>0.4103214188682642</v>
+        <v>0.4087302796655763</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>0.5424311194845899</v>
+        <v>0.5434278221095283</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X &lt; 0.5056</t>
+          <t>X &lt; 0.5055</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>3826</v>
+        <v>3827</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>0.02023711610156198</v>
+        <v>0.0190839694656475</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>0.06382600325098764</v>
+        <v>0.06262567009810027</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-0.1084289848320736</v>
+        <v>-0.109593675106737</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-0.04220310674622141</v>
+        <v>-0.04338279270334766</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>0.1897348501243599</v>
+        <v>0.18848231154508</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>0.1885585780258126</v>
+        <v>0.1873122525828848</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>0.1181215383852958</v>
+        <v>0.1168911150540097</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>0.1610669136226335</v>
+        <v>0.1598144267492856</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>0.1928165943456221</v>
+        <v>0.1915538666038614</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>0.2448888872239934</v>
+        <v>0.2435932741148861</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>0.3160087772858873</v>
+        <v>0.3146894623607608</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>0.4957927734697165</v>
+        <v>0.4944266208442443</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>0.5345765246654537</v>
+        <v>0.5331903426277336</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>0.6424261502701114</v>
+        <v>0.6432175810554526</v>
       </c>
     </row>
     <row r="30">
@@ -5156,257 +5156,257 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3874</v>
+        <v>3875</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-0.0108038977762277</v>
+        <v>-0.01178022806521994</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>0.0123323797439383</v>
+        <v>0.01131953835191268</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-0.05972619961637804</v>
+        <v>-0.06072837196619219</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>0.08454345061217339</v>
+        <v>0.08350607538958599</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>0.2554846282667</v>
+        <v>0.2543926691631313</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>0.309537471018551</v>
+        <v>0.308436626840205</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>0.2389547829283245</v>
+        <v>0.2378700080467482</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>0.198300841694433</v>
+        <v>0.1972172736275795</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>0.3062519286346514</v>
+        <v>0.3051388697246296</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>0.3987594861841899</v>
+        <v>0.3976061171992313</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>0.4149172808910961</v>
+        <v>0.4137553586196248</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>0.567126372079926</v>
+        <v>0.5659252830567212</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>0.6518552825571788</v>
+        <v>0.6506238859180016</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>0.7098667875315243</v>
+        <v>0.7105018178449853</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X &lt; 0.5783</t>
+          <t>X &lt; 0.5782</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>3905</v>
+        <v>3906</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>0.05888429336838641</v>
+        <v>0.05799695747279543</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>0.1456901347348847</v>
+        <v>0.1447534149418956</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>0.09664642866636086</v>
+        <v>0.0957152075007528</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>0.1897594660167599</v>
+        <v>0.1888061806896815</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>0.3806584826699719</v>
+        <v>0.3796470118967861</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>0.462227358081762</v>
+        <v>0.4611995251623711</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>0.4426963080238409</v>
+        <v>0.4416715741285984</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>0.4498514509988709</v>
+        <v>0.4488166179240736</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>0.5053764689985627</v>
+        <v>0.5043259366018233</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>0.4625495444607211</v>
+        <v>0.4614952863037729</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>0.4769712965290793</v>
+        <v>0.4759094360841161</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>0.6282613833837658</v>
+        <v>0.6271608879375066</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>0.7089981397000358</v>
+        <v>0.7078694479176733</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>0.6917215902578562</v>
+        <v>0.692273451229525</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>X &lt; 0.6146</t>
+          <t>X &lt; 0.6145</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>3941</v>
+        <v>3942</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>0.1115186853540138</v>
+        <v>0.1107401009447813</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>0.1828706876201025</v>
+        <v>0.1820506331038985</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>0.02947158694983187</v>
+        <v>0.02868429584612642</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>0.1229060286503909</v>
+        <v>0.1220965745063936</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>0.3577740625746344</v>
+        <v>0.3568970606259043</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>0.4666279584530741</v>
+        <v>0.4657272510150463</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>0.4465034698391008</v>
+        <v>0.4456062285782565</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>0.4493332060896762</v>
+        <v>0.44842813202456</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>0.4784528984949716</v>
+        <v>0.477539152857581</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>0.4029036264417627</v>
+        <v>0.401996399153326</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>0.4153096714442128</v>
+        <v>0.4143959355048707</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>0.5401553476756646</v>
+        <v>0.5392100262318777</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>0.6923979905324984</v>
+        <v>0.6914075819664589</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>0.7283047254325368</v>
+        <v>0.7287470184145448</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X &lt; 0.651</t>
+          <t>X &lt; 0.6509</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>3963</v>
+        <v>3964</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>0.07195403391477839</v>
+        <v>0.07125897575179607</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>0.1088245448131886</v>
+        <v>0.1080990836452784</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>0.004397165966466332</v>
+        <v>0.003692529382625764</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>0.09802917544428169</v>
+        <v>0.0973023146513512</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>0.2782554066668297</v>
+        <v>0.2774758752428923</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>0.4133166604562462</v>
+        <v>0.4125066052287139</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>0.3676317903993294</v>
+        <v>0.3668317711434739</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>0.317445865110443</v>
+        <v>0.3166520709382539</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>0.4216375035666644</v>
+        <v>0.4208162976259118</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>0.341778303235067</v>
+        <v>0.3409658332883438</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>0.3781786418713509</v>
+        <v>0.3773539640822037</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>0.5529543795290124</v>
+        <v>0.552085696610618</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>0.7020229203293837</v>
+        <v>0.7011107960201954</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>0.7138856345562203</v>
+        <v>0.7142712263928885</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X &lt; 0.6873</t>
+          <t>X &lt; 0.6872</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>3979</v>
+        <v>3980</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>0.03662180003050963</v>
+        <v>0.03598855248593225</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>0.06687481200241052</v>
+        <v>0.06621450966835596</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-0.01366510092370277</v>
+        <v>-0.01431024100168088</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>0.1051782085548965</v>
+        <v>0.1045045174406525</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>0.3326734442640102</v>
+        <v>0.3319359853733417</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>0.3931554427186938</v>
+        <v>0.3924060215037173</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>0.3222209633358446</v>
+        <v>0.321487979746891</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>0.2954434770926397</v>
+        <v>0.2947112983854581</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>0.4240665746898742</v>
+        <v>0.4233010500658594</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>0.3913271768478452</v>
+        <v>0.3905593687204032</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>0.3765449665806457</v>
+        <v>0.3757780706693055</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>0.5758753601136419</v>
+        <v>0.5750584638767364</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>0.7226609236659414</v>
+        <v>0.7218017641211958</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>0.7354852804894421</v>
+        <v>0.7358219669777455</v>
       </c>
     </row>
     <row r="35">
@@ -5416,49 +5416,49 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>3997</v>
+        <v>3998</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>0.05020257754563318</v>
+        <v>0.04962498168205087</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>0.09803121973173035</v>
+        <v>0.09742406094046885</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>-0.008862675698971145</v>
+        <v>-0.009447716385146521</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>0.08507676036849432</v>
+        <v>0.08446939970620093</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>0.2592004040750453</v>
+        <v>0.2585434896762564</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>0.3456978347061366</v>
+        <v>0.3450222325933083</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>0.3745895681379636</v>
+        <v>0.3739055277892689</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>0.2958822947798723</v>
+        <v>0.295212553277068</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>0.4486401312850745</v>
+        <v>0.4479312599680227</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>0.4372233101456757</v>
+        <v>0.4365077800568926</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>0.4465977038985827</v>
+        <v>0.4458772920351848</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>0.5951906636946234</v>
+        <v>0.5944331499641251</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>0.7394281012245685</v>
+        <v>0.7386296334849192</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>0.7783422535786428</v>
+        <v>0.7786197477776966</v>
       </c>
     </row>
   </sheetData>

--- a/workspaces/btc_daily_14days/ma/ma_ratio_100.xlsx
+++ b/workspaces/btc_daily_14days/ma/ma_ratio_100.xlsx
@@ -572,49 +572,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>13.38384268776593</v>
+        <v>12.56461045224136</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-6.345804616093709</v>
+        <v>-7.559050953629189</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>6.857312608250965</v>
+        <v>5.961148826864942</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>11.52319753008707</v>
+        <v>10.73193959782937</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>15.52412192815257</v>
+        <v>14.88707859321085</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>6.752300741656377</v>
+        <v>5.879512529886185</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>11.20679867955565</v>
+        <v>10.46334325910247</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>1.666114378723265</v>
+        <v>0.7125643212758135</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>8.41542632685816</v>
+        <v>7.644001371853605</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>7.568374112956121</v>
+        <v>6.822813733100951</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>5.094746951385254</v>
+        <v>4.296738151585146</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>14.21678469882024</v>
+        <v>13.65367339408488</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>4.711743070446815</v>
+        <v>3.962100390579771</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>7.211381583240879</v>
+        <v>6.537714380863569</v>
       </c>
     </row>
     <row r="7">
@@ -627,46 +627,46 @@
         <v>78</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-1.195692956790559</v>
+        <v>-1.224792568978913</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-4.07949496273104</v>
+        <v>-4.080713394881187</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-8.310045195526861</v>
+        <v>-8.310261328024794</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-8.1821283996753</v>
+        <v>-8.182678707167724</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-10.00047794391597</v>
+        <v>-9.952112979822708</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-9.706004555431477</v>
+        <v>-9.682154217157233</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-13.63242201116286</v>
+        <v>-13.58456879529306</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-15.38217291545289</v>
+        <v>-15.33307154576692</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-10.32530112158189</v>
+        <v>-10.25218059780365</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-11.17709328506895</v>
+        <v>-11.07788548867331</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-12.6655236362932</v>
+        <v>-12.56572403965139</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-17.75994886523129</v>
+        <v>-17.63634491354053</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-16.90276405394299</v>
+        <v>-16.75412727379662</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-17.9634435915837</v>
+        <v>-17.79144483201762</v>
       </c>
     </row>
     <row r="8">
@@ -679,46 +679,46 @@
         <v>92</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-6.806152993593273</v>
+        <v>-6.835304401917988</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-2.995409953349963</v>
+        <v>-2.996621501636575</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-2.306398271313086</v>
+        <v>-2.306569749738031</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-3.261094087599304</v>
+        <v>-3.261611977733892</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-4.883425143362786</v>
+        <v>-4.835036017034433</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-4.587732360417178</v>
+        <v>-4.563858077821187</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-9.013346212760055</v>
+        <v>-8.965478507345999</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-9.481885016589288</v>
+        <v>-9.432766176181346</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-11.71640265897564</v>
+        <v>-11.64329528696921</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-13.65445486792552</v>
+        <v>-13.55526237510041</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-8.432101792652468</v>
+        <v>-8.332298588305854</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-12.74546890988811</v>
+        <v>-12.62186261076684</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-8.822206242128054</v>
+        <v>-8.673566205153406</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-7.511938574862377</v>
+        <v>-7.339939815294727</v>
       </c>
     </row>
     <row r="9">
@@ -728,1349 +728,1349 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-3.346506821168667</v>
+        <v>-3.824282777495711</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-7.575615785410676</v>
+        <v>-8.048872459862267</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-7.097162681672117</v>
+        <v>-7.561763647191732</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-4.344615635741953</v>
+        <v>-4.786427717047523</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-2.257639231868666</v>
+        <v>-2.627410529299837</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-3.711896705076157</v>
+        <v>-4.12179792548482</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-3.797335515503853</v>
+        <v>-4.183341268972484</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-2.513015328866274</v>
+        <v>-2.882381096078142</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>1.805337435330252</v>
+        <v>1.498629446095507</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-0.7958031666174179</v>
+        <v>-1.092051865735513</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-1.877202831095843</v>
+        <v>-2.180726478153794</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-1.84332232129767</v>
+        <v>-2.123149684560602</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-1.387025149450594</v>
+        <v>-1.634176132417345</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-1.161824158385905</v>
+        <v>-1.385726656388755</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X ≈ -0.1667</t>
+          <t>X ≈ -0.1668</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-5.059498495507881</v>
+        <v>-4.8931729361911</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-6.018285663035627</v>
+        <v>-5.930948311415207</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-3.824847932165433</v>
+        <v>-3.115150440036956</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-2.401173939562504</v>
+        <v>-1.044294901300837</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-0.3482152622740529</v>
+        <v>0.08918881146541224</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-0.6991947021902192</v>
+        <v>0.7212004692873037</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-2.728015054557851</v>
+        <v>-1.56955104726633</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-3.195016549980465</v>
+        <v>-1.69461860265212</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-3.257098739075282</v>
+        <v>-2.016728044524349</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-2.809818779266472</v>
+        <v>-1.848329131282227</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-1.068916744488185</v>
+        <v>-0.4002596235588953</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>0.2631185930864888</v>
+        <v>0.6672685338207174</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-0.1569856379552022</v>
+        <v>0.2722654915380289</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>2.665927037786339</v>
+        <v>2.456694125799039</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X ≈ -0.1303</t>
+          <t>X ≈ -0.1305</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>200</v>
+        <v>207</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-1.116400896557721</v>
+        <v>-0.8725641496581176</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>2.442008839256516</v>
+        <v>2.819329075309682</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>3.814407369423897</v>
+        <v>3.171825450727709</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>1.228748763476453</v>
+        <v>0.187465446997976</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>3.4501785937777</v>
+        <v>2.110116051838148</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>1.028374069510448</v>
+        <v>-0.03118844676947674</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-2.78345243033975</v>
+        <v>-4.442134678540477</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-2.483397041329567</v>
+        <v>-4.43035133057117</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>1.452856801429078</v>
+        <v>-0.6020420722822593</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>2.589853964677467</v>
+        <v>0.4982829780308862</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>3.884671365895308</v>
+        <v>2.225688328390085</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>5.201212570089062</v>
+        <v>3.248943504816928</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>3.562674392186651</v>
+        <v>1.192933887216618</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>1.575017946877239</v>
+        <v>-0.6974277380005347</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X ≈ -0.09402</t>
+          <t>X ≈ -0.09416</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-2.510991976318358</v>
+        <v>-2.344074953250654</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-3.074184151049373</v>
+        <v>-3.389063557930086</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-3.469277203673762</v>
+        <v>-3.430688870188526</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-2.270793065983547</v>
+        <v>-2.244466800804759</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-0.3205527591870734</v>
+        <v>-0.2689272093623032</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-0.02350039742141519</v>
+        <v>-0.3482543665998818</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>0.5980646617754317</v>
+        <v>0.6474275723437586</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>2.260115645197168</v>
+        <v>2.646383544354784</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>0.6210187064219213</v>
+        <v>0.8488475549362988</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>0.322329698612819</v>
+        <v>0.3771316501776525</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>0.6745567769683163</v>
+        <v>0.5251038786978981</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>1.064806815444555</v>
+        <v>0.935383292119127</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-0.06708781011085563</v>
+        <v>-0.1639999865573714</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>0.1586478401157621</v>
+        <v>0.08504487545799577</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X ≈ -0.05768</t>
+          <t>X ≈ -0.05788</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>2.190364246282336</v>
+        <v>2.350999286224045</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-0.1128633692730077</v>
+        <v>0.4205999788460488</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-2.237738560256254</v>
+        <v>-2.056471342801984</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-2.107513416668048</v>
+        <v>-2.273809523809526</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-2.299782208517996</v>
+        <v>-2.415836442539302</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-1.310366656391636</v>
+        <v>-1.448606479275774</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-0.01099397067494579</v>
+        <v>-0.1203736796124275</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-2.208166420690134</v>
+        <v>-2.669539773329099</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-4.345273144686885</v>
+        <v>-4.442623493577088</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-5.195191941016816</v>
+        <v>-5.266452074391992</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-4.707851576785743</v>
+        <v>-5.123370299705861</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-6.057556469413115</v>
+        <v>-6.454092451229933</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-6.477707322726445</v>
+        <v>-6.84925037779368</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-7.636054717482693</v>
+        <v>-7.989094404667277</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X ≈ -0.02134</t>
+          <t>X ≈ -0.02159</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-5.772452080691018</v>
+        <v>-5.506957250754489</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-2.681443816388082</v>
+        <v>-2.673730550421382</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-2.762735577318736</v>
+        <v>-2.752011125486881</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-3.259469681379279</v>
+        <v>-2.937584497521406</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-6.932555472719486</v>
+        <v>-6.581407770965441</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-7.575620314557682</v>
+        <v>-7.254994491894152</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-8.600769545297346</v>
+        <v>-8.262022820867244</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-7.186960446137377</v>
+        <v>-6.519653688506182</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-6.307503731186799</v>
+        <v>-5.925711471144481</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-8.09786139898987</v>
+        <v>-8.011369704956309</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-8.929521804899032</v>
+        <v>-8.530967565741612</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-8.895143652543645</v>
+        <v>-8.472800828376648</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-8.061376010559322</v>
+        <v>-7.606129101943701</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-5.641282993561624</v>
+        <v>-5.148882347183701</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X ≈ 0.01499</t>
+          <t>X ≈ 0.0147</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>0.2174966678782724</v>
+        <v>-0.1441812255178263</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-1.393689425185478</v>
+        <v>-1.411900897424466</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>0.4337614122817044</v>
+        <v>0.4025630070053055</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>0.8814468733303826</v>
+        <v>0.8479044614691276</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>1.612998590075954</v>
+        <v>1.620484973514124</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>1.275451984790408</v>
+        <v>1.262355665834555</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>2.143122577905189</v>
+        <v>2.148071816356733</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-0.5461682881036296</v>
+        <v>-0.8414202500202279</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-1.242071079547038</v>
+        <v>-1.509307685655521</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-0.8221486060359098</v>
+        <v>-0.7558492002243824</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-1.979230716676916</v>
+        <v>-1.90636188750824</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-2.262312881781909</v>
+        <v>-2.163652563392496</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-1.095162147793729</v>
+        <v>-0.9815234237102644</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-1.186886815027442</v>
+        <v>-1.047935974944103</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X ≈ 0.05133</t>
+          <t>X ≈ 0.051</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-0.2624859964046564</v>
+        <v>-0.7977830577637022</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-4.262750587761929</v>
+        <v>-4.778220416892232</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-3.633631187534029</v>
+        <v>-3.802095391508225</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-5.209890685583972</v>
+        <v>-5.042074363992093</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-3.359101740386073</v>
+        <v>-3.476528984396147</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-4.085618495734082</v>
+        <v>-4.231140725851191</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-2.805141141689589</v>
+        <v>-2.921933801378032</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-2.930912857148755</v>
+        <v>-3.045300808336712</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-3.674488870326826</v>
+        <v>-3.767204924322819</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-2.135329168362929</v>
+        <v>-2.193773231165352</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-2.681327254951007</v>
+        <v>-2.74037943212587</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-3.329542959250816</v>
+        <v>-3.367144201610373</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-4.090990740891947</v>
+        <v>-4.10476788159886</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-5.571739732303719</v>
+        <v>-5.568051786706853</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X ≈ 0.08765</t>
+          <t>X ≈ 0.08727</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-2.688384910202402</v>
+        <v>-1.260111824886934</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>1.509557627439122</v>
+        <v>2.573377756623827</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>1.114786242683984</v>
+        <v>1.762973101642359</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-5.393992763105153</v>
+        <v>-5.190476190476339</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-2.197842482176007</v>
+        <v>-2.346391998094823</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>0.1742203441397265</v>
+        <v>0.009726854057475975</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>0.5044477442096564</v>
+        <v>0.365737431498637</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>1.282192378431169</v>
+        <v>1.149904671115344</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>2.880961259252842</v>
+        <v>2.779598728645219</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>2.860917981595087</v>
+        <v>2.789103481163657</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>1.826341304662876</v>
+        <v>1.751629700294188</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>4.350346013034567</v>
+        <v>3.893129770992367</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>3.930195159721251</v>
+        <v>3.497971844428541</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>4.570868569283938</v>
+        <v>4.163683373110572</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X ≈ 0.124</t>
+          <t>X ≈ 0.1235</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>1.923229047185792</v>
+        <v>1.098135597793373</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>0.830177669147929</v>
+        <v>0.03042243016334822</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>3.544214574548398</v>
+        <v>2.214004029477508</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>3.67443971813676</v>
+        <v>2.343888070692245</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-4.635870560347598</v>
+        <v>-4.846391998094845</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-4.856631245738356</v>
+        <v>-4.573606479275853</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-4.4232068899788</v>
+        <v>-4.118798650975485</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-2.29960195863589</v>
+        <v>-1.491847906204242</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-1.324314685106913</v>
+        <v>-0.4978926802894961</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-1.656098766410864</v>
+        <v>-0.8062573435787002</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-0.3063957795933945</v>
+        <v>0.5359939614624096</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>0.7642518028137957</v>
+        <v>2.140552451404673</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>1.380370379552261</v>
+        <v>2.776322359892461</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>0.5698365997269192</v>
+        <v>1.994439386856286</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X ≈ 0.1603</t>
+          <t>X ≈ 0.1598</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>1.97917786617937</v>
+        <v>1.69549565174848</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>3.654376749641202</v>
+        <v>3.383346603975909</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-0.4962631797147239</v>
+        <v>-0.2814194217219779</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>1.981379804249286</v>
+        <v>2.184913217623553</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>4.259991659604232</v>
+        <v>4.499402394428586</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>4.557365689239319</v>
+        <v>4.304898193621341</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>9.167491010724383</v>
+        <v>8.91713930065756</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>11.51732377538828</v>
+        <v>10.78775513840507</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>13.80375945924111</v>
+        <v>13.0872311273991</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>13.89280779906147</v>
+        <v>13.19798198583646</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>13.21862307272622</v>
+        <v>12.52655181867426</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>12.31403408893132</v>
+        <v>11.65013911678681</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>11.89388323561785</v>
+        <v>11.25498119022294</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>11.65013531776928</v>
+        <v>11.03673633261213</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X ≈ 0.1966</t>
+          <t>X ≈ 0.1961</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>0.495274445656122</v>
+        <v>0.1844989535562647</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>3.645993114497053</v>
+        <v>3.990543425286511</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>2.655983634503919</v>
+        <v>3.596805436971657</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>0.40525639713983</v>
+        <v>1.331479897348018</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>2.247919224996586</v>
+        <v>2.638637942024978</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>1.35481706415549</v>
+        <v>1.713818670424743</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>0.0796305144131324</v>
+        <v>0.4555577907801265</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>0.8030380611025123</v>
+        <v>1.187329820815876</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-5.805563143039315</v>
+        <v>-5.436469135626311</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-1.893577177464344</v>
+        <v>-1.469878554764584</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-4.479230716676909</v>
+        <v>-4.069228583138994</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-0.8734239928930876</v>
+        <v>-0.4182474745166189</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-0.1030986557302427</v>
+        <v>0.3841993893387254</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-1.067839195979964</v>
+        <v>-0.5643605390650777</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X ≈ 0.233</t>
+          <t>X ≈ 0.2324</t>
         </is>
       </c>
       <c r="B21" t="n">
         <v>164</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>4.836157140197251</v>
+        <v>4.806961345844655</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>6.883507632499381</v>
+        <v>7.492076943615629</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>4.659467955061409</v>
+        <v>4.049558467496148</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>9.057985781576569</v>
+        <v>7.837979094076715</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>9.129452326041893</v>
+        <v>8.568242148246647</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>8.207314160554986</v>
+        <v>8.84102766706561</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>8.122603801288889</v>
+        <v>8.78037157784015</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>9.484803450185147</v>
+        <v>10.14380711013977</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>8.20430909854035</v>
+        <v>8.88732230588105</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>7.964146399771437</v>
+        <v>8.673249822626985</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>5.320420851267336</v>
+        <v>6.030084984846987</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>5.354799003622723</v>
+        <v>6.088251722211879</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>3.105379857626353</v>
+        <v>3.863825502965128</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>6.379895995657797</v>
+        <v>5.942138657663456</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X ≈ 0.2693</t>
+          <t>X ≈ 0.2687</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-0.6952017448200323</v>
+        <v>0.1526100686041403</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>1.860278828782803</v>
+        <v>0.9362968887737324</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>2.655983634503919</v>
+        <v>3.501138782115859</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>1.595732587616126</v>
+        <v>3.039306846999153</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>1.652681129758491</v>
+        <v>3.14177368237862</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>3.73576944510787</v>
+        <v>4.006275177528877</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>4.841535276317856</v>
+        <v>5.129051040966147</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>1.398276156340643</v>
+        <v>1.704638398926029</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>1.932532095056025</v>
+        <v>2.259381766120562</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>0.4873752034880354</v>
+        <v>0.8438372089742145</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-0.3125640500102449</v>
+        <v>0.04798078510675907</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>0.9122902928212611</v>
+        <v>1.289579475134417</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>3.468329915698298</v>
+        <v>3.853001430227359</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>1.31311318497248</v>
+        <v>2.918614339579975</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X ≈ 0.3057</t>
+          <t>X ≈ 0.305</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-0.5941235777041669</v>
+        <v>-1.584185898961053</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-3.148705897183142</v>
+        <v>-3.167362984116906</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>1.173503850137401</v>
+        <v>0.1426027312721416</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-2.469855911934673</v>
+        <v>-3.43121693121693</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-3.008145465030367</v>
+        <v>-3.92046607216885</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>2.949605923095341</v>
+        <v>1.907875002205621</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>0.97810311099893</v>
+        <v>-0.004632938871687031</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-2.319154212033091</v>
+        <v>-3.248243477032808</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>2.336844763519608</v>
+        <v>1.344413543460021</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-0.3998664856404446</v>
+        <v>-1.331266889206809</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>4.112413488174838</v>
+        <v>3.094222292886727</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>2.259999187699968</v>
+        <v>1.300537178399715</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>4.670037013631841</v>
+        <v>3.683157029613724</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>9.612753795933848</v>
+        <v>8.561831521258718</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X ≈ 0.3421</t>
+          <t>X ≈ 0.3413</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>0.4602604400538866</v>
+        <v>0.501936367884106</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>4.731427288166529</v>
+        <v>3.738036391162048</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-3.89863821423571</v>
+        <v>-3.884617259803328</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>4.466881046999852</v>
+        <v>4.679001721170458</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>1.575650317433634</v>
+        <v>1.780114026001677</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>1.87302434706865</v>
+        <v>2.052899544820541</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-2.917568365138685</v>
+        <v>-2.827033652838729</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>3.674186520486401</v>
+        <v>3.936049249428663</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>1.260263187493038</v>
+        <v>1.489438086075005</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>7.46916792057494</v>
+        <v>6.689705890802124</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>4.911525585844096</v>
+        <v>4.075926889049164</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>10.82825667937588</v>
+        <v>10.15819001195629</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>6.878694061356526</v>
+        <v>6.1485742540671</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>7.104429711583123</v>
+        <v>6.397619116082531</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X ≈ 0.3784</t>
+          <t>X ≈ 0.3776</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>6.555228547778903</v>
+        <v>6.313417586877726</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>10.96813884025724</v>
+        <v>11.78906403113357</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>10.57336745550227</v>
+        <v>10.21885545458358</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>9.498773321982121</v>
+        <v>9.172268907562952</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>8.960483768886363</v>
+        <v>8.683019766611032</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>10.46267707562995</v>
+        <v>10.13227587366532</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>10.37796671636376</v>
+        <v>10.0716197844399</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>9.910898072576977</v>
+        <v>9.605787024056461</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>7.440277361837339</v>
+        <v>7.21587323844907</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>6.590358565507479</v>
+        <v>7.568515245869442</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>10.00011523857266</v>
+        <v>10.89378656303923</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>7.624854836711101</v>
+        <v>8.599012123933484</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>8.409523260506205</v>
+        <v>9.380324785605005</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>8.635258910732638</v>
+        <v>9.629369647620273</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X ≈ 0.4147</t>
+          <t>X ≈ 0.4139</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>2.280988731370336</v>
+        <v>3.587449150722776</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>0.669802638306507</v>
+        <v>2.004272065566923</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>0.2750312535515462</v>
+        <v>1.610534077252218</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>5.167161159044667</v>
+        <v>6.618466898954701</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>7.009823986901353</v>
+        <v>8.568242148246682</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>9.688150397488826</v>
+        <v>11.28005205730952</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>16.74629718107987</v>
+        <v>18.53646913881583</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>16.27922853729306</v>
+        <v>18.07063637843242</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>16.21824638077028</v>
+        <v>18.03366376929562</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>10.60642282253565</v>
+        <v>12.33178640799284</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>12.78267404522778</v>
+        <v>14.56667035070058</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>10.43609981663078</v>
+        <v>12.18581269782164</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>14.77785372522222</v>
+        <v>16.66870355174569</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>10.24168461354397</v>
+        <v>12.03969963327325</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X ≈ 0.4511</t>
+          <t>X ≈ 0.4502</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>14.960944434582</v>
+        <v>13.39897908420392</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>13.34975834151817</v>
+        <v>11.81580199904807</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>12.95498695676306</v>
+        <v>11.42206401073337</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>15.4107934957002</v>
+        <v>13.82467532467525</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>17.19808533795339</v>
+        <v>15.60815345645067</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>12.84429657689081</v>
+        <v>11.33548442981505</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>8.108423426926969</v>
+        <v>6.729373795135054</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>5.315773387791388</v>
+        <v>3.990813762024437</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>7.580372626617454</v>
+        <v>6.226568425614914</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>9.056035225636435</v>
+        <v>7.675467117527198</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>18.15365964877165</v>
+        <v>16.56223576090026</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>15.86245640577814</v>
+        <v>14.34767522553788</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>13.11672415711577</v>
+        <v>11.67979002624666</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>11.01687841199352</v>
+        <v>9.656107615534815</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X ≈ 0.4873</t>
+          <t>X ≈ 0.4866</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>10.85241730279898</v>
+        <v>11.28299162338888</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>5.907897876401819</v>
+        <v>6.25153867616406</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-1.153540175019884</v>
+        <v>-1.038751036288581</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>3.976684968568478</v>
+        <v>4.263546798029651</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>3.438395415472826</v>
+        <v>2.050159726043098</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>0.402436111774584</v>
+        <v>-1.125330617206934</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-3.015607580824962</v>
+        <v>-4.634262568501313</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>3.183990442055006</v>
+        <v>1.796456395253223</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-0.2103250478011418</v>
+        <v>-1.688792075952492</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>2.273089489202327</v>
+        <v>0.9356552053015008</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>3.735054997608749</v>
+        <v>2.45565268879988</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>3.769433149964073</v>
+        <v>4.237957357199164</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>8.349282296650713</v>
+        <v>7.291075292704406</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>6.908351280210574</v>
+        <v>7.540120154719723</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X ≈ 0.5237</t>
+          <t>X ≈ 0.5229</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-2.480916030534353</v>
+        <v>-3.530519988152292</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-4.092102123598181</v>
+        <v>-5.113697073308117</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>3.84645982498008</v>
+        <v>2.655830244499597</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>10.2266849685685</v>
+        <v>8.908163265306058</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>5.521728748806055</v>
+        <v>6.378097797823642</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>9.985769445107806</v>
+        <v>10.7325159697038</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>9.901059085841709</v>
+        <v>10.67185988047828</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>3.183990442054878</v>
+        <v>4.083578140503157</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>9.373008285532151</v>
+        <v>10.16905451095814</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>12.68975615586899</v>
+        <v>13.42685858320438</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>8.318388330942199</v>
+        <v>9.141085482607068</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>6.269433149964122</v>
+        <v>5.11761956691079</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>10.01594896331737</v>
+        <v>10.84491061993874</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>6.075017946877246</v>
+        <v>4.971506502362331</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X ≈ 0.5601</t>
+          <t>X ≈ 0.5592</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>8.809406550110808</v>
+        <v>9.989888175113016</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>16.87563981188573</v>
+        <v>17.78171108995716</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>19.70667487874365</v>
+        <v>20.5129731016425</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>13.38528711910616</v>
+        <v>14.39285714285714</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>16.07280401762332</v>
+        <v>17.02860800190522</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>19.5959844988713</v>
+        <v>20.42639352072415</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>25.96288704283094</v>
+        <v>26.61573743149869</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>31.94743130227005</v>
+        <v>32.39990467111534</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>25.43483624252148</v>
+        <v>26.11293206197855</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>8.455885188127056</v>
+        <v>9.664103481163565</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>8.25118402986682</v>
+        <v>9.459963033627432</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>8.285562182222186</v>
+        <v>9.518129770992367</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>7.865411328908777</v>
+        <v>9.122971844428541</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-1.586272375703402</v>
+        <v>-0.002983293556091837</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X ≈ 0.5964</t>
+          <t>X ≈ 0.5955</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>5.852417302799019</v>
+        <v>3.372241116289487</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>4.241231209735112</v>
+        <v>1.789064031133634</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-7.264651286131077</v>
+        <v>-10.36937983953406</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-7.134426142542637</v>
+        <v>-7.298319327731136</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-2.117160140082817</v>
+        <v>-4.846391998094781</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>0.9579916673300914</v>
+        <v>-1.632430008687571</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>0.8732813080639232</v>
+        <v>1.248090372675158</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>0.4062126642771844</v>
+        <v>3.723434082880054</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-2.43254727002337</v>
+        <v>0.7452850031550611</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>-6.060243844131008</v>
+        <v>-3.019720048248246</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>-6.264945002391158</v>
+        <v>-3.223860495784244</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>-9.008344627813656</v>
+        <v>-6.106870229007676</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>-1.095162147793729</v>
+        <v>-0.6196752143949453</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>4.68612905798836</v>
+        <v>5.51172258879685</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>X ≈ 0.6327</t>
+          <t>X ≈ 0.6317</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>-7.026370575988963</v>
+        <v>-2.510111824886984</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>-13.18301121450727</v>
+        <v>-8.259955576709558</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-4.486873508353156</v>
+        <v>-0.3203602316908771</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-4.356648364764794</v>
+        <v>-4.35714285714274</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-13.98584700876958</v>
+        <v>-9.013058664761452</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-9.143018433680012</v>
+        <v>-4.573606479275917</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>-13.77318333840072</v>
+        <v>-12.96759590183464</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>-23.33116107309656</v>
+        <v>-25.93342866221799</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-9.755779593255696</v>
+        <v>-13.47040127135485</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>-10.60569838958556</v>
+        <v>-14.29422985216971</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>-6.264945002391201</v>
+        <v>-10.3317036330392</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>2.860342240873216</v>
+        <v>-1.940203562340905</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>2.440191387559807</v>
+        <v>1.831305177761813</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>-1.879527507668215</v>
+        <v>-2.086316626889428</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X ≈ 0.6691</t>
+          <t>X ≈ 0.668</t>
         </is>
       </c>
       <c r="B33" t="n">
         <v>16</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>-8.730916030534353</v>
+        <v>-8.760111824886984</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>-10.34210212359818</v>
+        <v>-10.34328891004284</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>-4.486873508353263</v>
+        <v>-4.487026898357584</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>1.893351635235007</v>
+        <v>1.892857142857004</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>13.85506208213945</v>
+        <v>13.90360800190522</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-4.597563888225466</v>
+        <v>-4.573606479275853</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>-10.93227424749163</v>
+        <v>-10.88426256850131</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-5.149342891278373</v>
+        <v>-5.100095328884656</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>1.039674952198851</v>
+        <v>1.112932061978547</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>12.68975615586899</v>
+        <v>12.78910348116356</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>-0.014945002391201</v>
+        <v>0.08496303362747426</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>6.269433149964122</v>
+        <v>6.393129770992367</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>5.849282296650713</v>
+        <v>5.997971844428541</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>6.075017946877246</v>
+        <v>6.247016706443908</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X ≈ 0.7054</t>
+          <t>X ≈ 0.7043</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>3.074639525021205</v>
+        <v>6.313417586877726</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>7.019008987512933</v>
+        <v>10.61259344289834</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>1.068682047202373</v>
+        <v>4.336502513407211</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-4.356648364764816</v>
+        <v>-7.298319327731015</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-16.00604902897166</v>
+        <v>-13.66992140985949</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-10.15311944378102</v>
+        <v>-7.514782949864092</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>11.98439241917499</v>
+        <v>15.95397272561634</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>0.4062126642771844</v>
+        <v>3.723434082880054</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>5.900786063309923</v>
+        <v>3.686461473743257</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>10.60642282253562</v>
+        <v>8.744985834104739</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>15.95727721983101</v>
+        <v>14.42319832774513</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>4.880544261075194</v>
+        <v>8.599012123933583</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>4.460393407761828</v>
+        <v>8.203854197369743</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>10.2416846135439</v>
+        <v>14.33525200056156</v>
       </c>
     </row>
   </sheetData>
@@ -2210,105 +2210,105 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X &gt; -0.3302</t>
+          <t>X &gt; -0.3301</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3998</v>
+        <v>4008</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-0.0999636495819658</v>
+        <v>-0.1102113026288336</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-0.07713953008196484</v>
+        <v>-0.08831378566473091</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-0.1341670977770164</v>
+        <v>-0.1451508097783005</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-0.04028109929580381</v>
+        <v>-0.05151816824291444</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-0.06588875389748949</v>
+        <v>-0.07915276483613098</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-0.05437866605871733</v>
+        <v>-0.06663436772206666</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-0.1005014634716588</v>
+        <v>-0.1137146232958344</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-0.1293628712983548</v>
+        <v>-0.1424470976938181</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>0.02324977108468573</v>
+        <v>0.008708289239947931</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-0.08822985112750814</v>
+        <v>-0.1034688019869847</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-0.1039852423312198</v>
+        <v>-0.1191631194515566</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-0.005566850035876314</v>
+        <v>-0.02208219908244047</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>0.06346084128687579</v>
+        <v>0.04573936750163199</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>0.07826957269015367</v>
+        <v>0.05939195594491053</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X &gt; -0.2939</t>
+          <t>X &gt; -0.2938</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3954</v>
+        <v>3965</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-0.2500110645651006</v>
+        <v>-0.2476683859729505</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-0.007382002569443102</v>
+        <v>-0.00729444185073902</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-0.2119680859068112</v>
+        <v>-0.2113729748162996</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-0.1689591619394264</v>
+        <v>-0.1684636118598419</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-0.2393739511686519</v>
+        <v>-0.2414599397153196</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-0.1301232017035048</v>
+        <v>-0.1311196934716747</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-0.2263287791755531</v>
+        <v>-0.2284216822978848</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-0.1493428912783656</v>
+        <v>-0.1517196048856704</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-0.07013813191330343</v>
+        <v>-0.07409564583001327</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-0.1734323231608172</v>
+        <v>-0.1785835936663744</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-0.1618365869249345</v>
+        <v>-0.1670530954047891</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-0.1638327752128248</v>
+        <v>-0.1703943026148949</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>0.01173488830684732</v>
+        <v>0.003266851992833608</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-0.001107495712538764</v>
+        <v>-0.0108647563555877</v>
       </c>
     </row>
     <row r="8">
@@ -2318,49 +2318,49 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3876</v>
+        <v>3887</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-0.2309803144119584</v>
+        <v>-0.2280605428357063</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>0.07456454306848315</v>
+        <v>0.07444640670505009</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-0.04900368586801562</v>
+        <v>-0.04885347608971102</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-0.007703434245044605</v>
+        <v>-0.007643242054335531</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-0.04294306586569263</v>
+        <v>-0.04659733690380818</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>0.0625802930309689</v>
+        <v>0.06053986218756791</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>0.04345328276846772</v>
+        <v>0.03959464772877652</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>0.1572001277839661</v>
+        <v>0.1529229089781694</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>0.1362351171048033</v>
+        <v>0.1301468615674537</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>0.04800357854940529</v>
+        <v>0.04013149452774201</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>0.08978559827907873</v>
+        <v>0.08174966601821865</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>0.1902686321714455</v>
+        <v>0.1800930006143773</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>0.3521195419434591</v>
+        <v>0.3395356304367709</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>0.3603636641115031</v>
+        <v>0.3459361816175672</v>
       </c>
     </row>
     <row r="9">
@@ -2370,49 +2370,49 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3784</v>
+        <v>3795</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-0.07111882221199295</v>
+        <v>-0.06788493413068153</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>0.14920451496873</v>
+        <v>0.1488965378163698</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>0.005880114835186134</v>
+        <v>0.005879039635097172</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>0.07139591567793957</v>
+        <v>0.07124084850759971</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>0.07474307343920827</v>
+        <v>0.06948602503876344</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>0.1756428628293847</v>
+        <v>0.1726464789150484</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>0.263650310672439</v>
+        <v>0.2578994514881643</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>0.3915542063469601</v>
+        <v>0.3853032504365785</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>0.4244070714915367</v>
+        <v>0.4155636409259102</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>0.3811500312649727</v>
+        <v>0.3697168004581215</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>0.296977363597712</v>
+        <v>0.2857265933957791</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>0.5047738789657075</v>
+        <v>0.4904434396781667</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>0.5751739743257502</v>
+        <v>0.5580350688753271</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>0.5517621329237556</v>
+        <v>0.5322604482093851</v>
       </c>
     </row>
     <row r="10">
@@ -2422,1349 +2422,1349 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3670</v>
+        <v>3682</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>0.03062347530327969</v>
+        <v>0.04739832396280974</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>0.3891580610840535</v>
+        <v>0.4004847770172617</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>0.2265195913479516</v>
+        <v>0.2381288016153889</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>0.2085690265394859</v>
+        <v>0.2203219315895382</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>0.1471930960019066</v>
+        <v>0.1522533554679413</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>0.2964002227043849</v>
+        <v>0.3044423012119566</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>0.3897953744828087</v>
+        <v>0.3942004296011561</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>0.4817778921819169</v>
+        <v>0.4855879682953912</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>0.3815116868927291</v>
+        <v>0.3823245219731248</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>0.4177093404089973</v>
+        <v>0.4145782505612914</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>0.3645132061576675</v>
+        <v>0.3614216496383307</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>0.5777120170665242</v>
+        <v>0.5706542009597939</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>0.6361251187700248</v>
+        <v>0.6253136853191208</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>0.6049906989208438</v>
+        <v>0.5911231703222413</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X &gt; -0.1485</t>
+          <t>X &gt; -0.1486</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3516</v>
+        <v>3527</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>0.2535696594628192</v>
+        <v>0.2645201116928604</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>0.6698026383065852</v>
+        <v>0.6787303479577318</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>0.4039685670649789</v>
+        <v>0.3854943481013891</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>0.3228751746565806</v>
+        <v>0.2758976642512962</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>0.1688918693734891</v>
+        <v>0.155024833868957</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>0.3400070538857705</v>
+        <v>0.2861271563149685</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>0.5263547618753819</v>
+        <v>0.4805008205607493</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>0.642820652162861</v>
+        <v>0.5814008456690445</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>0.5408819956524198</v>
+        <v>0.4877549579830784</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>0.5590743376871714</v>
+        <v>0.5140255554055599</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>0.4272971118458031</v>
+        <v>0.3948950256932093</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>0.5914911374570124</v>
+        <v>0.5664083201564409</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>0.67086318945708</v>
+        <v>0.6408289872856798</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>0.5147221562060267</v>
+        <v>0.509137488978638</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X &gt; -0.1122</t>
+          <t>X &gt; -0.1123</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3316</v>
+        <v>3320</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>0.3361975578959004</v>
+        <v>0.3354166303975674</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>0.5629144476582155</v>
+        <v>0.5452653068246391</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>0.1982726199986971</v>
+        <v>0.2117682823653482</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>0.2682386493960394</v>
+        <v>0.2814113597246148</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-0.02901444693556954</v>
+        <v>0.03312607419437796</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>0.2984891397950236</v>
+        <v>0.3059115930133061</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>0.7259812511525325</v>
+        <v>0.7874241784866385</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>0.8313741921805047</v>
+        <v>0.8938805747297991</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>0.4858774838444191</v>
+        <v>0.5557031463158921</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>0.4365906448650776</v>
+        <v>0.5150070956213995</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>0.2187703172710442</v>
+        <v>0.2807461661575985</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>0.3134621005069462</v>
+        <v>0.3991538673779118</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>0.4964475559993247</v>
+        <v>0.6064055793682996</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>0.4507718672632564</v>
+        <v>0.5843661040342738</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X &gt; -0.07585</t>
+          <t>X &gt; -0.07603</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3035</v>
+        <v>3036</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>0.5998088459071695</v>
+        <v>0.5860673582487195</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>0.8996606441118686</v>
+        <v>0.9132987052404289</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>0.5378381885166377</v>
+        <v>0.5524987933420675</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>0.503318686305974</v>
+        <v>0.5176924524750603</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-0.002021937629912429</v>
+        <v>0.06138138793946979</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>0.3283010211649753</v>
+        <v>0.3671049831747482</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>0.7378245992958483</v>
+        <v>0.8005200401943426</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>0.6990920345865348</v>
+        <v>0.7299441968070468</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>0.4733652322647544</v>
+        <v>0.5282812055885557</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>0.4471696649299446</v>
+        <v>0.5279045351820102</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>0.1765706483501432</v>
+        <v>0.2578879348132403</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>0.2438977298652745</v>
+        <v>0.3489927485944762</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>0.54862331806752</v>
+        <v>0.6784725031900649</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>0.4778186058558234</v>
+        <v>0.6310746774584004</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X &gt; -0.03951</t>
+          <t>X &gt; -0.03973</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2746</v>
+        <v>2748</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>0.4324124472515152</v>
+        <v>0.4010963264958463</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>1.006222712527098</v>
+        <v>0.964935252984823</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>0.8299509636059952</v>
+        <v>0.8259279779161162</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>0.7780930773327412</v>
+        <v>0.8102516115616538</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>0.2398035242370469</v>
+        <v>0.3210024706097343</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>0.5007609478998134</v>
+        <v>0.557397887536375</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>0.8166332543291901</v>
+        <v>0.8970329191260475</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>1.005063518044281</v>
+        <v>1.08622199280385</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>0.9804979674938252</v>
+        <v>1.049249383667053</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>1.040994320472052</v>
+        <v>1.135173350159199</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>0.6906267383225639</v>
+        <v>0.8218625969462536</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>0.9070879205395102</v>
+        <v>1.061979843772576</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>1.288102398617205</v>
+        <v>1.467404158839024</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>1.331755018982129</v>
+        <v>1.534498511392968</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X &gt; -0.003174</t>
+          <t>X &gt; -0.00344</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2427</v>
+        <v>2431</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>1.247967364603674</v>
+        <v>1.171500680254937</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>1.490922186249371</v>
+        <v>1.439413681483281</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>1.302166458684269</v>
+        <v>1.292487704686472</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>1.308782207958672</v>
+        <v>1.298965740142208</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>1.182523969242865</v>
+        <v>1.221069951720111</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>1.56230426175393</v>
+        <v>1.576126141045009</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>2.054437742619612</v>
+        <v>2.09136474536129</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>2.081806676088753</v>
+        <v>2.078020672760765</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>1.938418256689999</v>
+        <v>1.958777393117998</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>2.242187140623827</v>
+        <v>2.327873534639501</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>1.955079719487657</v>
+        <v>2.04146241659744</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>2.195473529032931</v>
+        <v>2.305305830227255</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>2.516979041603328</v>
+        <v>2.650583938217103</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>2.248277114573987</v>
+        <v>2.406004777196678</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X &gt; 0.03316</t>
+          <t>X &gt; 0.03285</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2112</v>
+        <v>2114</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>1.401659727041405</v>
+        <v>1.368790729512263</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>1.921155452159397</v>
+        <v>1.866975990619409</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>1.431687097707389</v>
+        <v>1.42593431261691</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>1.372518301901806</v>
+        <v>1.366603595080413</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>1.118319657897025</v>
+        <v>1.161176592255259</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>1.60508762692605</v>
+        <v>1.623176869825379</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>2.041210600993217</v>
+        <v>2.08286136716567</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>2.473763169327682</v>
+        <v>2.51579871085044</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>2.412781012804906</v>
+        <v>2.478826101713643</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>2.699225852838694</v>
+        <v>2.790286073405753</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>2.541873179426979</v>
+        <v>2.633449315557471</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>2.860342240873216</v>
+        <v>2.975438191049129</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>3.055721690590104</v>
+        <v>3.19522823042665</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>2.760624007483301</v>
+        <v>2.923932505876259</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X &gt; 0.0695</t>
+          <t>X &gt; 0.06915</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1819</v>
+        <v>1822</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>1.669716184968671</v>
+        <v>1.716013312324868</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>2.917243670794335</v>
+        <v>2.93195807129635</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>2.247595980376843</v>
+        <v>2.263796372773079</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>2.432796385097703</v>
+        <v>2.393680413987759</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>1.839531570869511</v>
+        <v>1.90443127303584</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>2.521732428432045</v>
+        <v>2.561409986146764</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>2.821848897093304</v>
+        <v>2.884947091213284</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>3.344334953691387</v>
+        <v>3.40703968758077</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>3.393303319433592</v>
+        <v>3.479836562527396</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>3.477963962356064</v>
+        <v>3.589048596421527</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>3.383213326360867</v>
+        <v>3.494677632968859</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>3.8573935677761</v>
+        <v>3.991922306667448</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>4.206896370317565</v>
+        <v>4.365150768687599</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>4.102780453749155</v>
+        <v>4.284887178452692</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X &gt; 0.1058</t>
+          <t>X &gt; 0.1054</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1578</v>
+        <v>1582</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>2.335307036639286</v>
+        <v>2.167511436807068</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>3.132232477162269</v>
+        <v>2.986357107656275</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>2.420604311672136</v>
+        <v>2.339774618709463</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>3.628142509759861</v>
+        <v>3.544247787610622</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>2.456139395193944</v>
+        <v>2.549309645394466</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>2.880256137123084</v>
+        <v>2.948517414529455</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>3.175773914739032</v>
+        <v>3.26712807625217</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>3.659275613157625</v>
+        <v>3.749462193239239</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>3.471550744340796</v>
+        <v>3.586067333786382</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>3.572202290216261</v>
+        <v>3.710405630341818</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>3.620986556544153</v>
+        <v>3.759109683437835</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>3.78210742119353</v>
+        <v>4.006909796276815</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>4.249155553938422</v>
+        <v>4.496707621925381</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>4.031291711135793</v>
+        <v>4.303274607834553</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X &gt; 0.1422</t>
+          <t>X &gt; 0.1417</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1385</v>
+        <v>1388</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>2.392730178851934</v>
+        <v>2.316977512288808</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>3.453024230192426</v>
+        <v>3.399506479006156</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>2.264029018722589</v>
+        <v>2.357353505100676</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>3.621690985415647</v>
+        <v>3.712021407986818</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>3.44441226264486</v>
+        <v>3.583002814585335</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>3.958392790474896</v>
+        <v>3.999880552424436</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>4.234693261533643</v>
+        <v>4.299455010749412</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>4.489646278396719</v>
+        <v>4.482037235956838</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>4.139855457614011</v>
+        <v>4.156880188779702</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>4.300766986193906</v>
+        <v>4.341697141105925</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>4.168267993998697</v>
+        <v>4.209602803079932</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>4.20264614635402</v>
+        <v>4.267769540444824</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>4.648921285820393</v>
+        <v>4.737164928002024</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>4.51364610572201</v>
+        <v>4.625979242466961</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X &gt; 0.1785</t>
+          <t>X &gt; 0.178</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1172</v>
+        <v>1174</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>2.467889430216495</v>
+        <v>2.430262962165834</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>3.416430299610013</v>
+        <v>3.402452146175214</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>2.76568621860924</v>
+        <v>2.838356406582825</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>3.919802147180526</v>
+        <v>3.990386955463606</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>3.29618836200293</v>
+        <v>3.415958938872855</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>3.849535087883744</v>
+        <v>3.944281084608299</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>3.338203568208023</v>
+        <v>3.457730617188638</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>3.212431852748935</v>
+        <v>3.332613359360657</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>2.383531607488948</v>
+        <v>2.529030869474283</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>2.557503596142027</v>
+        <v>2.727348796325401</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>2.52345090204566</v>
+        <v>2.693566100066995</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>2.728477518564802</v>
+        <v>2.922090588709573</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>3.332217450234332</v>
+        <v>3.54907916981184</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>3.21665617213322</v>
+        <v>3.457408529271845</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X &gt; 0.2148</t>
+          <t>X &gt; 0.2143</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1004</v>
+        <v>1007</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>2.797968431617036</v>
+        <v>2.802698502819069</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>3.378017398314171</v>
+        <v>3.304923602370266</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>2.784042826308138</v>
+        <v>2.712575882178712</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>4.507893467904466</v>
+        <v>4.431337778408285</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>3.471595946681283</v>
+        <v>3.544869173702637</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>4.266977944443859</v>
+        <v>4.314179022213722</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>3.883462804301196</v>
+        <v>3.955608335172968</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>3.615597347765458</v>
+        <v>3.68838530666649</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>3.753818378493676</v>
+        <v>3.850022429406557</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>3.302305956665805</v>
+        <v>3.423413312345289</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>3.695214360158602</v>
+        <v>3.815102060439791</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>3.331186138011937</v>
+        <v>3.476049334050956</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>3.907051220953505</v>
+        <v>4.073940066871444</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>3.933583683929044</v>
+        <v>4.124375197009947</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X &gt; 0.2512</t>
+          <t>X &gt; 0.2506</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>840</v>
+        <v>843</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>2.400036350418034</v>
+        <v>2.412782599786802</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>2.693612162116104</v>
+        <v>2.490340983195594</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>2.417888396408685</v>
+        <v>2.452474881001898</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>3.619542111425623</v>
+        <v>3.768598542619891</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>2.366966844044207</v>
+        <v>2.567605629425984</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>3.497674207012636</v>
+        <v>3.433510958446568</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>3.0558209906036</v>
+        <v>3.016982983100114</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>2.469704727769241</v>
+        <v>2.43252626067644</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>2.884913047436953</v>
+        <v>2.870049499700968</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>2.392137108249948</v>
+        <v>2.40209280500698</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>3.377912140465938</v>
+        <v>3.38419197787421</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>2.936099816630787</v>
+        <v>2.967862867077777</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>4.063568010936422</v>
+        <v>4.114816447038272</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>3.455970327829625</v>
+        <v>3.770741498851969</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X &gt; 0.2875</t>
+          <t>X &gt; 0.2869</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>672</v>
+        <v>674</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>3.173845874227553</v>
+        <v>2.979502418436454</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>2.901945495449432</v>
+        <v>2.880004858503156</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>2.358364586884875</v>
+        <v>2.189530965143945</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>4.125494492378003</v>
+        <v>3.95146248410343</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>2.545538272615637</v>
+        <v>2.423637675495726</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>3.438150397488826</v>
+        <v>3.289895004403675</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>2.60939241917503</v>
+        <v>2.487399152566937</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>2.737561870626394</v>
+        <v>2.615038202272615</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>3.123008285532187</v>
+        <v>3.023169450702582</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>2.868327584440422</v>
+        <v>2.79281267997662</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>4.300531188084989</v>
+        <v>4.220719710185342</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>3.442052197583166</v>
+        <v>3.388678732416693</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>4.212377534745947</v>
+        <v>4.180464426030916</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>3.99168461354391</v>
+        <v>3.984405430479519</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X &gt; 0.3239</t>
+          <t>X &gt; 0.3232</t>
         </is>
       </c>
       <c r="B24" t="n">
         <v>566</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>3.879507997734201</v>
+        <v>3.85031220338157</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>4.035106356967191</v>
+        <v>4.033919570522535</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>2.580264300834052</v>
+        <v>2.580110910829731</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>5.360666122867656</v>
+        <v>5.360171630489653</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>3.585627453164186</v>
+        <v>3.634173372929958</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>3.529644592339906</v>
+        <v>3.553602001289519</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>2.914898897384688</v>
+        <v>2.962910576375009</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>3.684579370205725</v>
+        <v>3.733826932599442</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>3.270240323223589</v>
+        <v>3.343497433003286</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>3.480392198271822</v>
+        <v>3.579739523566396</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>4.335761711389715</v>
+        <v>4.43566974740839</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>3.663426082826319</v>
+        <v>3.787122703854564</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>4.126667455661313</v>
+        <v>4.27535700343914</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>2.938975544050393</v>
+        <v>3.110974303617056</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X &gt; 0.3602</t>
+          <t>X &gt; 0.3595</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>4.483740934122615</v>
+        <v>4.425705980496041</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>3.912055880559819</v>
+        <v>4.084764920184902</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>3.725184703704997</v>
+        <v>3.691026931870198</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>5.51861151049502</v>
+        <v>5.477225672877836</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>3.940820917898279</v>
+        <v>3.952779844555316</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>3.822394531732954</v>
+        <v>3.811486688426008</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>3.945584380366995</v>
+        <v>3.957869936674676</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>3.686415944480459</v>
+        <v>3.699076513765441</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>3.625433787957682</v>
+        <v>3.662103904628644</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>2.775514991627823</v>
+        <v>3.04531466128779</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>4.234015496569299</v>
+        <v>4.497488913544657</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>2.397291777822751</v>
+        <v>2.692301613642464</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>3.640342587711011</v>
+        <v>3.953458386871603</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>2.202876574735875</v>
+        <v>2.546188549094005</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X &gt; 0.3965</t>
+          <t>X &gt; 0.3958</t>
         </is>
       </c>
       <c r="B26" t="n">
         <v>398</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>4.05174728604856</v>
+        <v>4.022551491695928</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>2.440561192984731</v>
+        <v>2.439374406540075</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>2.29704608963673</v>
+        <v>2.296892699632409</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>4.688577765888404</v>
+        <v>4.688083273510401</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>2.894006805757535</v>
+        <v>2.942552725523306</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>2.437611991171515</v>
+        <v>2.461569400121128</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>2.604157913312392</v>
+        <v>2.652169592302712</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>2.388345550932684</v>
+        <v>2.4375931133264</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>2.829875957223976</v>
+        <v>2.903133067003672</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>1.979957160894116</v>
+        <v>2.07930448618869</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>3.031537409669099</v>
+        <v>3.131445445687774</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>1.307121592175179</v>
+        <v>1.430818213203423</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>2.645764708711013</v>
+        <v>2.794454256488841</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>0.8614501076812715</v>
+        <v>1.033448867247934</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X &gt; 0.4329</t>
+          <t>X &gt; 0.4321</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>4.26065700317352</v>
+        <v>4.072521228334303</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>2.649470910109692</v>
+        <v>2.48934414317845</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>2.535598401759138</v>
+        <v>2.375718199681671</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>4.632115680178963</v>
+        <v>4.466386554621849</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>2.408432868656298</v>
+        <v>2.296465144762358</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>1.582211392673415</v>
+        <v>1.448802484309581</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>0.9357032805982541</v>
+        <v>0.8279223054482685</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>0.7495335132160079</v>
+        <v>0.6422015898828519</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>1.250349109502224</v>
+        <v>1.165453070381908</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>0.9622280659813498</v>
+        <v>0.9018485792027775</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>1.881122413339142</v>
+        <v>1.818156310938406</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>0.2301073072674953</v>
+        <v>0.1956507793957272</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>1.21445083597655</v>
+        <v>1.201053076921532</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>-0.2452067722238738</v>
+        <v>-0.2305743299706577</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X &gt; 0.4692</t>
+          <t>X &gt; 0.4684</t>
         </is>
       </c>
       <c r="B28" t="n">
         <v>313</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>2.790649464673315</v>
+        <v>2.761453670320684</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>1.179463371609486</v>
+        <v>1.178276585164831</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>1.104180804745823</v>
+        <v>1.104027414741502</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>3.151338855682432</v>
+        <v>3.150844363304429</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>0.3766275773471151</v>
+        <v>0.4251734971128869</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>0.03502397119945044</v>
+        <v>0.05898138014906351</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-0.04968638806671777</v>
+        <v>-0.001674709076397107</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>0.1222226039292948</v>
+        <v>0.1714701663230116</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>0.3807292652978944</v>
+        <v>0.4539863750775908</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-0.1497007131405894</v>
+        <v>-0.05035338784601606</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-0.3544018714007819</v>
+        <v>-0.2544938353821067</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-1.917467808502337</v>
+        <v>-1.793771187474093</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-0.4206857544674989</v>
+        <v>-0.2719962066896713</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>-1.792394193697838</v>
+        <v>-1.620395434131176</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X &gt; 0.5055</t>
+          <t>X &gt; 0.5047</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>0.8787677639320535</v>
+        <v>0.8232215084463519</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>0.05809550486031867</v>
+        <v>0.02435814878069209</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>1.639608705085514</v>
+        <v>1.591404474191478</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>2.955604599662024</v>
+        <v>2.897759103641448</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-0.3494833724060129</v>
+        <v>0.05556878621894867</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-0.05210934277092605</v>
+        <v>0.3283543050378768</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>0.6536941319550067</v>
+        <v>1.052011941302609</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>-0.6038883458238331</v>
+        <v>-0.1981345445709266</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>0.5209002486415386</v>
+        <v>0.9413634345275668</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>-0.7242754646843679</v>
+        <v>-0.2746220090325124</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>-1.3242335399406</v>
+        <v>-0.8709193193136997</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>-3.266139972565519</v>
+        <v>-3.165693758419394</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>-2.500520074890787</v>
+        <v>-1.992224234002833</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>-3.855812092648449</v>
+        <v>-3.703963685712949</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X &gt; 0.5419</t>
+          <t>X &gt; 0.541</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>1.665425432880284</v>
+        <v>1.858820213947965</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>1.029849095914017</v>
+        <v>1.246516915199877</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>1.122882589207762</v>
+        <v>1.338215820089061</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>1.253107732796124</v>
+        <v>1.468099861303742</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-1.724206210543478</v>
+        <v>-1.448333745667597</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-2.402441937005953</v>
+        <v>-2.146422013256434</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>-1.51154254017456</v>
+        <v>-1.236204316074129</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-1.490806305912514</v>
+        <v>-1.21660018325359</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-1.55178846243529</v>
+        <v>-1.253572792390386</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-3.865121892911496</v>
+        <v>-3.533712052817016</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>-3.582018173122904</v>
+        <v>-3.252415607149224</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>-5.498859532962705</v>
+        <v>-5.135996442599868</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-5.431205508227336</v>
+        <v>-5.045717475959812</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-6.181079614098365</v>
+        <v>-5.767546400352209</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X &gt; 0.5782</t>
+          <t>X &gt; 0.5773</t>
         </is>
       </c>
       <c r="B31" t="n">
         <v>174</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>0.3926471878564541</v>
+        <v>0.3634513935038228</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>-1.793251548885543</v>
+        <v>-1.794438335330199</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-2.188022933640582</v>
+        <v>-2.188176323644903</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-0.9083725026958973</v>
+        <v>-0.9088669950739003</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-4.894937917860553</v>
+        <v>-4.846391998094781</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-6.32170181925995</v>
+        <v>-6.297744410310337</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>-6.406412178526118</v>
+        <v>-6.358400499535797</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>-7.448193465991018</v>
+        <v>-7.398945903597301</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-6.359750335157472</v>
+        <v>-6.286493225377775</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>-6.060243844131008</v>
+        <v>-5.960896518836435</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>-5.690232358713033</v>
+        <v>-5.590324322694357</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>-7.954704781070362</v>
+        <v>-7.831008160042117</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>-7.800142990705609</v>
+        <v>-7.651453442927782</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>-6.999694696800915</v>
+        <v>-6.827695937234253</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>X &gt; 0.6145</t>
+          <t>X &gt; 0.6136</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>-1.031640668215516</v>
+        <v>-0.3672546820298379</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>-3.367464442438759</v>
+        <v>-2.664717481471413</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-0.8636851025561114</v>
+        <v>-0.2013126126432567</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>0.7158154033510868</v>
+        <v>0.6428571428571459</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-5.619575599019967</v>
+        <v>-4.846391998094781</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-8.220752294022567</v>
+        <v>-7.430749336418714</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>-8.305462653288735</v>
+        <v>-8.205691139929883</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>-9.497168978234896</v>
+        <v>-10.10009532888466</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-7.384238091279407</v>
+        <v>-7.994210795164314</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>-6.060243844131008</v>
+        <v>-6.675182233122143</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>-5.540307321231779</v>
+        <v>-6.165036966372526</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>-7.679842212354721</v>
+        <v>-8.249727371864772</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>-9.549268427986966</v>
+        <v>-9.35917101271432</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>-10.04817045891986</v>
+        <v>-9.824411864984661</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X &gt; 0.6509</t>
+          <t>X &gt; 0.6498</t>
         </is>
       </c>
       <c r="B33" t="n">
         <v>116</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>0.1052908660173699</v>
+        <v>0.07609507166473861</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>-1.505895227046459</v>
+        <v>-1.507082013491114</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>-0.1765286807670137</v>
+        <v>-0.176682070771335</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>1.677834393855825</v>
+        <v>1.677339901477822</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-4.032868952343314</v>
+        <v>-3.984323032577542</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-8.045839750294434</v>
+        <v>-8.021882341344821</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>-7.268481144043356</v>
+        <v>-7.220469465053036</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-6.873480822312857</v>
+        <v>-6.82423325991914</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-6.934462978835633</v>
+        <v>-6.861205869055937</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>-5.19817487861377</v>
+        <v>-5.098827553319197</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>-5.402876036873963</v>
+        <v>-5.302968000855287</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>-9.678842712104846</v>
+        <v>-9.555146091076601</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>-11.82313149645273</v>
+        <v>-11.6744419486749</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>-11.5973958462262</v>
+        <v>-11.42539708665954</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X &gt; 0.6872</t>
+          <t>X &gt; 0.6861</t>
         </is>
       </c>
       <c r="B34" t="n">
         <v>100</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>1.519083969465647</v>
+        <v>1.489888175113016</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>-0.09210212359818115</v>
+        <v>-0.0932889100428369</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>0.513126491646787</v>
+        <v>0.5129731016424657</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>1.643351635235149</v>
+        <v>1.642857142857146</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-6.894937917860553</v>
+        <v>-6.846391998094781</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-8.597563888225466</v>
+        <v>-8.573606479275853</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>-6.682274247491634</v>
+        <v>-6.634262568501313</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>-7.149342891278373</v>
+        <v>-7.100095328884656</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>-8.210325047801149</v>
+        <v>-8.137067938021453</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>-8.060243844131008</v>
+        <v>-7.960896518836435</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>-6.264945002391201</v>
+        <v>-6.165036966372526</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>-12.23056685003588</v>
+        <v>-12.10687022900763</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>-14.65071770334929</v>
+        <v>-14.50202815557146</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>-14.42498205312275</v>
+        <v>-14.25298329355609</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>X &gt; 0.7236</t>
+          <t>X &gt; 0.7224</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>1.177620554831506</v>
+        <v>0.501936367884106</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>-1.65307773335428</v>
+        <v>-2.286059994380189</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>0.3911752721345891</v>
+        <v>-0.2701594284780242</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>2.960424805966845</v>
+        <v>3.474182444061952</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>-4.894937917860553</v>
+        <v>-5.448801636649002</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>-8.256100473591317</v>
+        <v>-8.79047394915537</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>-10.77983522310139</v>
+        <v>-11.2607685925977</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>-8.807879476644224</v>
+        <v>-9.316962798764173</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>-11.3078860234109</v>
+        <v>-10.5587546850094</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>-12.15780481974076</v>
+        <v>-11.38258326582439</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>-11.142993782879</v>
+        <v>-10.38190443625204</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>-15.98666441101148</v>
+        <v>-16.34783408442932</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>-18.8458396545688</v>
+        <v>-19.15263056521002</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>-19.83961619946422</v>
+        <v>-20.10840498030308</v>
       </c>
     </row>
   </sheetData>
@@ -3904,105 +3904,105 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X &lt; -0.3302</t>
+          <t>X &lt; -0.3301</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>8.494693725563209</v>
+        <v>8.935671307643133</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>6.883507632499381</v>
+        <v>7.35249422248728</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>6.488736247744342</v>
+        <v>6.958756234172576</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>9.057985781576605</v>
+        <v>9.498278829604118</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>10.95872061872482</v>
+        <v>11.41866824286908</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>11.25609464835991</v>
+        <v>11.69145376168801</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>12.39089648421569</v>
+        <v>12.83561694957098</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>11.92382784042895</v>
+        <v>12.36978418918763</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>9.423821293662272</v>
+        <v>9.923173025833968</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>13.4519512778202</v>
+        <v>13.91862155345272</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>15.68627450980392</v>
+        <v>16.1241196601335</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>13.28162827191533</v>
+        <v>13.77264784328153</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>14.08098961372389</v>
+        <v>14.58230919382613</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>14.30672526395042</v>
+        <v>14.83135405584149</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X &lt; -0.2939</t>
+          <t>X &lt; -0.2938</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>126</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>10.21749666787834</v>
+        <v>10.18830087352571</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>2.257104225608167</v>
+        <v>2.255917439163511</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>6.624237602757894</v>
+        <v>6.624084212753573</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>9.929065920949434</v>
+        <v>9.928571428571431</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>12.56537954245692</v>
+        <v>12.61392546222269</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>9.688150397488826</v>
+        <v>9.712107806438439</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>11.98439241917502</v>
+        <v>12.03240409816534</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>8.342720600785114</v>
+        <v>8.391968163178831</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>9.075389237913143</v>
+        <v>9.148646347692839</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>11.40007361618646</v>
+        <v>11.49942094148103</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>11.98902325157705</v>
+        <v>12.08893128759573</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>13.61070299123396</v>
+        <v>13.7343996122622</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>10.80959975696818</v>
+        <v>10.95828930474601</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>11.8289862008455</v>
+        <v>12.00098496041216</v>
       </c>
     </row>
     <row r="8">
@@ -4015,46 +4015,46 @@
         <v>204</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>5.852417302798983</v>
+        <v>5.823221508446352</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-0.1705334961472005</v>
+        <v>-0.1717202825918562</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>0.9052833543918837</v>
+        <v>0.9051299643875623</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>2.996292811705729</v>
+        <v>2.995798319327726</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>3.928591493904158</v>
+        <v>3.977137413669929</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>2.265181209813747</v>
+        <v>2.28913861876336</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>2.180470850547579</v>
+        <v>2.228482529537899</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-0.7375781853960248</v>
+        <v>-0.6883306230023081</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>1.652420050238064</v>
+        <v>1.72567716001776</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>2.763285567633702</v>
+        <v>2.862632892928275</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>2.558584409373509</v>
+        <v>2.658492445392184</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>1.612570404866091</v>
+        <v>1.736267025894335</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>0.212027394689926</v>
+        <v>0.3607169424677537</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>0.4377630449164585</v>
+        <v>0.6097618044831208</v>
       </c>
     </row>
     <row r="9">
@@ -4067,46 +4067,46 @@
         <v>296</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>1.910975861357542</v>
+        <v>1.881780067004911</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-1.051561583057641</v>
+        <v>-1.052748369502297</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-0.0949816164613253</v>
+        <v>-0.09513500646564665</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>1.048757040640545</v>
+        <v>1.048262548262542</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>1.186143163220535</v>
+        <v>1.234689082986307</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>0.1321658415042606</v>
+        <v>0.1561232504538737</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-1.303895869113255</v>
+        <v>-1.255884190122934</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-3.460153702089187</v>
+        <v>-3.41090613969547</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-2.507622345098454</v>
+        <v>-2.434365235318758</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-2.344027627914791</v>
+        <v>-2.244680302620218</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-0.8595395969857975</v>
+        <v>-0.7596315609671223</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-2.852188471657499</v>
+        <v>-2.728491850629254</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-2.59666364929523</v>
+        <v>-2.447974101517403</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-2.033090161230859</v>
+        <v>-1.861091401664197</v>
       </c>
     </row>
     <row r="10">
@@ -4116,1349 +4116,1349 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>0.445913237758333</v>
+        <v>0.3016241164333096</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-2.872589928476231</v>
+        <v>-2.993044411265338</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-2.047849118109319</v>
+        <v>-2.164288512049474</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-0.4542093403746108</v>
+        <v>-0.5674118057981161</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>0.2270133016516453</v>
+        <v>0.1658329407805255</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-0.939027302859607</v>
+        <v>-1.028374205437224</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-1.999347418223337</v>
+        <v>-2.067025404687129</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-3.198123379083249</v>
+        <v>-3.266354497588814</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-1.307886023410902</v>
+        <v>-1.347336886676707</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-1.913902380716372</v>
+        <v>-1.926666689985581</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-1.142993782879003</v>
+        <v>-1.15281202749722</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-2.572030264670019</v>
+        <v>-2.561637955169004</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-2.260473800910262</v>
+        <v>-2.223299549214495</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-1.790835711659334</v>
+        <v>-1.729755909693012</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X &lt; -0.1485</t>
+          <t>X &lt; -0.1486</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>564</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-1.062476314222295</v>
+        <v>-1.111510426285591</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-3.737492194520172</v>
+        <v>-3.743638560392483</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-2.536518898424148</v>
+        <v>-2.389124800455448</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-0.9878540385237287</v>
+        <v>-0.6858141858141948</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>0.06960108923163943</v>
+        <v>0.144851434479655</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-0.8741596329063128</v>
+        <v>-0.538518759977606</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-2.200004743945534</v>
+        <v>-1.91018523985457</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-3.198988281349301</v>
+        <v>-2.811362934518456</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-1.841530721560019</v>
+        <v>-1.521547655834503</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-2.159534624272851</v>
+        <v>-1.897292278553756</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-1.12310103075999</v>
+        <v>-0.9437980283194278</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-1.797942736560699</v>
+        <v>-1.674246115532455</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-1.686178696257095</v>
+        <v>-1.537489148479267</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-0.5739182233355251</v>
+        <v>-0.5792244283078674</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X &lt; -0.1122</t>
+          <t>X &lt; -0.1123</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>764</v>
+        <v>771</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-1.0597274000434</v>
+        <v>-1.041401735487234</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-2.086927479354969</v>
+        <v>-1.986009216556248</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-0.8599305031718742</v>
+        <v>-0.9064642385109991</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-0.4007469380463107</v>
+        <v>-0.4518931772452888</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>0.9492179262952902</v>
+        <v>0.6664285147257374</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-0.3712960078613534</v>
+        <v>-0.4015910749112805</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-2.338524247491634</v>
+        <v>-2.577707298578439</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-2.998104299361813</v>
+        <v>-3.233943462732789</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-0.973036912207931</v>
+        <v>-1.271088556578157</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-0.9103090331792458</v>
+        <v>-1.251219099481595</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>0.1887707733584705</v>
+        <v>-0.09268554518389749</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>0.03575168782312943</v>
+        <v>-0.3500785084384219</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-0.3108484223035362</v>
+        <v>-0.8025462902864859</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-0.01136948767772594</v>
+        <v>-0.6109599472525886</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X &lt; -0.07585</t>
+          <t>X &lt; -0.07603</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1045</v>
+        <v>1055</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-1.441218488001276</v>
+        <v>-1.386516319269006</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-2.341865605149749</v>
+        <v>-2.359455732910689</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-1.551267447747165</v>
+        <v>-1.578959356143656</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-0.8969327249544321</v>
+        <v>-0.9299128101945016</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>0.6079083819496987</v>
+        <v>0.4167658966420689</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-0.2765762339044784</v>
+        <v>-0.3873411923520536</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-1.545392118214068</v>
+        <v>-1.715241852870435</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-1.581312444085221</v>
+        <v>-1.659944527753652</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-0.5436583811344846</v>
+        <v>-0.7031056738705033</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-0.5788329766381537</v>
+        <v>-0.8145320240300151</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>0.3190244632576551</v>
+        <v>0.07314828882596913</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>0.3119355377387194</v>
+        <v>-0.004694259281990298</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-0.2453639748598064</v>
+        <v>-0.6308160343593343</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>0.03434809041790743</v>
+        <v>-0.4235994073001663</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X &lt; -0.03951</t>
+          <t>X &lt; -0.03973</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1334</v>
+        <v>1343</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-0.6620593119003573</v>
+        <v>-0.5927076950934733</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-1.863275972037997</v>
+        <v>-1.76856566281036</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-1.698769419133889</v>
+        <v>-1.680527636909986</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-1.157243602860092</v>
+        <v>-1.215975081828745</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-0.01779718815094355</v>
+        <v>-0.1866286844853136</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-0.4992032324877584</v>
+        <v>-0.6135768715778482</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-1.214712726238844</v>
+        <v>-1.375003309242054</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-1.716507070382853</v>
+        <v>-1.875484506052928</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-1.364171201647302</v>
+        <v>-1.502053101226203</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-1.575938911395582</v>
+        <v>-1.766390208517208</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-0.7675628034383166</v>
+        <v>-1.038736817784113</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-1.065896191353239</v>
+        <v>-1.385680637929568</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-1.594537928068384</v>
+        <v>-1.963337679380984</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-1.62738085372245</v>
+        <v>-2.045984038157734</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X &lt; -0.003174</t>
+          <t>X &lt; -0.00344</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1653</v>
+        <v>1660</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-1.640579896080574</v>
+        <v>-1.523859583404615</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-2.020030051526106</v>
+        <v>-1.94017886219595</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-1.902738892968607</v>
+        <v>-1.883795300511942</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-1.560496831391433</v>
+        <v>-1.542771599657833</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-1.344998086332268</v>
+        <v>-1.40121524554835</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-1.858250221759484</v>
+        <v>-1.87576475265714</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-2.634081476407303</v>
+        <v>-2.684652490516918</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-2.768390510325986</v>
+        <v>-2.759158954334836</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-2.315270765533356</v>
+        <v>-2.344275145228657</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-2.831517229767698</v>
+        <v>-2.956088826528749</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-2.339824229444346</v>
+        <v>-2.466901067394772</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-2.574977726168811</v>
+        <v>-2.737435812641806</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-2.841769698512536</v>
+        <v>-3.040258137510051</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-2.401993547375625</v>
+        <v>-2.638525462230788</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X &lt; 0.03316</t>
+          <t>X &lt; 0.03285</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1968</v>
+        <v>1977</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-1.345126025486401</v>
+        <v>-1.304081674133215</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-1.920384951881012</v>
+        <v>-1.855983731561182</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-1.530835105119266</v>
+        <v>-1.519220057311273</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-1.171612975482759</v>
+        <v>-1.16137033575383</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-0.8736936083006199</v>
+        <v>-0.9188995509648734</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-1.358697491464333</v>
+        <v>-1.37461403595092</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-1.872147665213149</v>
+        <v>-1.912488374952929</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-2.413780581247977</v>
+        <v>-2.452591546736393</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-2.143928697066222</v>
+        <v>-2.210730904721757</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-2.510548103765899</v>
+        <v>-2.604006059472475</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-2.282195129230374</v>
+        <v>-2.377158178493744</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-2.5249830936907</v>
+        <v>-2.645526115819152</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-2.562347972521451</v>
+        <v>-2.710319358807055</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-2.207502378326012</v>
+        <v>-2.383484052281439</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X &lt; 0.0695</t>
+          <t>X &lt; 0.06915</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2261</v>
+        <v>2269</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-1.205630190604715</v>
+        <v>-1.239296750390928</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-2.222326496673404</v>
+        <v>-2.230071023151126</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-1.802014353423644</v>
+        <v>-1.811588301866308</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-1.692623706024222</v>
+        <v>-1.658590860653177</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-1.194497389226193</v>
+        <v>-1.246743183345004</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-1.710829644065036</v>
+        <v>-1.740931907470845</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-1.992679891230608</v>
+        <v>-2.041995433176183</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-2.48061770380594</v>
+        <v>-2.528666757456087</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-2.341834315232745</v>
+        <v>-2.410594762999459</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-2.462009848546018</v>
+        <v>-2.551305669738326</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-2.333849596030781</v>
+        <v>-2.423839783273941</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-2.629152797892708</v>
+        <v>-2.738310123327317</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-2.760355192297119</v>
+        <v>-2.889693353809342</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-2.643469448080737</v>
+        <v>-2.793309428417267</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X &lt; 0.1058</t>
+          <t>X &lt; 0.1054</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2502</v>
+        <v>2509</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-1.347715235305721</v>
+        <v>-1.241277566362008</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-1.86457626838736</v>
+        <v>-1.772781175017059</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-1.522289345997464</v>
+        <v>-1.471153882484522</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-2.047731167312627</v>
+        <v>-1.995094425225432</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-1.290796141675763</v>
+        <v>-1.351554825735768</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-1.529834804560124</v>
+        <v>-1.574003777646929</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-1.752820281768237</v>
+        <v>-1.812322981855843</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-2.119039860975342</v>
+        <v>-2.177630120137138</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-1.839762622591735</v>
+        <v>-1.915110897448663</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-1.95010816974952</v>
+        <v>-2.041278532366078</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-1.933607677041898</v>
+        <v>-2.024909577837498</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-1.957403910738755</v>
+        <v>-2.104480742747185</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-2.116159173584997</v>
+        <v>-2.278920585850344</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-1.948563188214685</v>
+        <v>-2.127833831619064</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X &lt; 0.1422</t>
+          <t>X &lt; 0.1417</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2695</v>
+        <v>2703</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-1.114594021671721</v>
+        <v>-1.074176626065189</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-1.672449371474059</v>
+        <v>-1.643933477261996</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-1.160931158020631</v>
+        <v>-1.207734341246265</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-1.639457976594805</v>
+        <v>-1.684824390500765</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-1.529553302475939</v>
+        <v>-1.601554239982683</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-1.767375208980184</v>
+        <v>-1.788656276398683</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-1.943562182354697</v>
+        <v>-1.977436000235635</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-2.131941928671928</v>
+        <v>-2.128519101494476</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-1.802917640393744</v>
+        <v>-1.81358197051776</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-1.929084155357387</v>
+        <v>-1.952769440890371</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-1.8172059364164</v>
+        <v>-1.841311910940156</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-1.762639523376627</v>
+        <v>-1.80003104231632</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-1.865851234506557</v>
+        <v>-1.916229339003415</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-1.768210253493812</v>
+        <v>-1.831969605061822</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X &lt; 0.1785</t>
+          <t>X &lt; 0.178</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2908</v>
+        <v>2917</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-0.8889954553888515</v>
+        <v>-0.8718865689142916</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-1.283882945515984</v>
+        <v>-1.276627933600359</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-1.11243020585237</v>
+        <v>-1.140032362838419</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-1.375154190673008</v>
+        <v>-1.401898579725717</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-1.106799419403238</v>
+        <v>-1.155346201785825</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-1.305382818266622</v>
+        <v>-1.342837248506626</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-1.131673904438458</v>
+        <v>-1.180090201880247</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-1.134243371717638</v>
+        <v>-1.182886981296562</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-0.6617496959302258</v>
+        <v>-0.722283543770935</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-0.7717823056694684</v>
+        <v>-0.8427862826159611</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-0.7170233259913417</v>
+        <v>-0.7883246376054061</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-0.7322850630942952</v>
+        <v>-0.8139616986890275</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-0.8583491918332982</v>
+        <v>-0.9502803831245785</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-0.7853671975519134</v>
+        <v>-0.8878821622568154</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X &lt; 0.2148</t>
+          <t>X &lt; 0.2143</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>3076</v>
+        <v>3084</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-0.813709814930597</v>
+        <v>-0.8149229324103899</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-1.015677253131862</v>
+        <v>-0.9925137162443818</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-0.907346459438422</v>
+        <v>-0.8844420841410638</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-1.278229699826426</v>
+        <v>-1.254363283775049</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-0.9241113376336472</v>
+        <v>-0.9504980440049025</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-1.160469205994595</v>
+        <v>-1.177746194670419</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-1.065667046713166</v>
+        <v>-1.091719702115036</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-1.028642047670324</v>
+        <v>-1.054787885518955</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-0.9422302733772554</v>
+        <v>-0.9771456330683961</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-0.8329711168582818</v>
+        <v>-0.8766996276447259</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-0.922301286899156</v>
+        <v>-0.9658144202112027</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-0.7399885524400389</v>
+        <v>-0.7925474811139139</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-0.8171135434532886</v>
+        <v>-0.8780411215358015</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-0.8007947969459082</v>
+        <v>-0.8703633194964269</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X &lt; 0.2512</t>
+          <t>X &lt; 0.2506</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>3240</v>
+        <v>3248</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-0.5288717637037337</v>
+        <v>-0.5321909417223125</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-0.6173173757507016</v>
+        <v>-0.5656815480796453</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-0.6265228470182436</v>
+        <v>-0.6361523969767475</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-0.7566483647648568</v>
+        <v>-0.7966763132508987</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-0.4166369021634111</v>
+        <v>-0.4712001037134428</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-0.6874653660579852</v>
+        <v>-0.6731150787844484</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-0.6015843799215688</v>
+        <v>-0.5943240124337237</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-0.4974636552956255</v>
+        <v>-0.4903842041151449</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-0.4799706564298134</v>
+        <v>-0.4798284667641539</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-0.3882339797660279</v>
+        <v>-0.3950908607798596</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-0.6066039601463729</v>
+        <v>-0.6128991626198399</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-0.4316772756990517</v>
+        <v>-0.4453317674691704</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-0.6186288418867747</v>
+        <v>-0.6386855886277871</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-0.4373277321350955</v>
+        <v>-0.5263823083344192</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X &lt; 0.2875</t>
+          <t>X &lt; 0.2869</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>3408</v>
+        <v>3417</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-0.5370399709026614</v>
+        <v>-0.4984500173068085</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-0.495610895528003</v>
+        <v>-0.4916557808506568</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-0.4652297528691562</v>
+        <v>-0.4321844246119184</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-0.6410251933195639</v>
+        <v>-0.6075076076535169</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-0.3148969462480338</v>
+        <v>-0.2929769367988087</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-0.4699292278039238</v>
+        <v>-0.4422196179619817</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-0.3338115827771446</v>
+        <v>-0.311832661959258</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-0.4041759317001663</v>
+        <v>-0.3820117764452746</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-0.361218689758374</v>
+        <v>-0.3445489432815378</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-0.3451207491720325</v>
+        <v>-0.3338868725341868</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-0.5921217833938428</v>
+        <v>-0.5802416447350964</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-0.3654642107396953</v>
+        <v>-0.3595756984431375</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-0.4172181433610191</v>
+        <v>-0.4165980795035793</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-0.3510383911509294</v>
+        <v>-0.3559976336204755</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X &lt; 0.3239</t>
+          <t>X &lt; 0.3232</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>3514</v>
+        <v>3525</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-0.5387555542088549</v>
+        <v>-0.5315928876343037</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-0.5753692818511666</v>
+        <v>-0.5733567641565003</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-0.4159515225376182</v>
+        <v>-0.4146287083122928</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-0.696035424923771</v>
+        <v>-0.6937765205091964</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-0.3959313893337253</v>
+        <v>-0.4038339901717407</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-0.3670130648296706</v>
+        <v>-0.3703797597740106</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-0.2943162810048463</v>
+        <v>-0.3024392389429877</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-0.4618428912783727</v>
+        <v>-0.4696790162253563</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-0.2799470995203848</v>
+        <v>-0.2928753034605478</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-0.3467702796057139</v>
+        <v>-0.3644102621064889</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-0.4503302739294455</v>
+        <v>-0.467758054807895</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-0.2863120149960565</v>
+        <v>-0.3087415077147497</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-0.2638044743307972</v>
+        <v>-0.2910241850666324</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-0.05048006109087311</v>
+        <v>-0.08277052759864034</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X &lt; 0.3602</t>
+          <t>X &lt; 0.3595</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>3599</v>
+        <v>3608</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-0.515246041608556</v>
+        <v>-0.5079024904489842</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-0.4504516112747226</v>
+        <v>-0.4745043796560964</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-0.4979538407631878</v>
+        <v>-0.4942112034141886</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-0.5744372259452462</v>
+        <v>-0.5705204138039974</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-0.3494833724060129</v>
+        <v>-0.3537185117801585</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-0.3142259342470908</v>
+        <v>-0.3147569217537267</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-0.3561511193718374</v>
+        <v>-0.3604036473394885</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-0.3643220868400974</v>
+        <v>-0.368495992968775</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-0.2436213852040297</v>
+        <v>-0.2519309327626615</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-0.1623809520965978</v>
+        <v>-0.2023140160678878</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-0.3238011933962071</v>
+        <v>-0.3633199904655697</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-0.0239575748345402</v>
+        <v>-0.0680890655727282</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-0.09516214779372945</v>
+        <v>-0.1429259111824308</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>0.1185022480720264</v>
+        <v>0.06630717207583814</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X &lt; 0.3965</t>
+          <t>X &lt; 0.3958</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3682</v>
+        <v>3693</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-0.3564234730242006</v>
+        <v>-0.3514501950974562</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-0.1938888047026737</v>
+        <v>-0.1931539572763015</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-0.2491264192657567</v>
+        <v>-0.2483659912301093</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-0.3479809758157728</v>
+        <v>-0.3468809073724088</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-0.1401289230082057</v>
+        <v>-0.1462299235404885</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-0.07181863077289563</v>
+        <v>-0.0748223668737964</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-0.1146407424767233</v>
+        <v>-0.1207490549878045</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-0.1330739108011514</v>
+        <v>-0.1392951126099931</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-0.07064509119686591</v>
+        <v>-0.08028048534432486</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-0.01032523317061873</v>
+        <v>-0.02365010282344571</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-0.09126793319174453</v>
+        <v>-0.1044309057664705</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>0.1483690891606528</v>
+        <v>0.1312894462291752</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>0.09649923936045468</v>
+        <v>0.07620682006470503</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>0.3104878002178282</v>
+        <v>0.2864155691571497</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X &lt; 0.4329</t>
+          <t>X &lt; 0.4321</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>3724</v>
+        <v>3734</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-0.3267816981822023</v>
+        <v>-0.3083504157596835</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-0.1841792113926175</v>
+        <v>-0.1691031118581066</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-0.2432322767601747</v>
+        <v>-0.2280148823361827</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-0.2859467043470758</v>
+        <v>-0.2706043956044013</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-0.05968477025808028</v>
+        <v>-0.05077351025079935</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>0.03802024896638301</v>
+        <v>0.0495896725146352</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>0.07516343677531978</v>
+        <v>0.08372727378684885</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>0.05172949478060929</v>
+        <v>0.06033247860197832</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>0.1128178859612561</v>
+        <v>0.1183479485792489</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>0.1092840528647017</v>
+        <v>0.1118696662892944</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>0.05381002846471716</v>
+        <v>0.05653113638369689</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>0.2643338477633677</v>
+        <v>0.2635794497932267</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>0.262033974503062</v>
+        <v>0.2583466770925256</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>0.4224937793154879</v>
+        <v>0.4154687685756642</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X &lt; 0.4692</t>
+          <t>X &lt; 0.4684</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>3767</v>
+        <v>3778</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>-0.1528737024920304</v>
+        <v>-0.1492571691233309</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-0.03018098043861528</v>
+        <v>-0.02996437178426703</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-0.09301432359938389</v>
+        <v>-0.09272761094661064</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-0.1072440756465056</v>
+        <v>-0.1068788655905877</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>0.1368417431563884</v>
+        <v>0.1311627946171328</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>0.1838930654169175</v>
+        <v>0.1807516823723248</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>0.1666923661808681</v>
+        <v>0.1609818172318427</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>0.1117225738687253</v>
+        <v>0.1060357493394406</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>0.1979464262179391</v>
+        <v>0.1893925430782062</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>0.2113021648851614</v>
+        <v>0.199864983014443</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>0.2602539366008401</v>
+        <v>0.2486102169123185</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>0.4422906718532218</v>
+        <v>0.4275213053839053</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>0.4087302796655763</v>
+        <v>0.3913298756537316</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>0.5434278221095283</v>
+        <v>0.5230887022088595</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X &lt; 0.5055</t>
+          <t>X &lt; 0.5047</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>3827</v>
+        <v>3836</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>0.0190839694656475</v>
+        <v>0.02301366225253787</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>0.06262567009810027</v>
+        <v>0.064715247961324</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-0.109593675106737</v>
+        <v>-0.1069905063637862</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-0.04338279270334766</v>
+        <v>-0.04097021023697778</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>0.18848231154508</v>
+        <v>0.1601099524903944</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>0.1873122525828848</v>
+        <v>0.1610449255108293</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>0.1168911150540097</v>
+        <v>0.08861018715833069</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>0.1598144267492856</v>
+        <v>0.1315548533121103</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>0.1915538666038614</v>
+        <v>0.1610315152459307</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>0.2435932741148861</v>
+        <v>0.210978481163572</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>0.3146894623607608</v>
+        <v>0.2819544376389302</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>0.4944266208442443</v>
+        <v>0.4851047579647485</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>0.5331903426277336</v>
+        <v>0.4956262619422276</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>0.6432175810554526</v>
+        <v>0.6291856324084577</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X &lt; 0.5419</t>
+          <t>X &lt; 0.541</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3875</v>
+        <v>3885</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-0.01178022806521994</v>
+        <v>-0.02165620662120915</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>0.01131953835191268</v>
+        <v>-0.0003969418621778686</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-0.06072837196619219</v>
+        <v>-0.07224250410702382</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>0.08350607538958599</v>
+        <v>0.07161195672107112</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>0.2543926691631313</v>
+        <v>0.2383537646170808</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>0.308436626840205</v>
+        <v>0.2941047973745441</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>0.2378700080467482</v>
+        <v>0.2218525394123603</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>0.1972172736275795</v>
+        <v>0.1813233295579053</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>0.3051388697246296</v>
+        <v>0.2870965864001391</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>0.3976061171992313</v>
+        <v>0.37749381286838</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>0.4137553586196248</v>
+        <v>0.3936050089361203</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>0.5659252830567212</v>
+        <v>0.5435028093252683</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>0.6506238859180016</v>
+        <v>0.6261241861681199</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>0.7105018178449853</v>
+        <v>0.6839536433808391</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X &lt; 0.5782</t>
+          <t>X &lt; 0.5773</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>3906</v>
+        <v>3917</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>0.05799695747279543</v>
+        <v>0.05986272982039509</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>0.1447534149418956</v>
+        <v>0.1444306114639105</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>0.0957152075007528</v>
+        <v>0.09545782669337655</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>0.1888061806896815</v>
+        <v>0.1883116883116784</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>0.3796470118967861</v>
+        <v>0.3752075943657402</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>0.4611995251623711</v>
+        <v>0.4582406544821112</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>0.4416715741285984</v>
+        <v>0.4370931909278397</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>0.4488166179240736</v>
+        <v>0.4441310284949012</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>0.5043259366018233</v>
+        <v>0.497812225160601</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>0.4614952863037729</v>
+        <v>0.4532835372716946</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>0.4759094360841161</v>
+        <v>0.4676160948519623</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>0.6271608879375066</v>
+        <v>0.6167837643580185</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>0.7078694479176733</v>
+        <v>0.6955216147195102</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>0.692273451229525</v>
+        <v>0.6783417000614662</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>X &lt; 0.6145</t>
+          <t>X &lt; 0.6136</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>3942</v>
+        <v>3951</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>0.1107401009447813</v>
+        <v>0.08827364433602725</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>0.1820506331038985</v>
+        <v>0.15854051211209</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>0.02868429584612642</v>
+        <v>0.005653566054370174</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>0.1220965745063936</v>
+        <v>0.1240487611353487</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>0.3568970606259043</v>
+        <v>0.3303756786729011</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>0.4657272510150463</v>
+        <v>0.4402859177941139</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>0.4456062285782565</v>
+        <v>0.444059816541639</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>0.44842813202456</v>
+        <v>0.4723080069758439</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>0.477539152857581</v>
+        <v>0.4999391398349644</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>0.401996399153326</v>
+        <v>0.4234271221243731</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>0.4143959355048707</v>
+        <v>0.4358735040371897</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>0.5392100262318777</v>
+        <v>0.5589531962390168</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>0.6914075819664589</v>
+        <v>0.6842066622423033</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>0.7287470184145448</v>
+        <v>0.7199349549885738</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X &lt; 0.6509</t>
+          <t>X &lt; 0.6498</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>3964</v>
+        <v>3975</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>0.07125897575179607</v>
+        <v>0.07263641984721403</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>0.1080990836452784</v>
+        <v>0.1078648396436463</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>0.003692529382625764</v>
+        <v>0.003690612931968928</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>0.0973023146513512</v>
+        <v>0.09706040509051661</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>0.2774758752428923</v>
+        <v>0.2740899296160606</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>0.4125066052287139</v>
+        <v>0.4100741634557608</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>0.3668317711434739</v>
+        <v>0.363226130644847</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>0.3166520709382539</v>
+        <v>0.3131174317282515</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>0.4208162976259118</v>
+        <v>0.4156958810740221</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>0.3409658332883438</v>
+        <v>0.3346551273058154</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>0.3773539640822037</v>
+        <v>0.370910746045773</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>0.552085696610618</v>
+        <v>0.5438715361419852</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>0.7011107960201954</v>
+        <v>0.6911307981508727</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>0.7142712263928885</v>
+        <v>0.7029915492112053</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X &lt; 0.6872</t>
+          <t>X &lt; 0.6861</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>3980</v>
+        <v>3991</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>0.03598855248593225</v>
+        <v>0.03734072256555976</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>0.06621450966835596</v>
+        <v>0.06609155460866845</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-0.01431024100168088</v>
+        <v>-0.01426328016663803</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>0.1045045174406525</v>
+        <v>0.1042417966936782</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>0.3319359853733417</v>
+        <v>0.3286080019052164</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>0.3924060215037173</v>
+        <v>0.3901344559579556</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>0.321487979746891</v>
+        <v>0.318213669617748</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>0.2947112983854581</v>
+        <v>0.2914483288586496</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>0.4233010500658594</v>
+        <v>0.4184876175341046</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>0.3905593687204032</v>
+        <v>0.3845352709007273</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>0.3757780706693055</v>
+        <v>0.3697652369324302</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>0.5750584638767364</v>
+        <v>0.567309585668049</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>0.7218017641211958</v>
+        <v>0.7124007021439667</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>0.7358219669777455</v>
+        <v>0.7252176585862316</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>X &lt; 0.7236</t>
+          <t>X &lt; 0.7224</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>3998</v>
+        <v>4008</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>0.04962498168205087</v>
+        <v>0.06387474561786632</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>0.09742406094046885</v>
+        <v>0.1106911894596507</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>-0.009447716385146521</v>
+        <v>0.004140058596917129</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>0.08446939970620093</v>
+        <v>0.07292185166749476</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>0.2585434896762564</v>
+        <v>0.2693660302846084</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>0.3450222325933083</v>
+        <v>0.3566724051862948</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>0.3739055277892689</v>
+        <v>0.3844173816854877</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>0.295212553277068</v>
+        <v>0.305983395579716</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>0.4479312599680227</v>
+        <v>0.4323315137602535</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>0.4365077800568926</v>
+        <v>0.4199609088804124</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>0.4458772920351848</v>
+        <v>0.4293285285165283</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>0.5944331499641251</v>
+        <v>0.6013591974262837</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>0.7386296334849192</v>
+        <v>0.7441679032960877</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>0.7786197477776966</v>
+        <v>0.7829448501564826</v>
       </c>
     </row>
   </sheetData>
